--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -14579,7 +14579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D146"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -14603,16 +14603,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
       <c r="B2" t="str">
-        <v>Badminton</v>
+        <v>Bike Tyre</v>
       </c>
       <c r="C2" t="str">
-        <v>Badminton</v>
+        <v>Bike Tube And Tyre</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -14620,13 +14620,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B3" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C3" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -14634,13 +14634,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B4" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C4" t="str">
-        <v>Lidl - Prawns , Kefir And Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -14651,38 +14651,38 @@
         <v>Groceries</v>
       </c>
       <c r="C5" t="str">
-        <v>Fruits For Lakshmi Pooja</v>
+        <v>Lidl - Prawns , Kefir And Yogurt</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-21</v>
       </c>
       <c r="B6" t="str">
-        <v>Movie</v>
+        <v>Groceries</v>
       </c>
       <c r="C6" t="str">
-        <v>Toxic</v>
+        <v>Fruits For Lakshmi Pooja</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-08-15</v>
+        <v>2026-08-18</v>
       </c>
       <c r="B7" t="str">
-        <v>Groceries</v>
+        <v>Movie</v>
       </c>
       <c r="C7" t="str">
-        <v>Sainsbury's And Lidl</v>
+        <v>Toxic</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -14690,13 +14690,13 @@
         <v>2026-08-15</v>
       </c>
       <c r="B8" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C8" t="str">
-        <v>Fruit</v>
+        <v>Sainsbury's And Lidl</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -14704,27 +14704,27 @@
         <v>2026-08-15</v>
       </c>
       <c r="B9" t="str">
-        <v>Meats</v>
+        <v>Fruits</v>
       </c>
       <c r="C9" t="str">
-        <v>Lamb, Samosa, Chicken Keema</v>
+        <v>Fruit</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-15</v>
       </c>
       <c r="B10" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C10" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Lamb, Samosa, Chicken Keema</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -14732,125 +14732,125 @@
         <v>2026-08-14</v>
       </c>
       <c r="B11" t="str">
-        <v>Badminton</v>
+        <v>Groceries</v>
       </c>
       <c r="C11" t="str">
-        <v>Badminton</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D11">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-14</v>
       </c>
       <c r="B12" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C12" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D12">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-10</v>
       </c>
       <c r="B13" t="str">
-        <v>Badminton</v>
+        <v>Travel</v>
       </c>
       <c r="C13" t="str">
-        <v>Badminton</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D13">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B14" t="str">
-        <v>Groceries</v>
+        <v>Badminton</v>
       </c>
       <c r="C14" t="str">
-        <v>Yogurt And Cheese</v>
+        <v>Badminton</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-08-04</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B15" t="str">
         <v>Groceries</v>
       </c>
       <c r="C15" t="str">
-        <v>Cucumber, Tissues, Corn Flour</v>
+        <v>Yogurt And Cheese</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-04</v>
       </c>
       <c r="B16" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C16" t="str">
-        <v>Oyster Card</v>
+        <v>Cucumber, Tissues, Corn Flour</v>
       </c>
       <c r="D16">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-28</v>
       </c>
       <c r="B17" t="str">
-        <v>Provisions</v>
+        <v>Travel</v>
       </c>
       <c r="C17" t="str">
-        <v>Egg, Office Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-27</v>
       </c>
       <c r="B18" t="str">
         <v>Provisions</v>
       </c>
       <c r="C18" t="str">
-        <v>Lidl- Yogurt</v>
+        <v>Egg, Office Yogurt</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-30</v>
       </c>
       <c r="B19" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C19" t="str">
-        <v>Praveen - Boba Tea</v>
+        <v>Lidl- Yogurt</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -14858,27 +14858,27 @@
         <v>2026-07-25</v>
       </c>
       <c r="B20" t="str">
-        <v>Abdul Son Marriage Gift</v>
+        <v>Eating Out</v>
       </c>
       <c r="C20" t="str">
-        <v>Gift</v>
+        <v>Praveen - Boba Tea</v>
       </c>
       <c r="D20">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-26</v>
+        <v>2026-07-25</v>
       </c>
       <c r="B21" t="str">
-        <v>Badminton</v>
+        <v>Abdul Son Marriage Gift</v>
       </c>
       <c r="C21" t="str">
-        <v>Badminton</v>
+        <v>Gift</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
@@ -14886,27 +14886,27 @@
         <v>2026-07-26</v>
       </c>
       <c r="B22" t="str">
-        <v>House</v>
+        <v>Badminton</v>
       </c>
       <c r="C22" t="str">
-        <v>Houzecheck - House Evaluation</v>
+        <v>Badminton</v>
       </c>
       <c r="D22">
-        <v>593</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-26</v>
       </c>
       <c r="B23" t="str">
-        <v>Travel</v>
+        <v>House</v>
       </c>
       <c r="C23" t="str">
-        <v>Norway - H&amp;m - Pau Baby Dress</v>
+        <v>Houzecheck - House Evaluation</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>593</v>
       </c>
     </row>
     <row r="24">
@@ -14917,7 +14917,7 @@
         <v>Travel</v>
       </c>
       <c r="C24" t="str">
-        <v>Norway - Bus Pass</v>
+        <v>Norway - H&amp;m - Pau Baby Dress</v>
       </c>
       <c r="D24">
         <v>12</v>
@@ -14925,58 +14925,58 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B25" t="str">
         <v>Travel</v>
       </c>
       <c r="C25" t="str">
-        <v>Norway - Radical Storage Oslo</v>
+        <v>Norway - Bus Pass</v>
       </c>
       <c r="D25">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B26" t="str">
         <v>Travel</v>
       </c>
       <c r="C26" t="str">
-        <v>Oyster Card</v>
+        <v>Norway - Radical Storage Oslo</v>
       </c>
       <c r="D26">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B27" t="str">
-        <v>Norway</v>
+        <v>Travel</v>
       </c>
       <c r="C27" t="str">
-        <v>Travel Insurance</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D27">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B28" t="str">
         <v>Norway</v>
       </c>
       <c r="C28" t="str">
-        <v>Chocolate</v>
+        <v>Travel Insurance</v>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -14984,27 +14984,27 @@
         <v>2026-07-13</v>
       </c>
       <c r="B29" t="str">
-        <v>House</v>
+        <v>Norway</v>
       </c>
       <c r="C29" t="str">
-        <v>Leadenhall</v>
+        <v>Chocolate</v>
       </c>
       <c r="D29">
-        <v>820</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B30" t="str">
-        <v>Provisions</v>
+        <v>House</v>
       </c>
       <c r="C30" t="str">
-        <v>Yogurt</v>
+        <v>Leadenhall</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>820</v>
       </c>
     </row>
     <row r="31">
@@ -15012,13 +15012,13 @@
         <v>2026-07-11</v>
       </c>
       <c r="B31" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C31" t="str">
-        <v>Amarino Ice Cream</v>
+        <v>Yogurt</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -15026,55 +15026,55 @@
         <v>2026-07-11</v>
       </c>
       <c r="B32" t="str">
-        <v>Gifts To Norway</v>
+        <v>Eating Out</v>
       </c>
       <c r="C32" t="str">
-        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
+        <v>Amarino Ice Cream</v>
       </c>
       <c r="D32">
-        <v>97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B33" t="str">
-        <v>Praveen</v>
+        <v>Gifts To Norway</v>
       </c>
       <c r="C33" t="str">
-        <v>Badminton</v>
+        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B34" t="str">
-        <v>Travel</v>
+        <v>Praveen</v>
       </c>
       <c r="C34" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D34">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B35" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C35" t="str">
-        <v>Shakti</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D35">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
@@ -15082,13 +15082,13 @@
         <v>2026-07-05</v>
       </c>
       <c r="B36" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C36" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D36">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -15096,41 +15096,41 @@
         <v>2026-07-05</v>
       </c>
       <c r="B37" t="str">
-        <v>Haircut</v>
+        <v>Meats</v>
       </c>
       <c r="C37" t="str">
-        <v>Haircut</v>
+        <v>Chicken</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B38" t="str">
-        <v>Provisions</v>
+        <v>Haircut</v>
       </c>
       <c r="C38" t="str">
-        <v>Lidl, Sainsbury's, Iceland</v>
+        <v>Haircut</v>
       </c>
       <c r="D38">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B39" t="str">
-        <v>Superdrug</v>
+        <v>Provisions</v>
       </c>
       <c r="C39" t="str">
-        <v>Shoes Deodorant</v>
+        <v>Lidl, Sainsbury's, Iceland</v>
       </c>
       <c r="D39">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
@@ -15138,83 +15138,83 @@
         <v>2026-07-04</v>
       </c>
       <c r="B40" t="str">
-        <v>Medicine</v>
+        <v>Superdrug</v>
       </c>
       <c r="C40" t="str">
-        <v>H&amp;b</v>
+        <v>Shoes Deodorant</v>
       </c>
       <c r="D40">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B41" t="str">
-        <v>Praveen - Badminton</v>
+        <v>Medicine</v>
       </c>
       <c r="C41" t="str">
-        <v>Badminton</v>
+        <v>H&amp;b</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-06-30</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B42" t="str">
-        <v>Provisions</v>
+        <v>Praveen - Badminton</v>
       </c>
       <c r="C42" t="str">
-        <v>Lidl - Detergent</v>
+        <v>Badminton</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-06-29</v>
+        <v>2026-06-30</v>
       </c>
       <c r="B43" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C43" t="str">
-        <v>Praveen &amp; Poornima - Cake</v>
+        <v>Lidl - Detergent</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-06-28</v>
+        <v>2026-06-29</v>
       </c>
       <c r="B44" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C44" t="str">
-        <v>Poornima And Praveen (tajrish Restaurant)</v>
+        <v>Praveen &amp; Poornima - Cake</v>
       </c>
       <c r="D44">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="B45" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C45" t="str">
-        <v>Lidl</v>
+        <v>Poornima And Praveen (tajrish Restaurant)</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46">
@@ -15225,10 +15225,10 @@
         <v>Groceries</v>
       </c>
       <c r="C46" t="str">
-        <v>Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -15236,13 +15236,13 @@
         <v>2026-06-27</v>
       </c>
       <c r="B47" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C47" t="str">
-        <v>Grapes, Guava, Pomegranate, Avacado</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -15250,41 +15250,41 @@
         <v>2026-06-27</v>
       </c>
       <c r="B48" t="str">
-        <v>Provisions</v>
+        <v>Fruits</v>
       </c>
       <c r="C48" t="str">
-        <v>M&amp;s</v>
+        <v>Grapes, Guava, Pomegranate, Avacado</v>
       </c>
       <c r="D48">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-27</v>
       </c>
       <c r="B49" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C49" t="str">
-        <v>Oyster</v>
+        <v>M&amp;s</v>
       </c>
       <c r="D49">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-26</v>
       </c>
       <c r="B50" t="str">
-        <v>Fan</v>
+        <v>Travel</v>
       </c>
       <c r="C50" t="str">
-        <v>Fan</v>
+        <v>Oyster</v>
       </c>
       <c r="D50">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
@@ -15292,13 +15292,13 @@
         <v>2026-06-24</v>
       </c>
       <c r="B51" t="str">
-        <v>Groceries</v>
+        <v>Fan</v>
       </c>
       <c r="C51" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Fan</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
@@ -15306,27 +15306,27 @@
         <v>2026-06-24</v>
       </c>
       <c r="B52" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C52" t="str">
-        <v>Yogurt, Dates, Prunes</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D52">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-06-21</v>
+        <v>2026-06-24</v>
       </c>
       <c r="B53" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C53" t="str">
-        <v>Chicken</v>
+        <v>Yogurt, Dates, Prunes</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
@@ -15337,38 +15337,38 @@
         <v>Meats</v>
       </c>
       <c r="C54" t="str">
-        <v>Fish - Salmon And Travelly</v>
+        <v>Chicken</v>
       </c>
       <c r="D54">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-06-14</v>
+        <v>2026-06-21</v>
       </c>
       <c r="B55" t="str">
-        <v>Travel</v>
+        <v>Meats</v>
       </c>
       <c r="C55" t="str">
-        <v>Flight Trd - Lhr</v>
+        <v>Fish - Salmon And Travelly</v>
       </c>
       <c r="D55">
-        <v>91</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-06-13</v>
+        <v>2026-06-14</v>
       </c>
       <c r="B56" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C56" t="str">
-        <v>Lidl &amp; Sainsbury's</v>
+        <v>Flight Trd - Lhr</v>
       </c>
       <c r="D56">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57">
@@ -15376,27 +15376,27 @@
         <v>2026-06-13</v>
       </c>
       <c r="B57" t="str">
-        <v>Belgravia</v>
+        <v>Groceries</v>
       </c>
       <c r="C57" t="str">
-        <v>Belgravia</v>
+        <v>Lidl &amp; Sainsbury's</v>
       </c>
       <c r="D57">
-        <v>186</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-06-18</v>
+        <v>2026-06-13</v>
       </c>
       <c r="B58" t="str">
-        <v>Provisions</v>
+        <v>Belgravia</v>
       </c>
       <c r="C58" t="str">
-        <v>Egg</v>
+        <v>Belgravia</v>
       </c>
       <c r="D58">
-        <v>5</v>
+        <v>186</v>
       </c>
     </row>
     <row r="59">
@@ -15404,69 +15404,69 @@
         <v>2026-06-18</v>
       </c>
       <c r="B59" t="str">
-        <v>Cycle</v>
+        <v>Provisions</v>
       </c>
       <c r="C59" t="str">
-        <v>Cycle</v>
+        <v>Egg</v>
       </c>
       <c r="D59">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-18</v>
       </c>
       <c r="B60" t="str">
-        <v>Travel</v>
+        <v>Cycle</v>
       </c>
       <c r="C60" t="str">
-        <v>Lgw - Oslo</v>
+        <v>Cycle</v>
       </c>
       <c r="D60">
-        <v>168</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="B61" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C61" t="str">
-        <v>Lidl</v>
+        <v>Lgw - Oslo</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-10</v>
       </c>
       <c r="B62" t="str">
         <v>Groceries</v>
       </c>
       <c r="C62" t="str">
-        <v>Lidl And Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D62">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B63" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C63" t="str">
-        <v>Vegetables, Fruits</v>
+        <v>Lidl And Sainsbury's</v>
       </c>
       <c r="D63">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
@@ -15474,83 +15474,83 @@
         <v>2026-06-06</v>
       </c>
       <c r="B64" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C64" t="str">
-        <v>Lamb</v>
+        <v>Vegetables, Fruits</v>
       </c>
       <c r="D64">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-06-12</v>
+        <v>2026-06-06</v>
       </c>
       <c r="B65" t="str">
-        <v>Movie</v>
+        <v>Meats</v>
       </c>
       <c r="C65" t="str">
-        <v>Peddi</v>
+        <v>Lamb</v>
       </c>
       <c r="D65">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-05-31</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B66" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C66" t="str">
-        <v>Yogurt, Corn, Kefir</v>
+        <v>Peddi</v>
       </c>
       <c r="D66">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-31</v>
       </c>
       <c r="B67" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C67" t="str">
-        <v>Oyster Card</v>
+        <v>Yogurt, Corn, Kefir</v>
       </c>
       <c r="D67">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-29</v>
       </c>
       <c r="B68" t="str">
-        <v>Amazon</v>
+        <v>Travel</v>
       </c>
       <c r="C68" t="str">
-        <v>Face Wash, Moisturizer</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D68">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-28</v>
       </c>
       <c r="B69" t="str">
-        <v>Eating Out</v>
+        <v>Amazon</v>
       </c>
       <c r="C69" t="str">
-        <v>Praveen</v>
+        <v>Face Wash, Moisturizer</v>
       </c>
       <c r="D69">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="70">
@@ -15558,13 +15558,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B70" t="str">
-        <v>Meats</v>
+        <v>Eating Out</v>
       </c>
       <c r="C70" t="str">
-        <v>Chicken</v>
+        <v>Praveen</v>
       </c>
       <c r="D70">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71">
@@ -15572,13 +15572,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B71" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C71" t="str">
-        <v>Shakto</v>
+        <v>Chicken</v>
       </c>
       <c r="D71">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -15589,24 +15589,24 @@
         <v>Groceries</v>
       </c>
       <c r="C72" t="str">
-        <v>Bread, Avacado, Lemon, Onion</v>
+        <v>Shakto</v>
       </c>
       <c r="D72">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="B73" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C73" t="str">
-        <v>Praveen Cake</v>
+        <v>Bread, Avacado, Lemon, Onion</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -15614,10 +15614,10 @@
         <v>2026-05-23</v>
       </c>
       <c r="B74" t="str">
-        <v>Fruits</v>
+        <v>Eating Out</v>
       </c>
       <c r="C74" t="str">
-        <v>Avacado, Guava</v>
+        <v>Praveen Cake</v>
       </c>
       <c r="D74">
         <v>5</v>
@@ -15628,55 +15628,55 @@
         <v>2026-05-23</v>
       </c>
       <c r="B75" t="str">
-        <v>Groceries</v>
+        <v>Fruits</v>
       </c>
       <c r="C75" t="str">
-        <v>Corn, Yogurt, Cucumber, Cake</v>
+        <v>Avacado, Guava</v>
       </c>
       <c r="D75">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="B76" t="str">
         <v>Groceries</v>
       </c>
       <c r="C76" t="str">
-        <v>Banana</v>
+        <v>Corn, Yogurt, Cucumber, Cake</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="B77" t="str">
         <v>Groceries</v>
       </c>
       <c r="C77" t="str">
-        <v>Potatoes And Dish Was Liquid</v>
+        <v>Banana</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="B78" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C78" t="str">
-        <v>Lamb</v>
+        <v>Potatoes And Dish Was Liquid</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -15684,27 +15684,27 @@
         <v>2026-05-17</v>
       </c>
       <c r="B79" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C79" t="str">
-        <v>Sainsbury's - Carrots, Onion</v>
+        <v>Lamb</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="B80" t="str">
         <v>Groceries</v>
       </c>
       <c r="C80" t="str">
-        <v>Shakti</v>
+        <v>Sainsbury's - Carrots, Onion</v>
       </c>
       <c r="D80">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -15712,55 +15712,55 @@
         <v>2026-05-16</v>
       </c>
       <c r="B81" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C81" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D81">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="B82" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C82" t="str">
-        <v>Yogurt, Vegetables</v>
+        <v>Chicken</v>
       </c>
       <c r="D82">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B83" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C83" t="str">
-        <v>Munich - Gifts To Office</v>
+        <v>Yogurt, Vegetables</v>
       </c>
       <c r="D83">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="B84" t="str">
         <v>Travel</v>
       </c>
       <c r="C84" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Gifts To Office</v>
       </c>
       <c r="D84">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
@@ -15771,10 +15771,10 @@
         <v>Travel</v>
       </c>
       <c r="C85" t="str">
-        <v>Munich - Water And Juice</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D85">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86">
@@ -15785,10 +15785,10 @@
         <v>Travel</v>
       </c>
       <c r="C86" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Water And Juice</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -15799,24 +15799,24 @@
         <v>Travel</v>
       </c>
       <c r="C87" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D87">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="B88" t="str">
         <v>Travel</v>
       </c>
       <c r="C88" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D88">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89">
@@ -15827,10 +15827,10 @@
         <v>Travel</v>
       </c>
       <c r="C89" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
@@ -15841,10 +15841,10 @@
         <v>Travel</v>
       </c>
       <c r="C90" t="str">
-        <v>Munich - Bmw Museum Ticket</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D90">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -15855,10 +15855,10 @@
         <v>Travel</v>
       </c>
       <c r="C91" t="str">
-        <v>Munich Lunch</v>
+        <v>Munich - Bmw Museum Ticket</v>
       </c>
       <c r="D91">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
@@ -15869,10 +15869,10 @@
         <v>Travel</v>
       </c>
       <c r="C92" t="str">
-        <v>Munich Walking Tour</v>
+        <v>Munich Lunch</v>
       </c>
       <c r="D92">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93">
@@ -15883,24 +15883,24 @@
         <v>Travel</v>
       </c>
       <c r="C93" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich Walking Tour</v>
       </c>
       <c r="D93">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B94" t="str">
         <v>Travel</v>
       </c>
       <c r="C94" t="str">
-        <v>Dinner - Mac And Cheese</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D94">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -15911,10 +15911,10 @@
         <v>Travel</v>
       </c>
       <c r="C95" t="str">
-        <v>Pretzel Snack</v>
+        <v>Dinner - Mac And Cheese</v>
       </c>
       <c r="D95">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96">
@@ -15925,10 +15925,10 @@
         <v>Travel</v>
       </c>
       <c r="C96" t="str">
-        <v>Lidl - Water, Coke, Yogurt</v>
+        <v>Pretzel Snack</v>
       </c>
       <c r="D96">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
@@ -15939,10 +15939,10 @@
         <v>Travel</v>
       </c>
       <c r="C97" t="str">
-        <v>Germany Public Transport Ticket</v>
+        <v>Lidl - Water, Coke, Yogurt</v>
       </c>
       <c r="D97">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -15950,27 +15950,27 @@
         <v>2026-05-09</v>
       </c>
       <c r="B98" t="str">
-        <v>Eating Out</v>
+        <v>Travel</v>
       </c>
       <c r="C98" t="str">
-        <v>Airport Pret</v>
+        <v>Germany Public Transport Ticket</v>
       </c>
       <c r="D98">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B99" t="str">
-        <v>Boots</v>
+        <v>Eating Out</v>
       </c>
       <c r="C99" t="str">
-        <v>Face Moisturizer</v>
+        <v>Airport Pret</v>
       </c>
       <c r="D99">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
@@ -15978,13 +15978,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B100" t="str">
-        <v>Provisions</v>
+        <v>Boots</v>
       </c>
       <c r="C100" t="str">
-        <v>Eggs</v>
+        <v>Face Moisturizer</v>
       </c>
       <c r="D100">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101">
@@ -15992,13 +15992,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B101" t="str">
-        <v>Shopping</v>
+        <v>Provisions</v>
       </c>
       <c r="C101" t="str">
-        <v>Belt</v>
+        <v>Eggs</v>
       </c>
       <c r="D101">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -16006,10 +16006,10 @@
         <v>2026-05-08</v>
       </c>
       <c r="B102" t="str">
-        <v>Eating Out</v>
+        <v>Shopping</v>
       </c>
       <c r="C102" t="str">
-        <v>Praveen</v>
+        <v>Belt</v>
       </c>
       <c r="D102">
         <v>7</v>
@@ -16017,30 +16017,30 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B103" t="str">
-        <v>Travel</v>
+        <v>Eating Out</v>
       </c>
       <c r="C103" t="str">
-        <v>Oyster Card</v>
+        <v>Praveen</v>
       </c>
       <c r="D103">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2026-04-18</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B104" t="str">
-        <v>Souvenir</v>
+        <v>Travel</v>
       </c>
       <c r="C104" t="str">
-        <v>Gift, Biscuits</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D104">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105">
@@ -16048,55 +16048,55 @@
         <v>2026-04-18</v>
       </c>
       <c r="B105" t="str">
-        <v>Groceries</v>
+        <v>Souvenir</v>
       </c>
       <c r="C105" t="str">
-        <v>Corn And Gauva</v>
+        <v>Gift, Biscuits</v>
       </c>
       <c r="D105">
-        <v>3.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-18</v>
       </c>
       <c r="B106" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C106" t="str">
-        <v>Oyster Card</v>
+        <v>Corn And Gauva</v>
       </c>
       <c r="D106">
-        <v>30</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2026-03-31</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B107" t="str">
         <v>Travel</v>
       </c>
       <c r="C107" t="str">
-        <v>Total Tfl Cost</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D107">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2026-04-11</v>
+        <v>2026-03-31</v>
       </c>
       <c r="B108" t="str">
-        <v>Praveen Shoes</v>
+        <v>Travel</v>
       </c>
       <c r="C108" t="str">
-        <v>Shoes</v>
+        <v>Total Tfl Cost</v>
       </c>
       <c r="D108">
-        <v>110</v>
+        <v>67</v>
       </c>
     </row>
     <row r="109">
@@ -16104,27 +16104,27 @@
         <v>2026-04-11</v>
       </c>
       <c r="B109" t="str">
-        <v>Eating Out</v>
+        <v>Praveen Shoes</v>
       </c>
       <c r="C109" t="str">
-        <v>Spitalfield Market</v>
+        <v>Shoes</v>
       </c>
       <c r="D109">
-        <v>8</v>
+        <v>110</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="B110" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C110" t="str">
-        <v>Too Good To Go</v>
+        <v>Spitalfield Market</v>
       </c>
       <c r="D110">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111">
@@ -16132,10 +16132,10 @@
         <v>2026-04-09</v>
       </c>
       <c r="B111" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C111" t="str">
-        <v>Yogurt</v>
+        <v>Too Good To Go</v>
       </c>
       <c r="D111">
         <v>4</v>
@@ -16143,72 +16143,72 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-09</v>
       </c>
       <c r="B112" t="str">
-        <v>Visa Fee</v>
+        <v>Groceries</v>
       </c>
       <c r="C112" t="str">
-        <v>Visa Gee</v>
+        <v>Yogurt</v>
       </c>
       <c r="D112">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B113" t="str">
-        <v>Travel</v>
+        <v>Visa Fee</v>
       </c>
       <c r="C113" t="str">
-        <v>Oyster Card</v>
+        <v>Visa Gee</v>
       </c>
       <c r="D113">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B114" t="str">
-        <v>Visa Picture</v>
+        <v>Travel</v>
       </c>
       <c r="C114" t="str">
-        <v>Snappy Snap</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D114">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B115" t="str">
-        <v>Provisions</v>
+        <v>Visa Picture</v>
       </c>
       <c r="C115" t="str">
-        <v>Water Bottle</v>
+        <v>Snappy Snap</v>
       </c>
       <c r="D115">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B116" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C116" t="str">
-        <v>Poornima Roti Curry(malaysia Food)</v>
+        <v>Water Bottle</v>
       </c>
       <c r="D116">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -16216,41 +16216,41 @@
         <v>2026-04-06</v>
       </c>
       <c r="B117" t="str">
-        <v>Germany Visa Stuff</v>
+        <v>Eating Out</v>
       </c>
       <c r="C117" t="str">
-        <v>Travel Insurance, Airbnb</v>
+        <v>Poornima Roti Curry(malaysia Food)</v>
       </c>
       <c r="D117">
-        <v>111</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B118" t="str">
-        <v>Provisions</v>
+        <v>Germany Visa Stuff</v>
       </c>
       <c r="C118" t="str">
-        <v>Yogurt, Lemon</v>
+        <v>Travel Insurance, Airbnb</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>111</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="B119" t="str">
         <v>Provisions</v>
       </c>
       <c r="C119" t="str">
-        <v>Rice Flour, Oil,</v>
+        <v>Yogurt, Lemon</v>
       </c>
       <c r="D119">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -16258,13 +16258,13 @@
         <v>2026-04-04</v>
       </c>
       <c r="B120" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C120" t="str">
-        <v>Spinach, Ginger, Vegetable</v>
+        <v>Rice Flour, Oil,</v>
       </c>
       <c r="D120">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121">
@@ -16272,27 +16272,27 @@
         <v>2026-04-04</v>
       </c>
       <c r="B121" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C121" t="str">
-        <v>Lamb And Chicken</v>
+        <v>Spinach, Ginger, Vegetable</v>
       </c>
       <c r="D121">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-04</v>
       </c>
       <c r="B122" t="str">
-        <v>Cricket Tickets</v>
+        <v>Meats</v>
       </c>
       <c r="C122" t="str">
-        <v>Lords Women World Cup</v>
+        <v>Lamb And Chicken</v>
       </c>
       <c r="D122">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="123">
@@ -16300,27 +16300,27 @@
         <v>2026-04-02</v>
       </c>
       <c r="B123" t="str">
-        <v>Provisions</v>
+        <v>Cricket Tickets</v>
       </c>
       <c r="C123" t="str">
-        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
+        <v>Lords Women World Cup</v>
       </c>
       <c r="D123">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-02</v>
       </c>
       <c r="B124" t="str">
         <v>Provisions</v>
       </c>
       <c r="C124" t="str">
-        <v>Sainsbury's</v>
+        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
       </c>
       <c r="D124">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125">
@@ -16328,27 +16328,27 @@
         <v>2026-03-28</v>
       </c>
       <c r="B125" t="str">
-        <v>Fruits</v>
+        <v>Provisions</v>
       </c>
       <c r="C125" t="str">
-        <v>Blueberries, Avocado, Gauva</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D125">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-28</v>
       </c>
       <c r="B126" t="str">
-        <v>Movie</v>
+        <v>Fruits</v>
       </c>
       <c r="C126" t="str">
-        <v>Dhurandar</v>
+        <v>Blueberries, Avocado, Gauva</v>
       </c>
       <c r="D126">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
@@ -16356,69 +16356,69 @@
         <v>2026-03-25</v>
       </c>
       <c r="B127" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C127" t="str">
-        <v>Yogurt</v>
+        <v>Dhurandar</v>
       </c>
       <c r="D127">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-25</v>
       </c>
       <c r="B128" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C128" t="str">
-        <v>Pizza Pilgrims</v>
+        <v>Yogurt</v>
       </c>
       <c r="D128">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="B129" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C129" t="str">
-        <v>Milk, Yogurt, Flowers, Butter</v>
+        <v>Pizza Pilgrims</v>
       </c>
       <c r="D129">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="B130" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C130" t="str">
-        <v>Praveen</v>
+        <v>Milk, Yogurt, Flowers, Butter</v>
       </c>
       <c r="D130">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-17</v>
       </c>
       <c r="B131" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C131" t="str">
-        <v>Provisions</v>
+        <v>Praveen</v>
       </c>
       <c r="D131">
-        <v>59</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
@@ -16426,27 +16426,27 @@
         <v>2026-03-15</v>
       </c>
       <c r="B132" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C132" t="str">
-        <v>Vegetables</v>
+        <v>Provisions</v>
       </c>
       <c r="D132">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-15</v>
       </c>
       <c r="B133" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C133" t="str">
-        <v>Gauva, Blueberries</v>
+        <v>Vegetables</v>
       </c>
       <c r="D133">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="134">
@@ -16454,13 +16454,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B134" t="str">
-        <v>Eating Out</v>
+        <v>Fruits</v>
       </c>
       <c r="C134" t="str">
-        <v>Haleem And Samosa</v>
+        <v>Gauva, Blueberries</v>
       </c>
       <c r="D134">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
@@ -16468,13 +16468,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B135" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C135" t="str">
-        <v>Frozen Lotus Stem And Beans</v>
+        <v>Haleem And Samosa</v>
       </c>
       <c r="D135">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136">
@@ -16482,13 +16482,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B136" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C136" t="str">
-        <v>Vegetables</v>
+        <v>Frozen Lotus Stem And Beans</v>
       </c>
       <c r="D136">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137">
@@ -16496,27 +16496,27 @@
         <v>2026-03-14</v>
       </c>
       <c r="B137" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C137" t="str">
-        <v>Lidl</v>
+        <v>Vegetables</v>
       </c>
       <c r="D137">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-14</v>
       </c>
       <c r="B138" t="str">
-        <v>Medication</v>
+        <v>Provisions</v>
       </c>
       <c r="C138" t="str">
-        <v>Fish Oil, Pregnacare</v>
+        <v>Lidl</v>
       </c>
       <c r="D138">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139">
@@ -16524,69 +16524,69 @@
         <v>2026-03-09</v>
       </c>
       <c r="B139" t="str">
-        <v>Provisions</v>
+        <v>Medication</v>
       </c>
       <c r="C139" t="str">
-        <v>Yogurt, Oats, Sourdough, Detergent</v>
+        <v>Fish Oil, Pregnacare</v>
       </c>
       <c r="D139">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="B140" t="str">
-        <v>Washing</v>
+        <v>Provisions</v>
       </c>
       <c r="C140" t="str">
-        <v>Clothes</v>
+        <v>Yogurt, Oats, Sourdough, Detergent</v>
       </c>
       <c r="D140">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-08</v>
       </c>
       <c r="B141" t="str">
-        <v>Praveen</v>
+        <v>Washing</v>
       </c>
       <c r="C141" t="str">
-        <v>Praveen eating out</v>
+        <v>Clothes</v>
       </c>
       <c r="D141">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="B142" t="str">
-        <v>Meats</v>
+        <v>Praveen</v>
       </c>
       <c r="C142" t="str">
-        <v>Chicken and Fish</v>
+        <v>Praveen eating out</v>
       </c>
       <c r="D142">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-01</v>
       </c>
       <c r="B143" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C143" t="str">
-        <v>Vegetables</v>
+        <v>Chicken and Fish</v>
       </c>
       <c r="D143">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="144">
@@ -16594,32 +16594,46 @@
         <v>2026-03-07</v>
       </c>
       <c r="B144" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C144" t="str">
-        <v>Mobos Ethiopian Restaurant</v>
+        <v>Vegetables</v>
       </c>
       <c r="D144">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Eating Out</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Mobos Ethiopian Restaurant</v>
+      </c>
+      <c r="D145">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
         <v>2026-03-06</v>
       </c>
-      <c r="B145" t="str">
+      <c r="B146" t="str">
         <v>Provisions</v>
       </c>
-      <c r="C145" t="str">
+      <c r="C146" t="str">
         <v>Milk and Doritos</v>
       </c>
-      <c r="D145">
+      <c r="D146">
         <v>2.95</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D145"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D146"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -14579,7 +14579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D147"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -14603,30 +14603,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-25</v>
       </c>
       <c r="B2" t="str">
-        <v>Bike Tyre</v>
+        <v>Groceries</v>
       </c>
       <c r="C2" t="str">
-        <v>Bike Tube And Tyre</v>
+        <v>Sainsbury's , Tesco</v>
       </c>
       <c r="D2">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
       <c r="B3" t="str">
-        <v>Badminton</v>
+        <v>Bike Tyre</v>
       </c>
       <c r="C3" t="str">
-        <v>Badminton</v>
+        <v>Bike Tube And Tyre</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -14634,13 +14634,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B4" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C4" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -14648,13 +14648,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B5" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C5" t="str">
-        <v>Lidl - Prawns , Kefir And Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -14665,38 +14665,38 @@
         <v>Groceries</v>
       </c>
       <c r="C6" t="str">
-        <v>Fruits For Lakshmi Pooja</v>
+        <v>Lidl - Prawns , Kefir And Yogurt</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-21</v>
       </c>
       <c r="B7" t="str">
-        <v>Movie</v>
+        <v>Groceries</v>
       </c>
       <c r="C7" t="str">
-        <v>Toxic</v>
+        <v>Fruits For Lakshmi Pooja</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-08-15</v>
+        <v>2026-08-18</v>
       </c>
       <c r="B8" t="str">
-        <v>Groceries</v>
+        <v>Movie</v>
       </c>
       <c r="C8" t="str">
-        <v>Sainsbury's And Lidl</v>
+        <v>Toxic</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -14704,13 +14704,13 @@
         <v>2026-08-15</v>
       </c>
       <c r="B9" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C9" t="str">
-        <v>Fruit</v>
+        <v>Sainsbury's And Lidl</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -14718,27 +14718,27 @@
         <v>2026-08-15</v>
       </c>
       <c r="B10" t="str">
-        <v>Meats</v>
+        <v>Fruits</v>
       </c>
       <c r="C10" t="str">
-        <v>Lamb, Samosa, Chicken Keema</v>
+        <v>Fruit</v>
       </c>
       <c r="D10">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-15</v>
       </c>
       <c r="B11" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C11" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Lamb, Samosa, Chicken Keema</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -14746,125 +14746,125 @@
         <v>2026-08-14</v>
       </c>
       <c r="B12" t="str">
-        <v>Badminton</v>
+        <v>Groceries</v>
       </c>
       <c r="C12" t="str">
-        <v>Badminton</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D12">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-14</v>
       </c>
       <c r="B13" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C13" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-10</v>
       </c>
       <c r="B14" t="str">
-        <v>Badminton</v>
+        <v>Travel</v>
       </c>
       <c r="C14" t="str">
-        <v>Badminton</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D14">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B15" t="str">
-        <v>Groceries</v>
+        <v>Badminton</v>
       </c>
       <c r="C15" t="str">
-        <v>Yogurt And Cheese</v>
+        <v>Badminton</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-08-04</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B16" t="str">
         <v>Groceries</v>
       </c>
       <c r="C16" t="str">
-        <v>Cucumber, Tissues, Corn Flour</v>
+        <v>Yogurt And Cheese</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-04</v>
       </c>
       <c r="B17" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C17" t="str">
-        <v>Oyster Card</v>
+        <v>Cucumber, Tissues, Corn Flour</v>
       </c>
       <c r="D17">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-28</v>
       </c>
       <c r="B18" t="str">
-        <v>Provisions</v>
+        <v>Travel</v>
       </c>
       <c r="C18" t="str">
-        <v>Egg, Office Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-27</v>
       </c>
       <c r="B19" t="str">
         <v>Provisions</v>
       </c>
       <c r="C19" t="str">
-        <v>Lidl- Yogurt</v>
+        <v>Egg, Office Yogurt</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-30</v>
       </c>
       <c r="B20" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C20" t="str">
-        <v>Praveen - Boba Tea</v>
+        <v>Lidl- Yogurt</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -14872,27 +14872,27 @@
         <v>2026-07-25</v>
       </c>
       <c r="B21" t="str">
-        <v>Abdul Son Marriage Gift</v>
+        <v>Eating Out</v>
       </c>
       <c r="C21" t="str">
-        <v>Gift</v>
+        <v>Praveen - Boba Tea</v>
       </c>
       <c r="D21">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-07-26</v>
+        <v>2026-07-25</v>
       </c>
       <c r="B22" t="str">
-        <v>Badminton</v>
+        <v>Abdul Son Marriage Gift</v>
       </c>
       <c r="C22" t="str">
-        <v>Badminton</v>
+        <v>Gift</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -14900,27 +14900,27 @@
         <v>2026-07-26</v>
       </c>
       <c r="B23" t="str">
-        <v>House</v>
+        <v>Badminton</v>
       </c>
       <c r="C23" t="str">
-        <v>Houzecheck - House Evaluation</v>
+        <v>Badminton</v>
       </c>
       <c r="D23">
-        <v>593</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-26</v>
       </c>
       <c r="B24" t="str">
-        <v>Travel</v>
+        <v>House</v>
       </c>
       <c r="C24" t="str">
-        <v>Norway - H&amp;m - Pau Baby Dress</v>
+        <v>Houzecheck - House Evaluation</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>593</v>
       </c>
     </row>
     <row r="25">
@@ -14931,7 +14931,7 @@
         <v>Travel</v>
       </c>
       <c r="C25" t="str">
-        <v>Norway - Bus Pass</v>
+        <v>Norway - H&amp;m - Pau Baby Dress</v>
       </c>
       <c r="D25">
         <v>12</v>
@@ -14939,58 +14939,58 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B26" t="str">
         <v>Travel</v>
       </c>
       <c r="C26" t="str">
-        <v>Norway - Radical Storage Oslo</v>
+        <v>Norway - Bus Pass</v>
       </c>
       <c r="D26">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B27" t="str">
         <v>Travel</v>
       </c>
       <c r="C27" t="str">
-        <v>Oyster Card</v>
+        <v>Norway - Radical Storage Oslo</v>
       </c>
       <c r="D27">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B28" t="str">
-        <v>Norway</v>
+        <v>Travel</v>
       </c>
       <c r="C28" t="str">
-        <v>Travel Insurance</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D28">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B29" t="str">
         <v>Norway</v>
       </c>
       <c r="C29" t="str">
-        <v>Chocolate</v>
+        <v>Travel Insurance</v>
       </c>
       <c r="D29">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -14998,27 +14998,27 @@
         <v>2026-07-13</v>
       </c>
       <c r="B30" t="str">
-        <v>House</v>
+        <v>Norway</v>
       </c>
       <c r="C30" t="str">
-        <v>Leadenhall</v>
+        <v>Chocolate</v>
       </c>
       <c r="D30">
-        <v>820</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B31" t="str">
-        <v>Provisions</v>
+        <v>House</v>
       </c>
       <c r="C31" t="str">
-        <v>Yogurt</v>
+        <v>Leadenhall</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>820</v>
       </c>
     </row>
     <row r="32">
@@ -15026,13 +15026,13 @@
         <v>2026-07-11</v>
       </c>
       <c r="B32" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C32" t="str">
-        <v>Amarino Ice Cream</v>
+        <v>Yogurt</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -15040,55 +15040,55 @@
         <v>2026-07-11</v>
       </c>
       <c r="B33" t="str">
-        <v>Gifts To Norway</v>
+        <v>Eating Out</v>
       </c>
       <c r="C33" t="str">
-        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
+        <v>Amarino Ice Cream</v>
       </c>
       <c r="D33">
-        <v>97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B34" t="str">
-        <v>Praveen</v>
+        <v>Gifts To Norway</v>
       </c>
       <c r="C34" t="str">
-        <v>Badminton</v>
+        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B35" t="str">
-        <v>Travel</v>
+        <v>Praveen</v>
       </c>
       <c r="C35" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D35">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B36" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C36" t="str">
-        <v>Shakti</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D36">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
@@ -15096,13 +15096,13 @@
         <v>2026-07-05</v>
       </c>
       <c r="B37" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C37" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D37">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -15110,41 +15110,41 @@
         <v>2026-07-05</v>
       </c>
       <c r="B38" t="str">
-        <v>Haircut</v>
+        <v>Meats</v>
       </c>
       <c r="C38" t="str">
-        <v>Haircut</v>
+        <v>Chicken</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B39" t="str">
-        <v>Provisions</v>
+        <v>Haircut</v>
       </c>
       <c r="C39" t="str">
-        <v>Lidl, Sainsbury's, Iceland</v>
+        <v>Haircut</v>
       </c>
       <c r="D39">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B40" t="str">
-        <v>Superdrug</v>
+        <v>Provisions</v>
       </c>
       <c r="C40" t="str">
-        <v>Shoes Deodorant</v>
+        <v>Lidl, Sainsbury's, Iceland</v>
       </c>
       <c r="D40">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
@@ -15152,83 +15152,83 @@
         <v>2026-07-04</v>
       </c>
       <c r="B41" t="str">
-        <v>Medicine</v>
+        <v>Superdrug</v>
       </c>
       <c r="C41" t="str">
-        <v>H&amp;b</v>
+        <v>Shoes Deodorant</v>
       </c>
       <c r="D41">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B42" t="str">
-        <v>Praveen - Badminton</v>
+        <v>Medicine</v>
       </c>
       <c r="C42" t="str">
-        <v>Badminton</v>
+        <v>H&amp;b</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-06-30</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B43" t="str">
-        <v>Provisions</v>
+        <v>Praveen - Badminton</v>
       </c>
       <c r="C43" t="str">
-        <v>Lidl - Detergent</v>
+        <v>Badminton</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-06-29</v>
+        <v>2026-06-30</v>
       </c>
       <c r="B44" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C44" t="str">
-        <v>Praveen &amp; Poornima - Cake</v>
+        <v>Lidl - Detergent</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-06-28</v>
+        <v>2026-06-29</v>
       </c>
       <c r="B45" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C45" t="str">
-        <v>Poornima And Praveen (tajrish Restaurant)</v>
+        <v>Praveen &amp; Poornima - Cake</v>
       </c>
       <c r="D45">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="B46" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C46" t="str">
-        <v>Lidl</v>
+        <v>Poornima And Praveen (tajrish Restaurant)</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47">
@@ -15239,10 +15239,10 @@
         <v>Groceries</v>
       </c>
       <c r="C47" t="str">
-        <v>Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -15250,13 +15250,13 @@
         <v>2026-06-27</v>
       </c>
       <c r="B48" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C48" t="str">
-        <v>Grapes, Guava, Pomegranate, Avacado</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D48">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -15264,41 +15264,41 @@
         <v>2026-06-27</v>
       </c>
       <c r="B49" t="str">
-        <v>Provisions</v>
+        <v>Fruits</v>
       </c>
       <c r="C49" t="str">
-        <v>M&amp;s</v>
+        <v>Grapes, Guava, Pomegranate, Avacado</v>
       </c>
       <c r="D49">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-27</v>
       </c>
       <c r="B50" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C50" t="str">
-        <v>Oyster</v>
+        <v>M&amp;s</v>
       </c>
       <c r="D50">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-26</v>
       </c>
       <c r="B51" t="str">
-        <v>Fan</v>
+        <v>Travel</v>
       </c>
       <c r="C51" t="str">
-        <v>Fan</v>
+        <v>Oyster</v>
       </c>
       <c r="D51">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -15306,13 +15306,13 @@
         <v>2026-06-24</v>
       </c>
       <c r="B52" t="str">
-        <v>Groceries</v>
+        <v>Fan</v>
       </c>
       <c r="C52" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Fan</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53">
@@ -15320,27 +15320,27 @@
         <v>2026-06-24</v>
       </c>
       <c r="B53" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C53" t="str">
-        <v>Yogurt, Dates, Prunes</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D53">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-06-21</v>
+        <v>2026-06-24</v>
       </c>
       <c r="B54" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C54" t="str">
-        <v>Chicken</v>
+        <v>Yogurt, Dates, Prunes</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
@@ -15351,38 +15351,38 @@
         <v>Meats</v>
       </c>
       <c r="C55" t="str">
-        <v>Fish - Salmon And Travelly</v>
+        <v>Chicken</v>
       </c>
       <c r="D55">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-06-14</v>
+        <v>2026-06-21</v>
       </c>
       <c r="B56" t="str">
-        <v>Travel</v>
+        <v>Meats</v>
       </c>
       <c r="C56" t="str">
-        <v>Flight Trd - Lhr</v>
+        <v>Fish - Salmon And Travelly</v>
       </c>
       <c r="D56">
-        <v>91</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-06-13</v>
+        <v>2026-06-14</v>
       </c>
       <c r="B57" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C57" t="str">
-        <v>Lidl &amp; Sainsbury's</v>
+        <v>Flight Trd - Lhr</v>
       </c>
       <c r="D57">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58">
@@ -15390,27 +15390,27 @@
         <v>2026-06-13</v>
       </c>
       <c r="B58" t="str">
-        <v>Belgravia</v>
+        <v>Groceries</v>
       </c>
       <c r="C58" t="str">
-        <v>Belgravia</v>
+        <v>Lidl &amp; Sainsbury's</v>
       </c>
       <c r="D58">
-        <v>186</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-06-18</v>
+        <v>2026-06-13</v>
       </c>
       <c r="B59" t="str">
-        <v>Provisions</v>
+        <v>Belgravia</v>
       </c>
       <c r="C59" t="str">
-        <v>Egg</v>
+        <v>Belgravia</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>186</v>
       </c>
     </row>
     <row r="60">
@@ -15418,69 +15418,69 @@
         <v>2026-06-18</v>
       </c>
       <c r="B60" t="str">
-        <v>Cycle</v>
+        <v>Provisions</v>
       </c>
       <c r="C60" t="str">
-        <v>Cycle</v>
+        <v>Egg</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-18</v>
       </c>
       <c r="B61" t="str">
-        <v>Travel</v>
+        <v>Cycle</v>
       </c>
       <c r="C61" t="str">
-        <v>Lgw - Oslo</v>
+        <v>Cycle</v>
       </c>
       <c r="D61">
-        <v>168</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="B62" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C62" t="str">
-        <v>Lidl</v>
+        <v>Lgw - Oslo</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-10</v>
       </c>
       <c r="B63" t="str">
         <v>Groceries</v>
       </c>
       <c r="C63" t="str">
-        <v>Lidl And Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D63">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B64" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C64" t="str">
-        <v>Vegetables, Fruits</v>
+        <v>Lidl And Sainsbury's</v>
       </c>
       <c r="D64">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -15488,83 +15488,83 @@
         <v>2026-06-06</v>
       </c>
       <c r="B65" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C65" t="str">
-        <v>Lamb</v>
+        <v>Vegetables, Fruits</v>
       </c>
       <c r="D65">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-06-12</v>
+        <v>2026-06-06</v>
       </c>
       <c r="B66" t="str">
-        <v>Movie</v>
+        <v>Meats</v>
       </c>
       <c r="C66" t="str">
-        <v>Peddi</v>
+        <v>Lamb</v>
       </c>
       <c r="D66">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-05-31</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B67" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C67" t="str">
-        <v>Yogurt, Corn, Kefir</v>
+        <v>Peddi</v>
       </c>
       <c r="D67">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-31</v>
       </c>
       <c r="B68" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C68" t="str">
-        <v>Oyster Card</v>
+        <v>Yogurt, Corn, Kefir</v>
       </c>
       <c r="D68">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-29</v>
       </c>
       <c r="B69" t="str">
-        <v>Amazon</v>
+        <v>Travel</v>
       </c>
       <c r="C69" t="str">
-        <v>Face Wash, Moisturizer</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D69">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-28</v>
       </c>
       <c r="B70" t="str">
-        <v>Eating Out</v>
+        <v>Amazon</v>
       </c>
       <c r="C70" t="str">
-        <v>Praveen</v>
+        <v>Face Wash, Moisturizer</v>
       </c>
       <c r="D70">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="71">
@@ -15572,13 +15572,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B71" t="str">
-        <v>Meats</v>
+        <v>Eating Out</v>
       </c>
       <c r="C71" t="str">
-        <v>Chicken</v>
+        <v>Praveen</v>
       </c>
       <c r="D71">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72">
@@ -15586,13 +15586,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B72" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C72" t="str">
-        <v>Shakto</v>
+        <v>Chicken</v>
       </c>
       <c r="D72">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -15603,24 +15603,24 @@
         <v>Groceries</v>
       </c>
       <c r="C73" t="str">
-        <v>Bread, Avacado, Lemon, Onion</v>
+        <v>Shakto</v>
       </c>
       <c r="D73">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="B74" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C74" t="str">
-        <v>Praveen Cake</v>
+        <v>Bread, Avacado, Lemon, Onion</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -15628,10 +15628,10 @@
         <v>2026-05-23</v>
       </c>
       <c r="B75" t="str">
-        <v>Fruits</v>
+        <v>Eating Out</v>
       </c>
       <c r="C75" t="str">
-        <v>Avacado, Guava</v>
+        <v>Praveen Cake</v>
       </c>
       <c r="D75">
         <v>5</v>
@@ -15642,55 +15642,55 @@
         <v>2026-05-23</v>
       </c>
       <c r="B76" t="str">
-        <v>Groceries</v>
+        <v>Fruits</v>
       </c>
       <c r="C76" t="str">
-        <v>Corn, Yogurt, Cucumber, Cake</v>
+        <v>Avacado, Guava</v>
       </c>
       <c r="D76">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="B77" t="str">
         <v>Groceries</v>
       </c>
       <c r="C77" t="str">
-        <v>Banana</v>
+        <v>Corn, Yogurt, Cucumber, Cake</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="B78" t="str">
         <v>Groceries</v>
       </c>
       <c r="C78" t="str">
-        <v>Potatoes And Dish Was Liquid</v>
+        <v>Banana</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="B79" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C79" t="str">
-        <v>Lamb</v>
+        <v>Potatoes And Dish Was Liquid</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -15698,27 +15698,27 @@
         <v>2026-05-17</v>
       </c>
       <c r="B80" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C80" t="str">
-        <v>Sainsbury's - Carrots, Onion</v>
+        <v>Lamb</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="B81" t="str">
         <v>Groceries</v>
       </c>
       <c r="C81" t="str">
-        <v>Shakti</v>
+        <v>Sainsbury's - Carrots, Onion</v>
       </c>
       <c r="D81">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -15726,55 +15726,55 @@
         <v>2026-05-16</v>
       </c>
       <c r="B82" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C82" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="B83" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C83" t="str">
-        <v>Yogurt, Vegetables</v>
+        <v>Chicken</v>
       </c>
       <c r="D83">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B84" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C84" t="str">
-        <v>Munich - Gifts To Office</v>
+        <v>Yogurt, Vegetables</v>
       </c>
       <c r="D84">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="B85" t="str">
         <v>Travel</v>
       </c>
       <c r="C85" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Gifts To Office</v>
       </c>
       <c r="D85">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
@@ -15785,10 +15785,10 @@
         <v>Travel</v>
       </c>
       <c r="C86" t="str">
-        <v>Munich - Water And Juice</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D86">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87">
@@ -15799,10 +15799,10 @@
         <v>Travel</v>
       </c>
       <c r="C87" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Water And Juice</v>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -15813,24 +15813,24 @@
         <v>Travel</v>
       </c>
       <c r="C88" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D88">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="B89" t="str">
         <v>Travel</v>
       </c>
       <c r="C89" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D89">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90">
@@ -15841,10 +15841,10 @@
         <v>Travel</v>
       </c>
       <c r="C90" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D90">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91">
@@ -15855,10 +15855,10 @@
         <v>Travel</v>
       </c>
       <c r="C91" t="str">
-        <v>Munich - Bmw Museum Ticket</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D91">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -15869,10 +15869,10 @@
         <v>Travel</v>
       </c>
       <c r="C92" t="str">
-        <v>Munich Lunch</v>
+        <v>Munich - Bmw Museum Ticket</v>
       </c>
       <c r="D92">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
@@ -15883,10 +15883,10 @@
         <v>Travel</v>
       </c>
       <c r="C93" t="str">
-        <v>Munich Walking Tour</v>
+        <v>Munich Lunch</v>
       </c>
       <c r="D93">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94">
@@ -15897,24 +15897,24 @@
         <v>Travel</v>
       </c>
       <c r="C94" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich Walking Tour</v>
       </c>
       <c r="D94">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B95" t="str">
         <v>Travel</v>
       </c>
       <c r="C95" t="str">
-        <v>Dinner - Mac And Cheese</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D95">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
@@ -15925,10 +15925,10 @@
         <v>Travel</v>
       </c>
       <c r="C96" t="str">
-        <v>Pretzel Snack</v>
+        <v>Dinner - Mac And Cheese</v>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97">
@@ -15939,10 +15939,10 @@
         <v>Travel</v>
       </c>
       <c r="C97" t="str">
-        <v>Lidl - Water, Coke, Yogurt</v>
+        <v>Pretzel Snack</v>
       </c>
       <c r="D97">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -15953,10 +15953,10 @@
         <v>Travel</v>
       </c>
       <c r="C98" t="str">
-        <v>Germany Public Transport Ticket</v>
+        <v>Lidl - Water, Coke, Yogurt</v>
       </c>
       <c r="D98">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -15964,27 +15964,27 @@
         <v>2026-05-09</v>
       </c>
       <c r="B99" t="str">
-        <v>Eating Out</v>
+        <v>Travel</v>
       </c>
       <c r="C99" t="str">
-        <v>Airport Pret</v>
+        <v>Germany Public Transport Ticket</v>
       </c>
       <c r="D99">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B100" t="str">
-        <v>Boots</v>
+        <v>Eating Out</v>
       </c>
       <c r="C100" t="str">
-        <v>Face Moisturizer</v>
+        <v>Airport Pret</v>
       </c>
       <c r="D100">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
@@ -15992,13 +15992,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B101" t="str">
-        <v>Provisions</v>
+        <v>Boots</v>
       </c>
       <c r="C101" t="str">
-        <v>Eggs</v>
+        <v>Face Moisturizer</v>
       </c>
       <c r="D101">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102">
@@ -16006,13 +16006,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B102" t="str">
-        <v>Shopping</v>
+        <v>Provisions</v>
       </c>
       <c r="C102" t="str">
-        <v>Belt</v>
+        <v>Eggs</v>
       </c>
       <c r="D102">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -16020,10 +16020,10 @@
         <v>2026-05-08</v>
       </c>
       <c r="B103" t="str">
-        <v>Eating Out</v>
+        <v>Shopping</v>
       </c>
       <c r="C103" t="str">
-        <v>Praveen</v>
+        <v>Belt</v>
       </c>
       <c r="D103">
         <v>7</v>
@@ -16031,30 +16031,30 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B104" t="str">
-        <v>Travel</v>
+        <v>Eating Out</v>
       </c>
       <c r="C104" t="str">
-        <v>Oyster Card</v>
+        <v>Praveen</v>
       </c>
       <c r="D104">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2026-04-18</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B105" t="str">
-        <v>Souvenir</v>
+        <v>Travel</v>
       </c>
       <c r="C105" t="str">
-        <v>Gift, Biscuits</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D105">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
@@ -16062,55 +16062,55 @@
         <v>2026-04-18</v>
       </c>
       <c r="B106" t="str">
-        <v>Groceries</v>
+        <v>Souvenir</v>
       </c>
       <c r="C106" t="str">
-        <v>Corn And Gauva</v>
+        <v>Gift, Biscuits</v>
       </c>
       <c r="D106">
-        <v>3.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-18</v>
       </c>
       <c r="B107" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C107" t="str">
-        <v>Oyster Card</v>
+        <v>Corn And Gauva</v>
       </c>
       <c r="D107">
-        <v>30</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2026-03-31</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B108" t="str">
         <v>Travel</v>
       </c>
       <c r="C108" t="str">
-        <v>Total Tfl Cost</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D108">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2026-04-11</v>
+        <v>2026-03-31</v>
       </c>
       <c r="B109" t="str">
-        <v>Praveen Shoes</v>
+        <v>Travel</v>
       </c>
       <c r="C109" t="str">
-        <v>Shoes</v>
+        <v>Total Tfl Cost</v>
       </c>
       <c r="D109">
-        <v>110</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110">
@@ -16118,27 +16118,27 @@
         <v>2026-04-11</v>
       </c>
       <c r="B110" t="str">
-        <v>Eating Out</v>
+        <v>Praveen Shoes</v>
       </c>
       <c r="C110" t="str">
-        <v>Spitalfield Market</v>
+        <v>Shoes</v>
       </c>
       <c r="D110">
-        <v>8</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="B111" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C111" t="str">
-        <v>Too Good To Go</v>
+        <v>Spitalfield Market</v>
       </c>
       <c r="D111">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112">
@@ -16146,10 +16146,10 @@
         <v>2026-04-09</v>
       </c>
       <c r="B112" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C112" t="str">
-        <v>Yogurt</v>
+        <v>Too Good To Go</v>
       </c>
       <c r="D112">
         <v>4</v>
@@ -16157,72 +16157,72 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-09</v>
       </c>
       <c r="B113" t="str">
-        <v>Visa Fee</v>
+        <v>Groceries</v>
       </c>
       <c r="C113" t="str">
-        <v>Visa Gee</v>
+        <v>Yogurt</v>
       </c>
       <c r="D113">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B114" t="str">
-        <v>Travel</v>
+        <v>Visa Fee</v>
       </c>
       <c r="C114" t="str">
-        <v>Oyster Card</v>
+        <v>Visa Gee</v>
       </c>
       <c r="D114">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B115" t="str">
-        <v>Visa Picture</v>
+        <v>Travel</v>
       </c>
       <c r="C115" t="str">
-        <v>Snappy Snap</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D115">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B116" t="str">
-        <v>Provisions</v>
+        <v>Visa Picture</v>
       </c>
       <c r="C116" t="str">
-        <v>Water Bottle</v>
+        <v>Snappy Snap</v>
       </c>
       <c r="D116">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B117" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C117" t="str">
-        <v>Poornima Roti Curry(malaysia Food)</v>
+        <v>Water Bottle</v>
       </c>
       <c r="D117">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -16230,41 +16230,41 @@
         <v>2026-04-06</v>
       </c>
       <c r="B118" t="str">
-        <v>Germany Visa Stuff</v>
+        <v>Eating Out</v>
       </c>
       <c r="C118" t="str">
-        <v>Travel Insurance, Airbnb</v>
+        <v>Poornima Roti Curry(malaysia Food)</v>
       </c>
       <c r="D118">
-        <v>111</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B119" t="str">
-        <v>Provisions</v>
+        <v>Germany Visa Stuff</v>
       </c>
       <c r="C119" t="str">
-        <v>Yogurt, Lemon</v>
+        <v>Travel Insurance, Airbnb</v>
       </c>
       <c r="D119">
-        <v>3</v>
+        <v>111</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="B120" t="str">
         <v>Provisions</v>
       </c>
       <c r="C120" t="str">
-        <v>Rice Flour, Oil,</v>
+        <v>Yogurt, Lemon</v>
       </c>
       <c r="D120">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -16272,13 +16272,13 @@
         <v>2026-04-04</v>
       </c>
       <c r="B121" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C121" t="str">
-        <v>Spinach, Ginger, Vegetable</v>
+        <v>Rice Flour, Oil,</v>
       </c>
       <c r="D121">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122">
@@ -16286,27 +16286,27 @@
         <v>2026-04-04</v>
       </c>
       <c r="B122" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C122" t="str">
-        <v>Lamb And Chicken</v>
+        <v>Spinach, Ginger, Vegetable</v>
       </c>
       <c r="D122">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-04</v>
       </c>
       <c r="B123" t="str">
-        <v>Cricket Tickets</v>
+        <v>Meats</v>
       </c>
       <c r="C123" t="str">
-        <v>Lords Women World Cup</v>
+        <v>Lamb And Chicken</v>
       </c>
       <c r="D123">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124">
@@ -16314,27 +16314,27 @@
         <v>2026-04-02</v>
       </c>
       <c r="B124" t="str">
-        <v>Provisions</v>
+        <v>Cricket Tickets</v>
       </c>
       <c r="C124" t="str">
-        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
+        <v>Lords Women World Cup</v>
       </c>
       <c r="D124">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-02</v>
       </c>
       <c r="B125" t="str">
         <v>Provisions</v>
       </c>
       <c r="C125" t="str">
-        <v>Sainsbury's</v>
+        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
       </c>
       <c r="D125">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126">
@@ -16342,27 +16342,27 @@
         <v>2026-03-28</v>
       </c>
       <c r="B126" t="str">
-        <v>Fruits</v>
+        <v>Provisions</v>
       </c>
       <c r="C126" t="str">
-        <v>Blueberries, Avocado, Gauva</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D126">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-28</v>
       </c>
       <c r="B127" t="str">
-        <v>Movie</v>
+        <v>Fruits</v>
       </c>
       <c r="C127" t="str">
-        <v>Dhurandar</v>
+        <v>Blueberries, Avocado, Gauva</v>
       </c>
       <c r="D127">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
@@ -16370,69 +16370,69 @@
         <v>2026-03-25</v>
       </c>
       <c r="B128" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C128" t="str">
-        <v>Yogurt</v>
+        <v>Dhurandar</v>
       </c>
       <c r="D128">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-25</v>
       </c>
       <c r="B129" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C129" t="str">
-        <v>Pizza Pilgrims</v>
+        <v>Yogurt</v>
       </c>
       <c r="D129">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="B130" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C130" t="str">
-        <v>Milk, Yogurt, Flowers, Butter</v>
+        <v>Pizza Pilgrims</v>
       </c>
       <c r="D130">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="B131" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C131" t="str">
-        <v>Praveen</v>
+        <v>Milk, Yogurt, Flowers, Butter</v>
       </c>
       <c r="D131">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-17</v>
       </c>
       <c r="B132" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C132" t="str">
-        <v>Provisions</v>
+        <v>Praveen</v>
       </c>
       <c r="D132">
-        <v>59</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
@@ -16440,27 +16440,27 @@
         <v>2026-03-15</v>
       </c>
       <c r="B133" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C133" t="str">
-        <v>Vegetables</v>
+        <v>Provisions</v>
       </c>
       <c r="D133">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-15</v>
       </c>
       <c r="B134" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C134" t="str">
-        <v>Gauva, Blueberries</v>
+        <v>Vegetables</v>
       </c>
       <c r="D134">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="135">
@@ -16468,13 +16468,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B135" t="str">
-        <v>Eating Out</v>
+        <v>Fruits</v>
       </c>
       <c r="C135" t="str">
-        <v>Haleem And Samosa</v>
+        <v>Gauva, Blueberries</v>
       </c>
       <c r="D135">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
@@ -16482,13 +16482,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B136" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C136" t="str">
-        <v>Frozen Lotus Stem And Beans</v>
+        <v>Haleem And Samosa</v>
       </c>
       <c r="D136">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137">
@@ -16496,13 +16496,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B137" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C137" t="str">
-        <v>Vegetables</v>
+        <v>Frozen Lotus Stem And Beans</v>
       </c>
       <c r="D137">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
@@ -16510,27 +16510,27 @@
         <v>2026-03-14</v>
       </c>
       <c r="B138" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C138" t="str">
-        <v>Lidl</v>
+        <v>Vegetables</v>
       </c>
       <c r="D138">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-14</v>
       </c>
       <c r="B139" t="str">
-        <v>Medication</v>
+        <v>Provisions</v>
       </c>
       <c r="C139" t="str">
-        <v>Fish Oil, Pregnacare</v>
+        <v>Lidl</v>
       </c>
       <c r="D139">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140">
@@ -16538,69 +16538,69 @@
         <v>2026-03-09</v>
       </c>
       <c r="B140" t="str">
-        <v>Provisions</v>
+        <v>Medication</v>
       </c>
       <c r="C140" t="str">
-        <v>Yogurt, Oats, Sourdough, Detergent</v>
+        <v>Fish Oil, Pregnacare</v>
       </c>
       <c r="D140">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="B141" t="str">
-        <v>Washing</v>
+        <v>Provisions</v>
       </c>
       <c r="C141" t="str">
-        <v>Clothes</v>
+        <v>Yogurt, Oats, Sourdough, Detergent</v>
       </c>
       <c r="D141">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-08</v>
       </c>
       <c r="B142" t="str">
-        <v>Praveen</v>
+        <v>Washing</v>
       </c>
       <c r="C142" t="str">
-        <v>Praveen eating out</v>
+        <v>Clothes</v>
       </c>
       <c r="D142">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="B143" t="str">
-        <v>Meats</v>
+        <v>Praveen</v>
       </c>
       <c r="C143" t="str">
-        <v>Chicken and Fish</v>
+        <v>Praveen eating out</v>
       </c>
       <c r="D143">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-01</v>
       </c>
       <c r="B144" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C144" t="str">
-        <v>Vegetables</v>
+        <v>Chicken and Fish</v>
       </c>
       <c r="D144">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="145">
@@ -16608,32 +16608,46 @@
         <v>2026-03-07</v>
       </c>
       <c r="B145" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C145" t="str">
-        <v>Mobos Ethiopian Restaurant</v>
+        <v>Vegetables</v>
       </c>
       <c r="D145">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Eating Out</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Mobos Ethiopian Restaurant</v>
+      </c>
+      <c r="D146">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
         <v>2026-03-06</v>
       </c>
-      <c r="B146" t="str">
+      <c r="B147" t="str">
         <v>Provisions</v>
       </c>
-      <c r="C146" t="str">
+      <c r="C147" t="str">
         <v>Milk and Doritos</v>
       </c>
-      <c r="D146">
+      <c r="D147">
         <v>2.95</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D146"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D147"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -14579,7 +14579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D148"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -14606,41 +14606,41 @@
         <v>2026-08-25</v>
       </c>
       <c r="B2" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C2" t="str">
-        <v>Sainsbury's , Tesco</v>
+        <v>Deliveroo</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-25</v>
       </c>
       <c r="B3" t="str">
-        <v>Bike Tyre</v>
+        <v>Groceries</v>
       </c>
       <c r="C3" t="str">
-        <v>Bike Tube And Tyre</v>
+        <v>Sainsbury's , Tesco</v>
       </c>
       <c r="D3">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
       <c r="B4" t="str">
-        <v>Badminton</v>
+        <v>Bike Tyre</v>
       </c>
       <c r="C4" t="str">
-        <v>Badminton</v>
+        <v>Bike Tube And Tyre</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -14648,13 +14648,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B5" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C5" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -14662,13 +14662,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B6" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C6" t="str">
-        <v>Lidl - Prawns , Kefir And Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -14679,38 +14679,38 @@
         <v>Groceries</v>
       </c>
       <c r="C7" t="str">
-        <v>Fruits For Lakshmi Pooja</v>
+        <v>Lidl - Prawns , Kefir And Yogurt</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-21</v>
       </c>
       <c r="B8" t="str">
-        <v>Movie</v>
+        <v>Groceries</v>
       </c>
       <c r="C8" t="str">
-        <v>Toxic</v>
+        <v>Fruits For Lakshmi Pooja</v>
       </c>
       <c r="D8">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-08-15</v>
+        <v>2026-08-18</v>
       </c>
       <c r="B9" t="str">
-        <v>Groceries</v>
+        <v>Movie</v>
       </c>
       <c r="C9" t="str">
-        <v>Sainsbury's And Lidl</v>
+        <v>Toxic</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -14718,13 +14718,13 @@
         <v>2026-08-15</v>
       </c>
       <c r="B10" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C10" t="str">
-        <v>Fruit</v>
+        <v>Sainsbury's And Lidl</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -14732,27 +14732,27 @@
         <v>2026-08-15</v>
       </c>
       <c r="B11" t="str">
-        <v>Meats</v>
+        <v>Fruits</v>
       </c>
       <c r="C11" t="str">
-        <v>Lamb, Samosa, Chicken Keema</v>
+        <v>Fruit</v>
       </c>
       <c r="D11">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-15</v>
       </c>
       <c r="B12" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C12" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Lamb, Samosa, Chicken Keema</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -14760,125 +14760,125 @@
         <v>2026-08-14</v>
       </c>
       <c r="B13" t="str">
-        <v>Badminton</v>
+        <v>Groceries</v>
       </c>
       <c r="C13" t="str">
-        <v>Badminton</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D13">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-14</v>
       </c>
       <c r="B14" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C14" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-10</v>
       </c>
       <c r="B15" t="str">
-        <v>Badminton</v>
+        <v>Travel</v>
       </c>
       <c r="C15" t="str">
-        <v>Badminton</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D15">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B16" t="str">
-        <v>Groceries</v>
+        <v>Badminton</v>
       </c>
       <c r="C16" t="str">
-        <v>Yogurt And Cheese</v>
+        <v>Badminton</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-08-04</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B17" t="str">
         <v>Groceries</v>
       </c>
       <c r="C17" t="str">
-        <v>Cucumber, Tissues, Corn Flour</v>
+        <v>Yogurt And Cheese</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-04</v>
       </c>
       <c r="B18" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C18" t="str">
-        <v>Oyster Card</v>
+        <v>Cucumber, Tissues, Corn Flour</v>
       </c>
       <c r="D18">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-28</v>
       </c>
       <c r="B19" t="str">
-        <v>Provisions</v>
+        <v>Travel</v>
       </c>
       <c r="C19" t="str">
-        <v>Egg, Office Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-27</v>
       </c>
       <c r="B20" t="str">
         <v>Provisions</v>
       </c>
       <c r="C20" t="str">
-        <v>Lidl- Yogurt</v>
+        <v>Egg, Office Yogurt</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-30</v>
       </c>
       <c r="B21" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C21" t="str">
-        <v>Praveen - Boba Tea</v>
+        <v>Lidl- Yogurt</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -14886,27 +14886,27 @@
         <v>2026-07-25</v>
       </c>
       <c r="B22" t="str">
-        <v>Abdul Son Marriage Gift</v>
+        <v>Eating Out</v>
       </c>
       <c r="C22" t="str">
-        <v>Gift</v>
+        <v>Praveen - Boba Tea</v>
       </c>
       <c r="D22">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-07-26</v>
+        <v>2026-07-25</v>
       </c>
       <c r="B23" t="str">
-        <v>Badminton</v>
+        <v>Abdul Son Marriage Gift</v>
       </c>
       <c r="C23" t="str">
-        <v>Badminton</v>
+        <v>Gift</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -14914,27 +14914,27 @@
         <v>2026-07-26</v>
       </c>
       <c r="B24" t="str">
-        <v>House</v>
+        <v>Badminton</v>
       </c>
       <c r="C24" t="str">
-        <v>Houzecheck - House Evaluation</v>
+        <v>Badminton</v>
       </c>
       <c r="D24">
-        <v>593</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-26</v>
       </c>
       <c r="B25" t="str">
-        <v>Travel</v>
+        <v>House</v>
       </c>
       <c r="C25" t="str">
-        <v>Norway - H&amp;m - Pau Baby Dress</v>
+        <v>Houzecheck - House Evaluation</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>593</v>
       </c>
     </row>
     <row r="26">
@@ -14945,7 +14945,7 @@
         <v>Travel</v>
       </c>
       <c r="C26" t="str">
-        <v>Norway - Bus Pass</v>
+        <v>Norway - H&amp;m - Pau Baby Dress</v>
       </c>
       <c r="D26">
         <v>12</v>
@@ -14953,58 +14953,58 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B27" t="str">
         <v>Travel</v>
       </c>
       <c r="C27" t="str">
-        <v>Norway - Radical Storage Oslo</v>
+        <v>Norway - Bus Pass</v>
       </c>
       <c r="D27">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B28" t="str">
         <v>Travel</v>
       </c>
       <c r="C28" t="str">
-        <v>Oyster Card</v>
+        <v>Norway - Radical Storage Oslo</v>
       </c>
       <c r="D28">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B29" t="str">
-        <v>Norway</v>
+        <v>Travel</v>
       </c>
       <c r="C29" t="str">
-        <v>Travel Insurance</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D29">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B30" t="str">
         <v>Norway</v>
       </c>
       <c r="C30" t="str">
-        <v>Chocolate</v>
+        <v>Travel Insurance</v>
       </c>
       <c r="D30">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -15012,27 +15012,27 @@
         <v>2026-07-13</v>
       </c>
       <c r="B31" t="str">
-        <v>House</v>
+        <v>Norway</v>
       </c>
       <c r="C31" t="str">
-        <v>Leadenhall</v>
+        <v>Chocolate</v>
       </c>
       <c r="D31">
-        <v>820</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B32" t="str">
-        <v>Provisions</v>
+        <v>House</v>
       </c>
       <c r="C32" t="str">
-        <v>Yogurt</v>
+        <v>Leadenhall</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>820</v>
       </c>
     </row>
     <row r="33">
@@ -15040,13 +15040,13 @@
         <v>2026-07-11</v>
       </c>
       <c r="B33" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C33" t="str">
-        <v>Amarino Ice Cream</v>
+        <v>Yogurt</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -15054,55 +15054,55 @@
         <v>2026-07-11</v>
       </c>
       <c r="B34" t="str">
-        <v>Gifts To Norway</v>
+        <v>Eating Out</v>
       </c>
       <c r="C34" t="str">
-        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
+        <v>Amarino Ice Cream</v>
       </c>
       <c r="D34">
-        <v>97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B35" t="str">
-        <v>Praveen</v>
+        <v>Gifts To Norway</v>
       </c>
       <c r="C35" t="str">
-        <v>Badminton</v>
+        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B36" t="str">
-        <v>Travel</v>
+        <v>Praveen</v>
       </c>
       <c r="C36" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D36">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B37" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C37" t="str">
-        <v>Shakti</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D37">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
@@ -15110,13 +15110,13 @@
         <v>2026-07-05</v>
       </c>
       <c r="B38" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C38" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D38">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -15124,41 +15124,41 @@
         <v>2026-07-05</v>
       </c>
       <c r="B39" t="str">
-        <v>Haircut</v>
+        <v>Meats</v>
       </c>
       <c r="C39" t="str">
-        <v>Haircut</v>
+        <v>Chicken</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B40" t="str">
-        <v>Provisions</v>
+        <v>Haircut</v>
       </c>
       <c r="C40" t="str">
-        <v>Lidl, Sainsbury's, Iceland</v>
+        <v>Haircut</v>
       </c>
       <c r="D40">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B41" t="str">
-        <v>Superdrug</v>
+        <v>Provisions</v>
       </c>
       <c r="C41" t="str">
-        <v>Shoes Deodorant</v>
+        <v>Lidl, Sainsbury's, Iceland</v>
       </c>
       <c r="D41">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42">
@@ -15166,83 +15166,83 @@
         <v>2026-07-04</v>
       </c>
       <c r="B42" t="str">
-        <v>Medicine</v>
+        <v>Superdrug</v>
       </c>
       <c r="C42" t="str">
-        <v>H&amp;b</v>
+        <v>Shoes Deodorant</v>
       </c>
       <c r="D42">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B43" t="str">
-        <v>Praveen - Badminton</v>
+        <v>Medicine</v>
       </c>
       <c r="C43" t="str">
-        <v>Badminton</v>
+        <v>H&amp;b</v>
       </c>
       <c r="D43">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-06-30</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B44" t="str">
-        <v>Provisions</v>
+        <v>Praveen - Badminton</v>
       </c>
       <c r="C44" t="str">
-        <v>Lidl - Detergent</v>
+        <v>Badminton</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-06-29</v>
+        <v>2026-06-30</v>
       </c>
       <c r="B45" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C45" t="str">
-        <v>Praveen &amp; Poornima - Cake</v>
+        <v>Lidl - Detergent</v>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-06-28</v>
+        <v>2026-06-29</v>
       </c>
       <c r="B46" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C46" t="str">
-        <v>Poornima And Praveen (tajrish Restaurant)</v>
+        <v>Praveen &amp; Poornima - Cake</v>
       </c>
       <c r="D46">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="B47" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C47" t="str">
-        <v>Lidl</v>
+        <v>Poornima And Praveen (tajrish Restaurant)</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48">
@@ -15253,10 +15253,10 @@
         <v>Groceries</v>
       </c>
       <c r="C48" t="str">
-        <v>Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -15264,13 +15264,13 @@
         <v>2026-06-27</v>
       </c>
       <c r="B49" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C49" t="str">
-        <v>Grapes, Guava, Pomegranate, Avacado</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D49">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -15278,41 +15278,41 @@
         <v>2026-06-27</v>
       </c>
       <c r="B50" t="str">
-        <v>Provisions</v>
+        <v>Fruits</v>
       </c>
       <c r="C50" t="str">
-        <v>M&amp;s</v>
+        <v>Grapes, Guava, Pomegranate, Avacado</v>
       </c>
       <c r="D50">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-27</v>
       </c>
       <c r="B51" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C51" t="str">
-        <v>Oyster</v>
+        <v>M&amp;s</v>
       </c>
       <c r="D51">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-26</v>
       </c>
       <c r="B52" t="str">
-        <v>Fan</v>
+        <v>Travel</v>
       </c>
       <c r="C52" t="str">
-        <v>Fan</v>
+        <v>Oyster</v>
       </c>
       <c r="D52">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
@@ -15320,13 +15320,13 @@
         <v>2026-06-24</v>
       </c>
       <c r="B53" t="str">
-        <v>Groceries</v>
+        <v>Fan</v>
       </c>
       <c r="C53" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Fan</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54">
@@ -15334,27 +15334,27 @@
         <v>2026-06-24</v>
       </c>
       <c r="B54" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C54" t="str">
-        <v>Yogurt, Dates, Prunes</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D54">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-06-21</v>
+        <v>2026-06-24</v>
       </c>
       <c r="B55" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C55" t="str">
-        <v>Chicken</v>
+        <v>Yogurt, Dates, Prunes</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
@@ -15365,38 +15365,38 @@
         <v>Meats</v>
       </c>
       <c r="C56" t="str">
-        <v>Fish - Salmon And Travelly</v>
+        <v>Chicken</v>
       </c>
       <c r="D56">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-06-14</v>
+        <v>2026-06-21</v>
       </c>
       <c r="B57" t="str">
-        <v>Travel</v>
+        <v>Meats</v>
       </c>
       <c r="C57" t="str">
-        <v>Flight Trd - Lhr</v>
+        <v>Fish - Salmon And Travelly</v>
       </c>
       <c r="D57">
-        <v>91</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-06-13</v>
+        <v>2026-06-14</v>
       </c>
       <c r="B58" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C58" t="str">
-        <v>Lidl &amp; Sainsbury's</v>
+        <v>Flight Trd - Lhr</v>
       </c>
       <c r="D58">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59">
@@ -15404,27 +15404,27 @@
         <v>2026-06-13</v>
       </c>
       <c r="B59" t="str">
-        <v>Belgravia</v>
+        <v>Groceries</v>
       </c>
       <c r="C59" t="str">
-        <v>Belgravia</v>
+        <v>Lidl &amp; Sainsbury's</v>
       </c>
       <c r="D59">
-        <v>186</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-06-18</v>
+        <v>2026-06-13</v>
       </c>
       <c r="B60" t="str">
-        <v>Provisions</v>
+        <v>Belgravia</v>
       </c>
       <c r="C60" t="str">
-        <v>Egg</v>
+        <v>Belgravia</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>186</v>
       </c>
     </row>
     <row r="61">
@@ -15432,69 +15432,69 @@
         <v>2026-06-18</v>
       </c>
       <c r="B61" t="str">
-        <v>Cycle</v>
+        <v>Provisions</v>
       </c>
       <c r="C61" t="str">
-        <v>Cycle</v>
+        <v>Egg</v>
       </c>
       <c r="D61">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-18</v>
       </c>
       <c r="B62" t="str">
-        <v>Travel</v>
+        <v>Cycle</v>
       </c>
       <c r="C62" t="str">
-        <v>Lgw - Oslo</v>
+        <v>Cycle</v>
       </c>
       <c r="D62">
-        <v>168</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="B63" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C63" t="str">
-        <v>Lidl</v>
+        <v>Lgw - Oslo</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-10</v>
       </c>
       <c r="B64" t="str">
         <v>Groceries</v>
       </c>
       <c r="C64" t="str">
-        <v>Lidl And Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D64">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B65" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C65" t="str">
-        <v>Vegetables, Fruits</v>
+        <v>Lidl And Sainsbury's</v>
       </c>
       <c r="D65">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
@@ -15502,83 +15502,83 @@
         <v>2026-06-06</v>
       </c>
       <c r="B66" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C66" t="str">
-        <v>Lamb</v>
+        <v>Vegetables, Fruits</v>
       </c>
       <c r="D66">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-06-12</v>
+        <v>2026-06-06</v>
       </c>
       <c r="B67" t="str">
-        <v>Movie</v>
+        <v>Meats</v>
       </c>
       <c r="C67" t="str">
-        <v>Peddi</v>
+        <v>Lamb</v>
       </c>
       <c r="D67">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-05-31</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B68" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C68" t="str">
-        <v>Yogurt, Corn, Kefir</v>
+        <v>Peddi</v>
       </c>
       <c r="D68">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-31</v>
       </c>
       <c r="B69" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C69" t="str">
-        <v>Oyster Card</v>
+        <v>Yogurt, Corn, Kefir</v>
       </c>
       <c r="D69">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-29</v>
       </c>
       <c r="B70" t="str">
-        <v>Amazon</v>
+        <v>Travel</v>
       </c>
       <c r="C70" t="str">
-        <v>Face Wash, Moisturizer</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D70">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-28</v>
       </c>
       <c r="B71" t="str">
-        <v>Eating Out</v>
+        <v>Amazon</v>
       </c>
       <c r="C71" t="str">
-        <v>Praveen</v>
+        <v>Face Wash, Moisturizer</v>
       </c>
       <c r="D71">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72">
@@ -15586,13 +15586,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B72" t="str">
-        <v>Meats</v>
+        <v>Eating Out</v>
       </c>
       <c r="C72" t="str">
-        <v>Chicken</v>
+        <v>Praveen</v>
       </c>
       <c r="D72">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73">
@@ -15600,13 +15600,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B73" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C73" t="str">
-        <v>Shakto</v>
+        <v>Chicken</v>
       </c>
       <c r="D73">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -15617,24 +15617,24 @@
         <v>Groceries</v>
       </c>
       <c r="C74" t="str">
-        <v>Bread, Avacado, Lemon, Onion</v>
+        <v>Shakto</v>
       </c>
       <c r="D74">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="B75" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C75" t="str">
-        <v>Praveen Cake</v>
+        <v>Bread, Avacado, Lemon, Onion</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -15642,10 +15642,10 @@
         <v>2026-05-23</v>
       </c>
       <c r="B76" t="str">
-        <v>Fruits</v>
+        <v>Eating Out</v>
       </c>
       <c r="C76" t="str">
-        <v>Avacado, Guava</v>
+        <v>Praveen Cake</v>
       </c>
       <c r="D76">
         <v>5</v>
@@ -15656,55 +15656,55 @@
         <v>2026-05-23</v>
       </c>
       <c r="B77" t="str">
-        <v>Groceries</v>
+        <v>Fruits</v>
       </c>
       <c r="C77" t="str">
-        <v>Corn, Yogurt, Cucumber, Cake</v>
+        <v>Avacado, Guava</v>
       </c>
       <c r="D77">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="B78" t="str">
         <v>Groceries</v>
       </c>
       <c r="C78" t="str">
-        <v>Banana</v>
+        <v>Corn, Yogurt, Cucumber, Cake</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="B79" t="str">
         <v>Groceries</v>
       </c>
       <c r="C79" t="str">
-        <v>Potatoes And Dish Was Liquid</v>
+        <v>Banana</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="B80" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C80" t="str">
-        <v>Lamb</v>
+        <v>Potatoes And Dish Was Liquid</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -15712,27 +15712,27 @@
         <v>2026-05-17</v>
       </c>
       <c r="B81" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C81" t="str">
-        <v>Sainsbury's - Carrots, Onion</v>
+        <v>Lamb</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="B82" t="str">
         <v>Groceries</v>
       </c>
       <c r="C82" t="str">
-        <v>Shakti</v>
+        <v>Sainsbury's - Carrots, Onion</v>
       </c>
       <c r="D82">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -15740,55 +15740,55 @@
         <v>2026-05-16</v>
       </c>
       <c r="B83" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C83" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D83">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="B84" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C84" t="str">
-        <v>Yogurt, Vegetables</v>
+        <v>Chicken</v>
       </c>
       <c r="D84">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B85" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C85" t="str">
-        <v>Munich - Gifts To Office</v>
+        <v>Yogurt, Vegetables</v>
       </c>
       <c r="D85">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="B86" t="str">
         <v>Travel</v>
       </c>
       <c r="C86" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Gifts To Office</v>
       </c>
       <c r="D86">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">
@@ -15799,10 +15799,10 @@
         <v>Travel</v>
       </c>
       <c r="C87" t="str">
-        <v>Munich - Water And Juice</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D87">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88">
@@ -15813,10 +15813,10 @@
         <v>Travel</v>
       </c>
       <c r="C88" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Water And Juice</v>
       </c>
       <c r="D88">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -15827,24 +15827,24 @@
         <v>Travel</v>
       </c>
       <c r="C89" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D89">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="B90" t="str">
         <v>Travel</v>
       </c>
       <c r="C90" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D90">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91">
@@ -15855,10 +15855,10 @@
         <v>Travel</v>
       </c>
       <c r="C91" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D91">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
@@ -15869,10 +15869,10 @@
         <v>Travel</v>
       </c>
       <c r="C92" t="str">
-        <v>Munich - Bmw Museum Ticket</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D92">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -15883,10 +15883,10 @@
         <v>Travel</v>
       </c>
       <c r="C93" t="str">
-        <v>Munich Lunch</v>
+        <v>Munich - Bmw Museum Ticket</v>
       </c>
       <c r="D93">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94">
@@ -15897,10 +15897,10 @@
         <v>Travel</v>
       </c>
       <c r="C94" t="str">
-        <v>Munich Walking Tour</v>
+        <v>Munich Lunch</v>
       </c>
       <c r="D94">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95">
@@ -15911,24 +15911,24 @@
         <v>Travel</v>
       </c>
       <c r="C95" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich Walking Tour</v>
       </c>
       <c r="D95">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B96" t="str">
         <v>Travel</v>
       </c>
       <c r="C96" t="str">
-        <v>Dinner - Mac And Cheese</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D96">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97">
@@ -15939,10 +15939,10 @@
         <v>Travel</v>
       </c>
       <c r="C97" t="str">
-        <v>Pretzel Snack</v>
+        <v>Dinner - Mac And Cheese</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98">
@@ -15953,10 +15953,10 @@
         <v>Travel</v>
       </c>
       <c r="C98" t="str">
-        <v>Lidl - Water, Coke, Yogurt</v>
+        <v>Pretzel Snack</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -15967,10 +15967,10 @@
         <v>Travel</v>
       </c>
       <c r="C99" t="str">
-        <v>Germany Public Transport Ticket</v>
+        <v>Lidl - Water, Coke, Yogurt</v>
       </c>
       <c r="D99">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -15978,27 +15978,27 @@
         <v>2026-05-09</v>
       </c>
       <c r="B100" t="str">
-        <v>Eating Out</v>
+        <v>Travel</v>
       </c>
       <c r="C100" t="str">
-        <v>Airport Pret</v>
+        <v>Germany Public Transport Ticket</v>
       </c>
       <c r="D100">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B101" t="str">
-        <v>Boots</v>
+        <v>Eating Out</v>
       </c>
       <c r="C101" t="str">
-        <v>Face Moisturizer</v>
+        <v>Airport Pret</v>
       </c>
       <c r="D101">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102">
@@ -16006,13 +16006,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B102" t="str">
-        <v>Provisions</v>
+        <v>Boots</v>
       </c>
       <c r="C102" t="str">
-        <v>Eggs</v>
+        <v>Face Moisturizer</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103">
@@ -16020,13 +16020,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B103" t="str">
-        <v>Shopping</v>
+        <v>Provisions</v>
       </c>
       <c r="C103" t="str">
-        <v>Belt</v>
+        <v>Eggs</v>
       </c>
       <c r="D103">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -16034,10 +16034,10 @@
         <v>2026-05-08</v>
       </c>
       <c r="B104" t="str">
-        <v>Eating Out</v>
+        <v>Shopping</v>
       </c>
       <c r="C104" t="str">
-        <v>Praveen</v>
+        <v>Belt</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -16045,30 +16045,30 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B105" t="str">
-        <v>Travel</v>
+        <v>Eating Out</v>
       </c>
       <c r="C105" t="str">
-        <v>Oyster Card</v>
+        <v>Praveen</v>
       </c>
       <c r="D105">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2026-04-18</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B106" t="str">
-        <v>Souvenir</v>
+        <v>Travel</v>
       </c>
       <c r="C106" t="str">
-        <v>Gift, Biscuits</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D106">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107">
@@ -16076,55 +16076,55 @@
         <v>2026-04-18</v>
       </c>
       <c r="B107" t="str">
-        <v>Groceries</v>
+        <v>Souvenir</v>
       </c>
       <c r="C107" t="str">
-        <v>Corn And Gauva</v>
+        <v>Gift, Biscuits</v>
       </c>
       <c r="D107">
-        <v>3.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-18</v>
       </c>
       <c r="B108" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C108" t="str">
-        <v>Oyster Card</v>
+        <v>Corn And Gauva</v>
       </c>
       <c r="D108">
-        <v>30</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2026-03-31</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B109" t="str">
         <v>Travel</v>
       </c>
       <c r="C109" t="str">
-        <v>Total Tfl Cost</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D109">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2026-04-11</v>
+        <v>2026-03-31</v>
       </c>
       <c r="B110" t="str">
-        <v>Praveen Shoes</v>
+        <v>Travel</v>
       </c>
       <c r="C110" t="str">
-        <v>Shoes</v>
+        <v>Total Tfl Cost</v>
       </c>
       <c r="D110">
-        <v>110</v>
+        <v>67</v>
       </c>
     </row>
     <row r="111">
@@ -16132,27 +16132,27 @@
         <v>2026-04-11</v>
       </c>
       <c r="B111" t="str">
-        <v>Eating Out</v>
+        <v>Praveen Shoes</v>
       </c>
       <c r="C111" t="str">
-        <v>Spitalfield Market</v>
+        <v>Shoes</v>
       </c>
       <c r="D111">
-        <v>8</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="B112" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C112" t="str">
-        <v>Too Good To Go</v>
+        <v>Spitalfield Market</v>
       </c>
       <c r="D112">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
@@ -16160,10 +16160,10 @@
         <v>2026-04-09</v>
       </c>
       <c r="B113" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C113" t="str">
-        <v>Yogurt</v>
+        <v>Too Good To Go</v>
       </c>
       <c r="D113">
         <v>4</v>
@@ -16171,72 +16171,72 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-09</v>
       </c>
       <c r="B114" t="str">
-        <v>Visa Fee</v>
+        <v>Groceries</v>
       </c>
       <c r="C114" t="str">
-        <v>Visa Gee</v>
+        <v>Yogurt</v>
       </c>
       <c r="D114">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B115" t="str">
-        <v>Travel</v>
+        <v>Visa Fee</v>
       </c>
       <c r="C115" t="str">
-        <v>Oyster Card</v>
+        <v>Visa Gee</v>
       </c>
       <c r="D115">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B116" t="str">
-        <v>Visa Picture</v>
+        <v>Travel</v>
       </c>
       <c r="C116" t="str">
-        <v>Snappy Snap</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D116">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B117" t="str">
-        <v>Provisions</v>
+        <v>Visa Picture</v>
       </c>
       <c r="C117" t="str">
-        <v>Water Bottle</v>
+        <v>Snappy Snap</v>
       </c>
       <c r="D117">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B118" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C118" t="str">
-        <v>Poornima Roti Curry(malaysia Food)</v>
+        <v>Water Bottle</v>
       </c>
       <c r="D118">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
@@ -16244,41 +16244,41 @@
         <v>2026-04-06</v>
       </c>
       <c r="B119" t="str">
-        <v>Germany Visa Stuff</v>
+        <v>Eating Out</v>
       </c>
       <c r="C119" t="str">
-        <v>Travel Insurance, Airbnb</v>
+        <v>Poornima Roti Curry(malaysia Food)</v>
       </c>
       <c r="D119">
-        <v>111</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B120" t="str">
-        <v>Provisions</v>
+        <v>Germany Visa Stuff</v>
       </c>
       <c r="C120" t="str">
-        <v>Yogurt, Lemon</v>
+        <v>Travel Insurance, Airbnb</v>
       </c>
       <c r="D120">
-        <v>3</v>
+        <v>111</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="B121" t="str">
         <v>Provisions</v>
       </c>
       <c r="C121" t="str">
-        <v>Rice Flour, Oil,</v>
+        <v>Yogurt, Lemon</v>
       </c>
       <c r="D121">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
@@ -16286,13 +16286,13 @@
         <v>2026-04-04</v>
       </c>
       <c r="B122" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C122" t="str">
-        <v>Spinach, Ginger, Vegetable</v>
+        <v>Rice Flour, Oil,</v>
       </c>
       <c r="D122">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123">
@@ -16300,27 +16300,27 @@
         <v>2026-04-04</v>
       </c>
       <c r="B123" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C123" t="str">
-        <v>Lamb And Chicken</v>
+        <v>Spinach, Ginger, Vegetable</v>
       </c>
       <c r="D123">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-04</v>
       </c>
       <c r="B124" t="str">
-        <v>Cricket Tickets</v>
+        <v>Meats</v>
       </c>
       <c r="C124" t="str">
-        <v>Lords Women World Cup</v>
+        <v>Lamb And Chicken</v>
       </c>
       <c r="D124">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="125">
@@ -16328,27 +16328,27 @@
         <v>2026-04-02</v>
       </c>
       <c r="B125" t="str">
-        <v>Provisions</v>
+        <v>Cricket Tickets</v>
       </c>
       <c r="C125" t="str">
-        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
+        <v>Lords Women World Cup</v>
       </c>
       <c r="D125">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-02</v>
       </c>
       <c r="B126" t="str">
         <v>Provisions</v>
       </c>
       <c r="C126" t="str">
-        <v>Sainsbury's</v>
+        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
       </c>
       <c r="D126">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127">
@@ -16356,27 +16356,27 @@
         <v>2026-03-28</v>
       </c>
       <c r="B127" t="str">
-        <v>Fruits</v>
+        <v>Provisions</v>
       </c>
       <c r="C127" t="str">
-        <v>Blueberries, Avocado, Gauva</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D127">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-28</v>
       </c>
       <c r="B128" t="str">
-        <v>Movie</v>
+        <v>Fruits</v>
       </c>
       <c r="C128" t="str">
-        <v>Dhurandar</v>
+        <v>Blueberries, Avocado, Gauva</v>
       </c>
       <c r="D128">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
@@ -16384,69 +16384,69 @@
         <v>2026-03-25</v>
       </c>
       <c r="B129" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C129" t="str">
-        <v>Yogurt</v>
+        <v>Dhurandar</v>
       </c>
       <c r="D129">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-25</v>
       </c>
       <c r="B130" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C130" t="str">
-        <v>Pizza Pilgrims</v>
+        <v>Yogurt</v>
       </c>
       <c r="D130">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="B131" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C131" t="str">
-        <v>Milk, Yogurt, Flowers, Butter</v>
+        <v>Pizza Pilgrims</v>
       </c>
       <c r="D131">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="B132" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C132" t="str">
-        <v>Praveen</v>
+        <v>Milk, Yogurt, Flowers, Butter</v>
       </c>
       <c r="D132">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-17</v>
       </c>
       <c r="B133" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C133" t="str">
-        <v>Provisions</v>
+        <v>Praveen</v>
       </c>
       <c r="D133">
-        <v>59</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
@@ -16454,27 +16454,27 @@
         <v>2026-03-15</v>
       </c>
       <c r="B134" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C134" t="str">
-        <v>Vegetables</v>
+        <v>Provisions</v>
       </c>
       <c r="D134">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-15</v>
       </c>
       <c r="B135" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C135" t="str">
-        <v>Gauva, Blueberries</v>
+        <v>Vegetables</v>
       </c>
       <c r="D135">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="136">
@@ -16482,13 +16482,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B136" t="str">
-        <v>Eating Out</v>
+        <v>Fruits</v>
       </c>
       <c r="C136" t="str">
-        <v>Haleem And Samosa</v>
+        <v>Gauva, Blueberries</v>
       </c>
       <c r="D136">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
@@ -16496,13 +16496,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B137" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C137" t="str">
-        <v>Frozen Lotus Stem And Beans</v>
+        <v>Haleem And Samosa</v>
       </c>
       <c r="D137">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138">
@@ -16510,13 +16510,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B138" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C138" t="str">
-        <v>Vegetables</v>
+        <v>Frozen Lotus Stem And Beans</v>
       </c>
       <c r="D138">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
@@ -16524,27 +16524,27 @@
         <v>2026-03-14</v>
       </c>
       <c r="B139" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C139" t="str">
-        <v>Lidl</v>
+        <v>Vegetables</v>
       </c>
       <c r="D139">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-14</v>
       </c>
       <c r="B140" t="str">
-        <v>Medication</v>
+        <v>Provisions</v>
       </c>
       <c r="C140" t="str">
-        <v>Fish Oil, Pregnacare</v>
+        <v>Lidl</v>
       </c>
       <c r="D140">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141">
@@ -16552,69 +16552,69 @@
         <v>2026-03-09</v>
       </c>
       <c r="B141" t="str">
-        <v>Provisions</v>
+        <v>Medication</v>
       </c>
       <c r="C141" t="str">
-        <v>Yogurt, Oats, Sourdough, Detergent</v>
+        <v>Fish Oil, Pregnacare</v>
       </c>
       <c r="D141">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="B142" t="str">
-        <v>Washing</v>
+        <v>Provisions</v>
       </c>
       <c r="C142" t="str">
-        <v>Clothes</v>
+        <v>Yogurt, Oats, Sourdough, Detergent</v>
       </c>
       <c r="D142">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-08</v>
       </c>
       <c r="B143" t="str">
-        <v>Praveen</v>
+        <v>Washing</v>
       </c>
       <c r="C143" t="str">
-        <v>Praveen eating out</v>
+        <v>Clothes</v>
       </c>
       <c r="D143">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="B144" t="str">
-        <v>Meats</v>
+        <v>Praveen</v>
       </c>
       <c r="C144" t="str">
-        <v>Chicken and Fish</v>
+        <v>Praveen eating out</v>
       </c>
       <c r="D144">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-01</v>
       </c>
       <c r="B145" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C145" t="str">
-        <v>Vegetables</v>
+        <v>Chicken and Fish</v>
       </c>
       <c r="D145">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="146">
@@ -16622,32 +16622,46 @@
         <v>2026-03-07</v>
       </c>
       <c r="B146" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C146" t="str">
-        <v>Mobos Ethiopian Restaurant</v>
+        <v>Vegetables</v>
       </c>
       <c r="D146">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Eating Out</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Mobos Ethiopian Restaurant</v>
+      </c>
+      <c r="D147">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
         <v>2026-03-06</v>
       </c>
-      <c r="B147" t="str">
+      <c r="B148" t="str">
         <v>Provisions</v>
       </c>
-      <c r="C147" t="str">
+      <c r="C148" t="str">
         <v>Milk and Doritos</v>
       </c>
-      <c r="D147">
+      <c r="D148">
         <v>2.95</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D147"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D148"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -14579,7 +14579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D149"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -14603,16 +14603,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-25</v>
+        <v>2026-08-28</v>
       </c>
       <c r="B2" t="str">
-        <v>Eating Out</v>
+        <v>Badminton</v>
       </c>
       <c r="C2" t="str">
-        <v>Deliveroo</v>
+        <v>Badminton</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -14620,41 +14620,41 @@
         <v>2026-08-25</v>
       </c>
       <c r="B3" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C3" t="str">
-        <v>Sainsbury's , Tesco</v>
+        <v>Deliveroo</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-25</v>
       </c>
       <c r="B4" t="str">
-        <v>Bike Tyre</v>
+        <v>Groceries</v>
       </c>
       <c r="C4" t="str">
-        <v>Bike Tube And Tyre</v>
+        <v>Sainsbury's , Tesco</v>
       </c>
       <c r="D4">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
       <c r="B5" t="str">
-        <v>Badminton</v>
+        <v>Bike Tyre</v>
       </c>
       <c r="C5" t="str">
-        <v>Badminton</v>
+        <v>Bike Tube And Tyre</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -14662,13 +14662,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B6" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C6" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -14676,13 +14676,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B7" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C7" t="str">
-        <v>Lidl - Prawns , Kefir And Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -14693,38 +14693,38 @@
         <v>Groceries</v>
       </c>
       <c r="C8" t="str">
-        <v>Fruits For Lakshmi Pooja</v>
+        <v>Lidl - Prawns , Kefir And Yogurt</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-21</v>
       </c>
       <c r="B9" t="str">
-        <v>Movie</v>
+        <v>Groceries</v>
       </c>
       <c r="C9" t="str">
-        <v>Toxic</v>
+        <v>Fruits For Lakshmi Pooja</v>
       </c>
       <c r="D9">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-08-15</v>
+        <v>2026-08-18</v>
       </c>
       <c r="B10" t="str">
-        <v>Groceries</v>
+        <v>Movie</v>
       </c>
       <c r="C10" t="str">
-        <v>Sainsbury's And Lidl</v>
+        <v>Toxic</v>
       </c>
       <c r="D10">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -14732,13 +14732,13 @@
         <v>2026-08-15</v>
       </c>
       <c r="B11" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C11" t="str">
-        <v>Fruit</v>
+        <v>Sainsbury's And Lidl</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -14746,27 +14746,27 @@
         <v>2026-08-15</v>
       </c>
       <c r="B12" t="str">
-        <v>Meats</v>
+        <v>Fruits</v>
       </c>
       <c r="C12" t="str">
-        <v>Lamb, Samosa, Chicken Keema</v>
+        <v>Fruit</v>
       </c>
       <c r="D12">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-15</v>
       </c>
       <c r="B13" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C13" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Lamb, Samosa, Chicken Keema</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -14774,125 +14774,125 @@
         <v>2026-08-14</v>
       </c>
       <c r="B14" t="str">
-        <v>Badminton</v>
+        <v>Groceries</v>
       </c>
       <c r="C14" t="str">
-        <v>Badminton</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D14">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-14</v>
       </c>
       <c r="B15" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C15" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D15">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-10</v>
       </c>
       <c r="B16" t="str">
-        <v>Badminton</v>
+        <v>Travel</v>
       </c>
       <c r="C16" t="str">
-        <v>Badminton</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D16">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B17" t="str">
-        <v>Groceries</v>
+        <v>Badminton</v>
       </c>
       <c r="C17" t="str">
-        <v>Yogurt And Cheese</v>
+        <v>Badminton</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-08-04</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B18" t="str">
         <v>Groceries</v>
       </c>
       <c r="C18" t="str">
-        <v>Cucumber, Tissues, Corn Flour</v>
+        <v>Yogurt And Cheese</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-04</v>
       </c>
       <c r="B19" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C19" t="str">
-        <v>Oyster Card</v>
+        <v>Cucumber, Tissues, Corn Flour</v>
       </c>
       <c r="D19">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-28</v>
       </c>
       <c r="B20" t="str">
-        <v>Provisions</v>
+        <v>Travel</v>
       </c>
       <c r="C20" t="str">
-        <v>Egg, Office Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-27</v>
       </c>
       <c r="B21" t="str">
         <v>Provisions</v>
       </c>
       <c r="C21" t="str">
-        <v>Lidl- Yogurt</v>
+        <v>Egg, Office Yogurt</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-30</v>
       </c>
       <c r="B22" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C22" t="str">
-        <v>Praveen - Boba Tea</v>
+        <v>Lidl- Yogurt</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -14900,27 +14900,27 @@
         <v>2026-07-25</v>
       </c>
       <c r="B23" t="str">
-        <v>Abdul Son Marriage Gift</v>
+        <v>Eating Out</v>
       </c>
       <c r="C23" t="str">
-        <v>Gift</v>
+        <v>Praveen - Boba Tea</v>
       </c>
       <c r="D23">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-07-26</v>
+        <v>2026-07-25</v>
       </c>
       <c r="B24" t="str">
-        <v>Badminton</v>
+        <v>Abdul Son Marriage Gift</v>
       </c>
       <c r="C24" t="str">
-        <v>Badminton</v>
+        <v>Gift</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -14928,27 +14928,27 @@
         <v>2026-07-26</v>
       </c>
       <c r="B25" t="str">
-        <v>House</v>
+        <v>Badminton</v>
       </c>
       <c r="C25" t="str">
-        <v>Houzecheck - House Evaluation</v>
+        <v>Badminton</v>
       </c>
       <c r="D25">
-        <v>593</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-26</v>
       </c>
       <c r="B26" t="str">
-        <v>Travel</v>
+        <v>House</v>
       </c>
       <c r="C26" t="str">
-        <v>Norway - H&amp;m - Pau Baby Dress</v>
+        <v>Houzecheck - House Evaluation</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>593</v>
       </c>
     </row>
     <row r="27">
@@ -14959,7 +14959,7 @@
         <v>Travel</v>
       </c>
       <c r="C27" t="str">
-        <v>Norway - Bus Pass</v>
+        <v>Norway - H&amp;m - Pau Baby Dress</v>
       </c>
       <c r="D27">
         <v>12</v>
@@ -14967,58 +14967,58 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B28" t="str">
         <v>Travel</v>
       </c>
       <c r="C28" t="str">
-        <v>Norway - Radical Storage Oslo</v>
+        <v>Norway - Bus Pass</v>
       </c>
       <c r="D28">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B29" t="str">
         <v>Travel</v>
       </c>
       <c r="C29" t="str">
-        <v>Oyster Card</v>
+        <v>Norway - Radical Storage Oslo</v>
       </c>
       <c r="D29">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B30" t="str">
-        <v>Norway</v>
+        <v>Travel</v>
       </c>
       <c r="C30" t="str">
-        <v>Travel Insurance</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D30">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B31" t="str">
         <v>Norway</v>
       </c>
       <c r="C31" t="str">
-        <v>Chocolate</v>
+        <v>Travel Insurance</v>
       </c>
       <c r="D31">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -15026,27 +15026,27 @@
         <v>2026-07-13</v>
       </c>
       <c r="B32" t="str">
-        <v>House</v>
+        <v>Norway</v>
       </c>
       <c r="C32" t="str">
-        <v>Leadenhall</v>
+        <v>Chocolate</v>
       </c>
       <c r="D32">
-        <v>820</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B33" t="str">
-        <v>Provisions</v>
+        <v>House</v>
       </c>
       <c r="C33" t="str">
-        <v>Yogurt</v>
+        <v>Leadenhall</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>820</v>
       </c>
     </row>
     <row r="34">
@@ -15054,13 +15054,13 @@
         <v>2026-07-11</v>
       </c>
       <c r="B34" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C34" t="str">
-        <v>Amarino Ice Cream</v>
+        <v>Yogurt</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -15068,55 +15068,55 @@
         <v>2026-07-11</v>
       </c>
       <c r="B35" t="str">
-        <v>Gifts To Norway</v>
+        <v>Eating Out</v>
       </c>
       <c r="C35" t="str">
-        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
+        <v>Amarino Ice Cream</v>
       </c>
       <c r="D35">
-        <v>97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B36" t="str">
-        <v>Praveen</v>
+        <v>Gifts To Norway</v>
       </c>
       <c r="C36" t="str">
-        <v>Badminton</v>
+        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B37" t="str">
-        <v>Travel</v>
+        <v>Praveen</v>
       </c>
       <c r="C37" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D37">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B38" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C38" t="str">
-        <v>Shakti</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D38">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -15124,13 +15124,13 @@
         <v>2026-07-05</v>
       </c>
       <c r="B39" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C39" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -15138,41 +15138,41 @@
         <v>2026-07-05</v>
       </c>
       <c r="B40" t="str">
-        <v>Haircut</v>
+        <v>Meats</v>
       </c>
       <c r="C40" t="str">
-        <v>Haircut</v>
+        <v>Chicken</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B41" t="str">
-        <v>Provisions</v>
+        <v>Haircut</v>
       </c>
       <c r="C41" t="str">
-        <v>Lidl, Sainsbury's, Iceland</v>
+        <v>Haircut</v>
       </c>
       <c r="D41">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B42" t="str">
-        <v>Superdrug</v>
+        <v>Provisions</v>
       </c>
       <c r="C42" t="str">
-        <v>Shoes Deodorant</v>
+        <v>Lidl, Sainsbury's, Iceland</v>
       </c>
       <c r="D42">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43">
@@ -15180,83 +15180,83 @@
         <v>2026-07-04</v>
       </c>
       <c r="B43" t="str">
-        <v>Medicine</v>
+        <v>Superdrug</v>
       </c>
       <c r="C43" t="str">
-        <v>H&amp;b</v>
+        <v>Shoes Deodorant</v>
       </c>
       <c r="D43">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B44" t="str">
-        <v>Praveen - Badminton</v>
+        <v>Medicine</v>
       </c>
       <c r="C44" t="str">
-        <v>Badminton</v>
+        <v>H&amp;b</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-06-30</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B45" t="str">
-        <v>Provisions</v>
+        <v>Praveen - Badminton</v>
       </c>
       <c r="C45" t="str">
-        <v>Lidl - Detergent</v>
+        <v>Badminton</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-06-29</v>
+        <v>2026-06-30</v>
       </c>
       <c r="B46" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C46" t="str">
-        <v>Praveen &amp; Poornima - Cake</v>
+        <v>Lidl - Detergent</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-06-28</v>
+        <v>2026-06-29</v>
       </c>
       <c r="B47" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C47" t="str">
-        <v>Poornima And Praveen (tajrish Restaurant)</v>
+        <v>Praveen &amp; Poornima - Cake</v>
       </c>
       <c r="D47">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="B48" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C48" t="str">
-        <v>Lidl</v>
+        <v>Poornima And Praveen (tajrish Restaurant)</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49">
@@ -15267,10 +15267,10 @@
         <v>Groceries</v>
       </c>
       <c r="C49" t="str">
-        <v>Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D49">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -15278,13 +15278,13 @@
         <v>2026-06-27</v>
       </c>
       <c r="B50" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C50" t="str">
-        <v>Grapes, Guava, Pomegranate, Avacado</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -15292,41 +15292,41 @@
         <v>2026-06-27</v>
       </c>
       <c r="B51" t="str">
-        <v>Provisions</v>
+        <v>Fruits</v>
       </c>
       <c r="C51" t="str">
-        <v>M&amp;s</v>
+        <v>Grapes, Guava, Pomegranate, Avacado</v>
       </c>
       <c r="D51">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-27</v>
       </c>
       <c r="B52" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C52" t="str">
-        <v>Oyster</v>
+        <v>M&amp;s</v>
       </c>
       <c r="D52">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-26</v>
       </c>
       <c r="B53" t="str">
-        <v>Fan</v>
+        <v>Travel</v>
       </c>
       <c r="C53" t="str">
-        <v>Fan</v>
+        <v>Oyster</v>
       </c>
       <c r="D53">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
@@ -15334,13 +15334,13 @@
         <v>2026-06-24</v>
       </c>
       <c r="B54" t="str">
-        <v>Groceries</v>
+        <v>Fan</v>
       </c>
       <c r="C54" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Fan</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55">
@@ -15348,27 +15348,27 @@
         <v>2026-06-24</v>
       </c>
       <c r="B55" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C55" t="str">
-        <v>Yogurt, Dates, Prunes</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D55">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-06-21</v>
+        <v>2026-06-24</v>
       </c>
       <c r="B56" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C56" t="str">
-        <v>Chicken</v>
+        <v>Yogurt, Dates, Prunes</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -15379,38 +15379,38 @@
         <v>Meats</v>
       </c>
       <c r="C57" t="str">
-        <v>Fish - Salmon And Travelly</v>
+        <v>Chicken</v>
       </c>
       <c r="D57">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-06-14</v>
+        <v>2026-06-21</v>
       </c>
       <c r="B58" t="str">
-        <v>Travel</v>
+        <v>Meats</v>
       </c>
       <c r="C58" t="str">
-        <v>Flight Trd - Lhr</v>
+        <v>Fish - Salmon And Travelly</v>
       </c>
       <c r="D58">
-        <v>91</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-06-13</v>
+        <v>2026-06-14</v>
       </c>
       <c r="B59" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C59" t="str">
-        <v>Lidl &amp; Sainsbury's</v>
+        <v>Flight Trd - Lhr</v>
       </c>
       <c r="D59">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60">
@@ -15418,27 +15418,27 @@
         <v>2026-06-13</v>
       </c>
       <c r="B60" t="str">
-        <v>Belgravia</v>
+        <v>Groceries</v>
       </c>
       <c r="C60" t="str">
-        <v>Belgravia</v>
+        <v>Lidl &amp; Sainsbury's</v>
       </c>
       <c r="D60">
-        <v>186</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-06-18</v>
+        <v>2026-06-13</v>
       </c>
       <c r="B61" t="str">
-        <v>Provisions</v>
+        <v>Belgravia</v>
       </c>
       <c r="C61" t="str">
-        <v>Egg</v>
+        <v>Belgravia</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62">
@@ -15446,69 +15446,69 @@
         <v>2026-06-18</v>
       </c>
       <c r="B62" t="str">
-        <v>Cycle</v>
+        <v>Provisions</v>
       </c>
       <c r="C62" t="str">
-        <v>Cycle</v>
+        <v>Egg</v>
       </c>
       <c r="D62">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-18</v>
       </c>
       <c r="B63" t="str">
-        <v>Travel</v>
+        <v>Cycle</v>
       </c>
       <c r="C63" t="str">
-        <v>Lgw - Oslo</v>
+        <v>Cycle</v>
       </c>
       <c r="D63">
-        <v>168</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="B64" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C64" t="str">
-        <v>Lidl</v>
+        <v>Lgw - Oslo</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-10</v>
       </c>
       <c r="B65" t="str">
         <v>Groceries</v>
       </c>
       <c r="C65" t="str">
-        <v>Lidl And Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D65">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B66" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C66" t="str">
-        <v>Vegetables, Fruits</v>
+        <v>Lidl And Sainsbury's</v>
       </c>
       <c r="D66">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
@@ -15516,83 +15516,83 @@
         <v>2026-06-06</v>
       </c>
       <c r="B67" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C67" t="str">
-        <v>Lamb</v>
+        <v>Vegetables, Fruits</v>
       </c>
       <c r="D67">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-06-12</v>
+        <v>2026-06-06</v>
       </c>
       <c r="B68" t="str">
-        <v>Movie</v>
+        <v>Meats</v>
       </c>
       <c r="C68" t="str">
-        <v>Peddi</v>
+        <v>Lamb</v>
       </c>
       <c r="D68">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-05-31</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B69" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C69" t="str">
-        <v>Yogurt, Corn, Kefir</v>
+        <v>Peddi</v>
       </c>
       <c r="D69">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-31</v>
       </c>
       <c r="B70" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C70" t="str">
-        <v>Oyster Card</v>
+        <v>Yogurt, Corn, Kefir</v>
       </c>
       <c r="D70">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-29</v>
       </c>
       <c r="B71" t="str">
-        <v>Amazon</v>
+        <v>Travel</v>
       </c>
       <c r="C71" t="str">
-        <v>Face Wash, Moisturizer</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D71">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-28</v>
       </c>
       <c r="B72" t="str">
-        <v>Eating Out</v>
+        <v>Amazon</v>
       </c>
       <c r="C72" t="str">
-        <v>Praveen</v>
+        <v>Face Wash, Moisturizer</v>
       </c>
       <c r="D72">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
@@ -15600,13 +15600,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B73" t="str">
-        <v>Meats</v>
+        <v>Eating Out</v>
       </c>
       <c r="C73" t="str">
-        <v>Chicken</v>
+        <v>Praveen</v>
       </c>
       <c r="D73">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">
@@ -15614,13 +15614,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B74" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C74" t="str">
-        <v>Shakto</v>
+        <v>Chicken</v>
       </c>
       <c r="D74">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -15631,24 +15631,24 @@
         <v>Groceries</v>
       </c>
       <c r="C75" t="str">
-        <v>Bread, Avacado, Lemon, Onion</v>
+        <v>Shakto</v>
       </c>
       <c r="D75">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="B76" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C76" t="str">
-        <v>Praveen Cake</v>
+        <v>Bread, Avacado, Lemon, Onion</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -15656,10 +15656,10 @@
         <v>2026-05-23</v>
       </c>
       <c r="B77" t="str">
-        <v>Fruits</v>
+        <v>Eating Out</v>
       </c>
       <c r="C77" t="str">
-        <v>Avacado, Guava</v>
+        <v>Praveen Cake</v>
       </c>
       <c r="D77">
         <v>5</v>
@@ -15670,55 +15670,55 @@
         <v>2026-05-23</v>
       </c>
       <c r="B78" t="str">
-        <v>Groceries</v>
+        <v>Fruits</v>
       </c>
       <c r="C78" t="str">
-        <v>Corn, Yogurt, Cucumber, Cake</v>
+        <v>Avacado, Guava</v>
       </c>
       <c r="D78">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="B79" t="str">
         <v>Groceries</v>
       </c>
       <c r="C79" t="str">
-        <v>Banana</v>
+        <v>Corn, Yogurt, Cucumber, Cake</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="B80" t="str">
         <v>Groceries</v>
       </c>
       <c r="C80" t="str">
-        <v>Potatoes And Dish Was Liquid</v>
+        <v>Banana</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="B81" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C81" t="str">
-        <v>Lamb</v>
+        <v>Potatoes And Dish Was Liquid</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -15726,27 +15726,27 @@
         <v>2026-05-17</v>
       </c>
       <c r="B82" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C82" t="str">
-        <v>Sainsbury's - Carrots, Onion</v>
+        <v>Lamb</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="B83" t="str">
         <v>Groceries</v>
       </c>
       <c r="C83" t="str">
-        <v>Shakti</v>
+        <v>Sainsbury's - Carrots, Onion</v>
       </c>
       <c r="D83">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -15754,55 +15754,55 @@
         <v>2026-05-16</v>
       </c>
       <c r="B84" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C84" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D84">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="B85" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C85" t="str">
-        <v>Yogurt, Vegetables</v>
+        <v>Chicken</v>
       </c>
       <c r="D85">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B86" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C86" t="str">
-        <v>Munich - Gifts To Office</v>
+        <v>Yogurt, Vegetables</v>
       </c>
       <c r="D86">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="B87" t="str">
         <v>Travel</v>
       </c>
       <c r="C87" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Gifts To Office</v>
       </c>
       <c r="D87">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
@@ -15813,10 +15813,10 @@
         <v>Travel</v>
       </c>
       <c r="C88" t="str">
-        <v>Munich - Water And Juice</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D88">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89">
@@ -15827,10 +15827,10 @@
         <v>Travel</v>
       </c>
       <c r="C89" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Water And Juice</v>
       </c>
       <c r="D89">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -15841,24 +15841,24 @@
         <v>Travel</v>
       </c>
       <c r="C90" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D90">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="B91" t="str">
         <v>Travel</v>
       </c>
       <c r="C91" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D91">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92">
@@ -15869,10 +15869,10 @@
         <v>Travel</v>
       </c>
       <c r="C92" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D92">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93">
@@ -15883,10 +15883,10 @@
         <v>Travel</v>
       </c>
       <c r="C93" t="str">
-        <v>Munich - Bmw Museum Ticket</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D93">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -15897,10 +15897,10 @@
         <v>Travel</v>
       </c>
       <c r="C94" t="str">
-        <v>Munich Lunch</v>
+        <v>Munich - Bmw Museum Ticket</v>
       </c>
       <c r="D94">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
@@ -15911,10 +15911,10 @@
         <v>Travel</v>
       </c>
       <c r="C95" t="str">
-        <v>Munich Walking Tour</v>
+        <v>Munich Lunch</v>
       </c>
       <c r="D95">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96">
@@ -15925,24 +15925,24 @@
         <v>Travel</v>
       </c>
       <c r="C96" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich Walking Tour</v>
       </c>
       <c r="D96">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B97" t="str">
         <v>Travel</v>
       </c>
       <c r="C97" t="str">
-        <v>Dinner - Mac And Cheese</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D97">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
@@ -15953,10 +15953,10 @@
         <v>Travel</v>
       </c>
       <c r="C98" t="str">
-        <v>Pretzel Snack</v>
+        <v>Dinner - Mac And Cheese</v>
       </c>
       <c r="D98">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99">
@@ -15967,10 +15967,10 @@
         <v>Travel</v>
       </c>
       <c r="C99" t="str">
-        <v>Lidl - Water, Coke, Yogurt</v>
+        <v>Pretzel Snack</v>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -15981,10 +15981,10 @@
         <v>Travel</v>
       </c>
       <c r="C100" t="str">
-        <v>Germany Public Transport Ticket</v>
+        <v>Lidl - Water, Coke, Yogurt</v>
       </c>
       <c r="D100">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -15992,27 +15992,27 @@
         <v>2026-05-09</v>
       </c>
       <c r="B101" t="str">
-        <v>Eating Out</v>
+        <v>Travel</v>
       </c>
       <c r="C101" t="str">
-        <v>Airport Pret</v>
+        <v>Germany Public Transport Ticket</v>
       </c>
       <c r="D101">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B102" t="str">
-        <v>Boots</v>
+        <v>Eating Out</v>
       </c>
       <c r="C102" t="str">
-        <v>Face Moisturizer</v>
+        <v>Airport Pret</v>
       </c>
       <c r="D102">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -16020,13 +16020,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B103" t="str">
-        <v>Provisions</v>
+        <v>Boots</v>
       </c>
       <c r="C103" t="str">
-        <v>Eggs</v>
+        <v>Face Moisturizer</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104">
@@ -16034,13 +16034,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B104" t="str">
-        <v>Shopping</v>
+        <v>Provisions</v>
       </c>
       <c r="C104" t="str">
-        <v>Belt</v>
+        <v>Eggs</v>
       </c>
       <c r="D104">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -16048,10 +16048,10 @@
         <v>2026-05-08</v>
       </c>
       <c r="B105" t="str">
-        <v>Eating Out</v>
+        <v>Shopping</v>
       </c>
       <c r="C105" t="str">
-        <v>Praveen</v>
+        <v>Belt</v>
       </c>
       <c r="D105">
         <v>7</v>
@@ -16059,30 +16059,30 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B106" t="str">
-        <v>Travel</v>
+        <v>Eating Out</v>
       </c>
       <c r="C106" t="str">
-        <v>Oyster Card</v>
+        <v>Praveen</v>
       </c>
       <c r="D106">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2026-04-18</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B107" t="str">
-        <v>Souvenir</v>
+        <v>Travel</v>
       </c>
       <c r="C107" t="str">
-        <v>Gift, Biscuits</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D107">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108">
@@ -16090,55 +16090,55 @@
         <v>2026-04-18</v>
       </c>
       <c r="B108" t="str">
-        <v>Groceries</v>
+        <v>Souvenir</v>
       </c>
       <c r="C108" t="str">
-        <v>Corn And Gauva</v>
+        <v>Gift, Biscuits</v>
       </c>
       <c r="D108">
-        <v>3.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-18</v>
       </c>
       <c r="B109" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C109" t="str">
-        <v>Oyster Card</v>
+        <v>Corn And Gauva</v>
       </c>
       <c r="D109">
-        <v>30</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2026-03-31</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B110" t="str">
         <v>Travel</v>
       </c>
       <c r="C110" t="str">
-        <v>Total Tfl Cost</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D110">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>2026-04-11</v>
+        <v>2026-03-31</v>
       </c>
       <c r="B111" t="str">
-        <v>Praveen Shoes</v>
+        <v>Travel</v>
       </c>
       <c r="C111" t="str">
-        <v>Shoes</v>
+        <v>Total Tfl Cost</v>
       </c>
       <c r="D111">
-        <v>110</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112">
@@ -16146,27 +16146,27 @@
         <v>2026-04-11</v>
       </c>
       <c r="B112" t="str">
-        <v>Eating Out</v>
+        <v>Praveen Shoes</v>
       </c>
       <c r="C112" t="str">
-        <v>Spitalfield Market</v>
+        <v>Shoes</v>
       </c>
       <c r="D112">
-        <v>8</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="B113" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C113" t="str">
-        <v>Too Good To Go</v>
+        <v>Spitalfield Market</v>
       </c>
       <c r="D113">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114">
@@ -16174,10 +16174,10 @@
         <v>2026-04-09</v>
       </c>
       <c r="B114" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C114" t="str">
-        <v>Yogurt</v>
+        <v>Too Good To Go</v>
       </c>
       <c r="D114">
         <v>4</v>
@@ -16185,72 +16185,72 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-09</v>
       </c>
       <c r="B115" t="str">
-        <v>Visa Fee</v>
+        <v>Groceries</v>
       </c>
       <c r="C115" t="str">
-        <v>Visa Gee</v>
+        <v>Yogurt</v>
       </c>
       <c r="D115">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B116" t="str">
-        <v>Travel</v>
+        <v>Visa Fee</v>
       </c>
       <c r="C116" t="str">
-        <v>Oyster Card</v>
+        <v>Visa Gee</v>
       </c>
       <c r="D116">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B117" t="str">
-        <v>Visa Picture</v>
+        <v>Travel</v>
       </c>
       <c r="C117" t="str">
-        <v>Snappy Snap</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D117">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B118" t="str">
-        <v>Provisions</v>
+        <v>Visa Picture</v>
       </c>
       <c r="C118" t="str">
-        <v>Water Bottle</v>
+        <v>Snappy Snap</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B119" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C119" t="str">
-        <v>Poornima Roti Curry(malaysia Food)</v>
+        <v>Water Bottle</v>
       </c>
       <c r="D119">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -16258,41 +16258,41 @@
         <v>2026-04-06</v>
       </c>
       <c r="B120" t="str">
-        <v>Germany Visa Stuff</v>
+        <v>Eating Out</v>
       </c>
       <c r="C120" t="str">
-        <v>Travel Insurance, Airbnb</v>
+        <v>Poornima Roti Curry(malaysia Food)</v>
       </c>
       <c r="D120">
-        <v>111</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B121" t="str">
-        <v>Provisions</v>
+        <v>Germany Visa Stuff</v>
       </c>
       <c r="C121" t="str">
-        <v>Yogurt, Lemon</v>
+        <v>Travel Insurance, Airbnb</v>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>111</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="B122" t="str">
         <v>Provisions</v>
       </c>
       <c r="C122" t="str">
-        <v>Rice Flour, Oil,</v>
+        <v>Yogurt, Lemon</v>
       </c>
       <c r="D122">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -16300,13 +16300,13 @@
         <v>2026-04-04</v>
       </c>
       <c r="B123" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C123" t="str">
-        <v>Spinach, Ginger, Vegetable</v>
+        <v>Rice Flour, Oil,</v>
       </c>
       <c r="D123">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124">
@@ -16314,27 +16314,27 @@
         <v>2026-04-04</v>
       </c>
       <c r="B124" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C124" t="str">
-        <v>Lamb And Chicken</v>
+        <v>Spinach, Ginger, Vegetable</v>
       </c>
       <c r="D124">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-04</v>
       </c>
       <c r="B125" t="str">
-        <v>Cricket Tickets</v>
+        <v>Meats</v>
       </c>
       <c r="C125" t="str">
-        <v>Lords Women World Cup</v>
+        <v>Lamb And Chicken</v>
       </c>
       <c r="D125">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126">
@@ -16342,27 +16342,27 @@
         <v>2026-04-02</v>
       </c>
       <c r="B126" t="str">
-        <v>Provisions</v>
+        <v>Cricket Tickets</v>
       </c>
       <c r="C126" t="str">
-        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
+        <v>Lords Women World Cup</v>
       </c>
       <c r="D126">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-02</v>
       </c>
       <c r="B127" t="str">
         <v>Provisions</v>
       </c>
       <c r="C127" t="str">
-        <v>Sainsbury's</v>
+        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
       </c>
       <c r="D127">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128">
@@ -16370,27 +16370,27 @@
         <v>2026-03-28</v>
       </c>
       <c r="B128" t="str">
-        <v>Fruits</v>
+        <v>Provisions</v>
       </c>
       <c r="C128" t="str">
-        <v>Blueberries, Avocado, Gauva</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D128">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-28</v>
       </c>
       <c r="B129" t="str">
-        <v>Movie</v>
+        <v>Fruits</v>
       </c>
       <c r="C129" t="str">
-        <v>Dhurandar</v>
+        <v>Blueberries, Avocado, Gauva</v>
       </c>
       <c r="D129">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
@@ -16398,69 +16398,69 @@
         <v>2026-03-25</v>
       </c>
       <c r="B130" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C130" t="str">
-        <v>Yogurt</v>
+        <v>Dhurandar</v>
       </c>
       <c r="D130">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-25</v>
       </c>
       <c r="B131" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C131" t="str">
-        <v>Pizza Pilgrims</v>
+        <v>Yogurt</v>
       </c>
       <c r="D131">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="B132" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C132" t="str">
-        <v>Milk, Yogurt, Flowers, Butter</v>
+        <v>Pizza Pilgrims</v>
       </c>
       <c r="D132">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="B133" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C133" t="str">
-        <v>Praveen</v>
+        <v>Milk, Yogurt, Flowers, Butter</v>
       </c>
       <c r="D133">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-17</v>
       </c>
       <c r="B134" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C134" t="str">
-        <v>Provisions</v>
+        <v>Praveen</v>
       </c>
       <c r="D134">
-        <v>59</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
@@ -16468,27 +16468,27 @@
         <v>2026-03-15</v>
       </c>
       <c r="B135" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C135" t="str">
-        <v>Vegetables</v>
+        <v>Provisions</v>
       </c>
       <c r="D135">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-15</v>
       </c>
       <c r="B136" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C136" t="str">
-        <v>Gauva, Blueberries</v>
+        <v>Vegetables</v>
       </c>
       <c r="D136">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="137">
@@ -16496,13 +16496,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B137" t="str">
-        <v>Eating Out</v>
+        <v>Fruits</v>
       </c>
       <c r="C137" t="str">
-        <v>Haleem And Samosa</v>
+        <v>Gauva, Blueberries</v>
       </c>
       <c r="D137">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
@@ -16510,13 +16510,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B138" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C138" t="str">
-        <v>Frozen Lotus Stem And Beans</v>
+        <v>Haleem And Samosa</v>
       </c>
       <c r="D138">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139">
@@ -16524,13 +16524,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B139" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C139" t="str">
-        <v>Vegetables</v>
+        <v>Frozen Lotus Stem And Beans</v>
       </c>
       <c r="D139">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
@@ -16538,27 +16538,27 @@
         <v>2026-03-14</v>
       </c>
       <c r="B140" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C140" t="str">
-        <v>Lidl</v>
+        <v>Vegetables</v>
       </c>
       <c r="D140">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-14</v>
       </c>
       <c r="B141" t="str">
-        <v>Medication</v>
+        <v>Provisions</v>
       </c>
       <c r="C141" t="str">
-        <v>Fish Oil, Pregnacare</v>
+        <v>Lidl</v>
       </c>
       <c r="D141">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142">
@@ -16566,69 +16566,69 @@
         <v>2026-03-09</v>
       </c>
       <c r="B142" t="str">
-        <v>Provisions</v>
+        <v>Medication</v>
       </c>
       <c r="C142" t="str">
-        <v>Yogurt, Oats, Sourdough, Detergent</v>
+        <v>Fish Oil, Pregnacare</v>
       </c>
       <c r="D142">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="B143" t="str">
-        <v>Washing</v>
+        <v>Provisions</v>
       </c>
       <c r="C143" t="str">
-        <v>Clothes</v>
+        <v>Yogurt, Oats, Sourdough, Detergent</v>
       </c>
       <c r="D143">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-08</v>
       </c>
       <c r="B144" t="str">
-        <v>Praveen</v>
+        <v>Washing</v>
       </c>
       <c r="C144" t="str">
-        <v>Praveen eating out</v>
+        <v>Clothes</v>
       </c>
       <c r="D144">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="B145" t="str">
-        <v>Meats</v>
+        <v>Praveen</v>
       </c>
       <c r="C145" t="str">
-        <v>Chicken and Fish</v>
+        <v>Praveen eating out</v>
       </c>
       <c r="D145">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-01</v>
       </c>
       <c r="B146" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C146" t="str">
-        <v>Vegetables</v>
+        <v>Chicken and Fish</v>
       </c>
       <c r="D146">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="147">
@@ -16636,32 +16636,46 @@
         <v>2026-03-07</v>
       </c>
       <c r="B147" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C147" t="str">
-        <v>Mobos Ethiopian Restaurant</v>
+        <v>Vegetables</v>
       </c>
       <c r="D147">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Eating Out</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Mobos Ethiopian Restaurant</v>
+      </c>
+      <c r="D148">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
         <v>2026-03-06</v>
       </c>
-      <c r="B148" t="str">
+      <c r="B149" t="str">
         <v>Provisions</v>
       </c>
-      <c r="C148" t="str">
+      <c r="C149" t="str">
         <v>Milk and Doritos</v>
       </c>
-      <c r="D148">
+      <c r="D149">
         <v>2.95</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D148"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D149"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -14579,7 +14579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D150"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -14603,30 +14603,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-28</v>
+        <v>2026-08-29</v>
       </c>
       <c r="B2" t="str">
-        <v>Badminton</v>
+        <v>Groceries</v>
       </c>
       <c r="C2" t="str">
-        <v>Badminton</v>
+        <v>Shakti</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-25</v>
+        <v>2026-08-28</v>
       </c>
       <c r="B3" t="str">
-        <v>Eating Out</v>
+        <v>Badminton</v>
       </c>
       <c r="C3" t="str">
-        <v>Deliveroo</v>
+        <v>Badminton</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -14634,41 +14634,41 @@
         <v>2026-08-25</v>
       </c>
       <c r="B4" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C4" t="str">
-        <v>Sainsbury's , Tesco</v>
+        <v>Deliveroo</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-25</v>
       </c>
       <c r="B5" t="str">
-        <v>Bike Tyre</v>
+        <v>Groceries</v>
       </c>
       <c r="C5" t="str">
-        <v>Bike Tube And Tyre</v>
+        <v>Sainsbury's , Tesco</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
       <c r="B6" t="str">
-        <v>Badminton</v>
+        <v>Bike Tyre</v>
       </c>
       <c r="C6" t="str">
-        <v>Badminton</v>
+        <v>Bike Tube And Tyre</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -14676,13 +14676,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B7" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C7" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -14690,13 +14690,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B8" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C8" t="str">
-        <v>Lidl - Prawns , Kefir And Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -14707,38 +14707,38 @@
         <v>Groceries</v>
       </c>
       <c r="C9" t="str">
-        <v>Fruits For Lakshmi Pooja</v>
+        <v>Lidl - Prawns , Kefir And Yogurt</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-21</v>
       </c>
       <c r="B10" t="str">
-        <v>Movie</v>
+        <v>Groceries</v>
       </c>
       <c r="C10" t="str">
-        <v>Toxic</v>
+        <v>Fruits For Lakshmi Pooja</v>
       </c>
       <c r="D10">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-08-15</v>
+        <v>2026-08-18</v>
       </c>
       <c r="B11" t="str">
-        <v>Groceries</v>
+        <v>Movie</v>
       </c>
       <c r="C11" t="str">
-        <v>Sainsbury's And Lidl</v>
+        <v>Toxic</v>
       </c>
       <c r="D11">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -14746,13 +14746,13 @@
         <v>2026-08-15</v>
       </c>
       <c r="B12" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C12" t="str">
-        <v>Fruit</v>
+        <v>Sainsbury's And Lidl</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -14760,27 +14760,27 @@
         <v>2026-08-15</v>
       </c>
       <c r="B13" t="str">
-        <v>Meats</v>
+        <v>Fruits</v>
       </c>
       <c r="C13" t="str">
-        <v>Lamb, Samosa, Chicken Keema</v>
+        <v>Fruit</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-15</v>
       </c>
       <c r="B14" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C14" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Lamb, Samosa, Chicken Keema</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -14788,125 +14788,125 @@
         <v>2026-08-14</v>
       </c>
       <c r="B15" t="str">
-        <v>Badminton</v>
+        <v>Groceries</v>
       </c>
       <c r="C15" t="str">
-        <v>Badminton</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D15">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-14</v>
       </c>
       <c r="B16" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C16" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D16">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-10</v>
       </c>
       <c r="B17" t="str">
-        <v>Badminton</v>
+        <v>Travel</v>
       </c>
       <c r="C17" t="str">
-        <v>Badminton</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D17">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B18" t="str">
-        <v>Groceries</v>
+        <v>Badminton</v>
       </c>
       <c r="C18" t="str">
-        <v>Yogurt And Cheese</v>
+        <v>Badminton</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-08-04</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B19" t="str">
         <v>Groceries</v>
       </c>
       <c r="C19" t="str">
-        <v>Cucumber, Tissues, Corn Flour</v>
+        <v>Yogurt And Cheese</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-04</v>
       </c>
       <c r="B20" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C20" t="str">
-        <v>Oyster Card</v>
+        <v>Cucumber, Tissues, Corn Flour</v>
       </c>
       <c r="D20">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-28</v>
       </c>
       <c r="B21" t="str">
-        <v>Provisions</v>
+        <v>Travel</v>
       </c>
       <c r="C21" t="str">
-        <v>Egg, Office Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-27</v>
       </c>
       <c r="B22" t="str">
         <v>Provisions</v>
       </c>
       <c r="C22" t="str">
-        <v>Lidl- Yogurt</v>
+        <v>Egg, Office Yogurt</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-30</v>
       </c>
       <c r="B23" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C23" t="str">
-        <v>Praveen - Boba Tea</v>
+        <v>Lidl- Yogurt</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -14914,27 +14914,27 @@
         <v>2026-07-25</v>
       </c>
       <c r="B24" t="str">
-        <v>Abdul Son Marriage Gift</v>
+        <v>Eating Out</v>
       </c>
       <c r="C24" t="str">
-        <v>Gift</v>
+        <v>Praveen - Boba Tea</v>
       </c>
       <c r="D24">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-07-26</v>
+        <v>2026-07-25</v>
       </c>
       <c r="B25" t="str">
-        <v>Badminton</v>
+        <v>Abdul Son Marriage Gift</v>
       </c>
       <c r="C25" t="str">
-        <v>Badminton</v>
+        <v>Gift</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -14942,27 +14942,27 @@
         <v>2026-07-26</v>
       </c>
       <c r="B26" t="str">
-        <v>House</v>
+        <v>Badminton</v>
       </c>
       <c r="C26" t="str">
-        <v>Houzecheck - House Evaluation</v>
+        <v>Badminton</v>
       </c>
       <c r="D26">
-        <v>593</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-26</v>
       </c>
       <c r="B27" t="str">
-        <v>Travel</v>
+        <v>House</v>
       </c>
       <c r="C27" t="str">
-        <v>Norway - H&amp;m - Pau Baby Dress</v>
+        <v>Houzecheck - House Evaluation</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>593</v>
       </c>
     </row>
     <row r="28">
@@ -14973,7 +14973,7 @@
         <v>Travel</v>
       </c>
       <c r="C28" t="str">
-        <v>Norway - Bus Pass</v>
+        <v>Norway - H&amp;m - Pau Baby Dress</v>
       </c>
       <c r="D28">
         <v>12</v>
@@ -14981,58 +14981,58 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B29" t="str">
         <v>Travel</v>
       </c>
       <c r="C29" t="str">
-        <v>Norway - Radical Storage Oslo</v>
+        <v>Norway - Bus Pass</v>
       </c>
       <c r="D29">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B30" t="str">
         <v>Travel</v>
       </c>
       <c r="C30" t="str">
-        <v>Oyster Card</v>
+        <v>Norway - Radical Storage Oslo</v>
       </c>
       <c r="D30">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B31" t="str">
-        <v>Norway</v>
+        <v>Travel</v>
       </c>
       <c r="C31" t="str">
-        <v>Travel Insurance</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B32" t="str">
         <v>Norway</v>
       </c>
       <c r="C32" t="str">
-        <v>Chocolate</v>
+        <v>Travel Insurance</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
@@ -15040,27 +15040,27 @@
         <v>2026-07-13</v>
       </c>
       <c r="B33" t="str">
-        <v>House</v>
+        <v>Norway</v>
       </c>
       <c r="C33" t="str">
-        <v>Leadenhall</v>
+        <v>Chocolate</v>
       </c>
       <c r="D33">
-        <v>820</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B34" t="str">
-        <v>Provisions</v>
+        <v>House</v>
       </c>
       <c r="C34" t="str">
-        <v>Yogurt</v>
+        <v>Leadenhall</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>820</v>
       </c>
     </row>
     <row r="35">
@@ -15068,13 +15068,13 @@
         <v>2026-07-11</v>
       </c>
       <c r="B35" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C35" t="str">
-        <v>Amarino Ice Cream</v>
+        <v>Yogurt</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -15082,55 +15082,55 @@
         <v>2026-07-11</v>
       </c>
       <c r="B36" t="str">
-        <v>Gifts To Norway</v>
+        <v>Eating Out</v>
       </c>
       <c r="C36" t="str">
-        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
+        <v>Amarino Ice Cream</v>
       </c>
       <c r="D36">
-        <v>97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B37" t="str">
-        <v>Praveen</v>
+        <v>Gifts To Norway</v>
       </c>
       <c r="C37" t="str">
-        <v>Badminton</v>
+        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B38" t="str">
-        <v>Travel</v>
+        <v>Praveen</v>
       </c>
       <c r="C38" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D38">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B39" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C39" t="str">
-        <v>Shakti</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D39">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
@@ -15138,13 +15138,13 @@
         <v>2026-07-05</v>
       </c>
       <c r="B40" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C40" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D40">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -15152,41 +15152,41 @@
         <v>2026-07-05</v>
       </c>
       <c r="B41" t="str">
-        <v>Haircut</v>
+        <v>Meats</v>
       </c>
       <c r="C41" t="str">
-        <v>Haircut</v>
+        <v>Chicken</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B42" t="str">
-        <v>Provisions</v>
+        <v>Haircut</v>
       </c>
       <c r="C42" t="str">
-        <v>Lidl, Sainsbury's, Iceland</v>
+        <v>Haircut</v>
       </c>
       <c r="D42">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B43" t="str">
-        <v>Superdrug</v>
+        <v>Provisions</v>
       </c>
       <c r="C43" t="str">
-        <v>Shoes Deodorant</v>
+        <v>Lidl, Sainsbury's, Iceland</v>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44">
@@ -15194,83 +15194,83 @@
         <v>2026-07-04</v>
       </c>
       <c r="B44" t="str">
-        <v>Medicine</v>
+        <v>Superdrug</v>
       </c>
       <c r="C44" t="str">
-        <v>H&amp;b</v>
+        <v>Shoes Deodorant</v>
       </c>
       <c r="D44">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B45" t="str">
-        <v>Praveen - Badminton</v>
+        <v>Medicine</v>
       </c>
       <c r="C45" t="str">
-        <v>Badminton</v>
+        <v>H&amp;b</v>
       </c>
       <c r="D45">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-06-30</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B46" t="str">
-        <v>Provisions</v>
+        <v>Praveen - Badminton</v>
       </c>
       <c r="C46" t="str">
-        <v>Lidl - Detergent</v>
+        <v>Badminton</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-06-29</v>
+        <v>2026-06-30</v>
       </c>
       <c r="B47" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C47" t="str">
-        <v>Praveen &amp; Poornima - Cake</v>
+        <v>Lidl - Detergent</v>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-06-28</v>
+        <v>2026-06-29</v>
       </c>
       <c r="B48" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C48" t="str">
-        <v>Poornima And Praveen (tajrish Restaurant)</v>
+        <v>Praveen &amp; Poornima - Cake</v>
       </c>
       <c r="D48">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="B49" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C49" t="str">
-        <v>Lidl</v>
+        <v>Poornima And Praveen (tajrish Restaurant)</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50">
@@ -15281,10 +15281,10 @@
         <v>Groceries</v>
       </c>
       <c r="C50" t="str">
-        <v>Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -15292,13 +15292,13 @@
         <v>2026-06-27</v>
       </c>
       <c r="B51" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C51" t="str">
-        <v>Grapes, Guava, Pomegranate, Avacado</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -15306,41 +15306,41 @@
         <v>2026-06-27</v>
       </c>
       <c r="B52" t="str">
-        <v>Provisions</v>
+        <v>Fruits</v>
       </c>
       <c r="C52" t="str">
-        <v>M&amp;s</v>
+        <v>Grapes, Guava, Pomegranate, Avacado</v>
       </c>
       <c r="D52">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-27</v>
       </c>
       <c r="B53" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C53" t="str">
-        <v>Oyster</v>
+        <v>M&amp;s</v>
       </c>
       <c r="D53">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-26</v>
       </c>
       <c r="B54" t="str">
-        <v>Fan</v>
+        <v>Travel</v>
       </c>
       <c r="C54" t="str">
-        <v>Fan</v>
+        <v>Oyster</v>
       </c>
       <c r="D54">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
@@ -15348,13 +15348,13 @@
         <v>2026-06-24</v>
       </c>
       <c r="B55" t="str">
-        <v>Groceries</v>
+        <v>Fan</v>
       </c>
       <c r="C55" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Fan</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56">
@@ -15362,27 +15362,27 @@
         <v>2026-06-24</v>
       </c>
       <c r="B56" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C56" t="str">
-        <v>Yogurt, Dates, Prunes</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D56">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-06-21</v>
+        <v>2026-06-24</v>
       </c>
       <c r="B57" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C57" t="str">
-        <v>Chicken</v>
+        <v>Yogurt, Dates, Prunes</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
@@ -15393,38 +15393,38 @@
         <v>Meats</v>
       </c>
       <c r="C58" t="str">
-        <v>Fish - Salmon And Travelly</v>
+        <v>Chicken</v>
       </c>
       <c r="D58">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-06-14</v>
+        <v>2026-06-21</v>
       </c>
       <c r="B59" t="str">
-        <v>Travel</v>
+        <v>Meats</v>
       </c>
       <c r="C59" t="str">
-        <v>Flight Trd - Lhr</v>
+        <v>Fish - Salmon And Travelly</v>
       </c>
       <c r="D59">
-        <v>91</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-06-13</v>
+        <v>2026-06-14</v>
       </c>
       <c r="B60" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C60" t="str">
-        <v>Lidl &amp; Sainsbury's</v>
+        <v>Flight Trd - Lhr</v>
       </c>
       <c r="D60">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61">
@@ -15432,27 +15432,27 @@
         <v>2026-06-13</v>
       </c>
       <c r="B61" t="str">
-        <v>Belgravia</v>
+        <v>Groceries</v>
       </c>
       <c r="C61" t="str">
-        <v>Belgravia</v>
+        <v>Lidl &amp; Sainsbury's</v>
       </c>
       <c r="D61">
-        <v>186</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-06-18</v>
+        <v>2026-06-13</v>
       </c>
       <c r="B62" t="str">
-        <v>Provisions</v>
+        <v>Belgravia</v>
       </c>
       <c r="C62" t="str">
-        <v>Egg</v>
+        <v>Belgravia</v>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63">
@@ -15460,69 +15460,69 @@
         <v>2026-06-18</v>
       </c>
       <c r="B63" t="str">
-        <v>Cycle</v>
+        <v>Provisions</v>
       </c>
       <c r="C63" t="str">
-        <v>Cycle</v>
+        <v>Egg</v>
       </c>
       <c r="D63">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-18</v>
       </c>
       <c r="B64" t="str">
-        <v>Travel</v>
+        <v>Cycle</v>
       </c>
       <c r="C64" t="str">
-        <v>Lgw - Oslo</v>
+        <v>Cycle</v>
       </c>
       <c r="D64">
-        <v>168</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="B65" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C65" t="str">
-        <v>Lidl</v>
+        <v>Lgw - Oslo</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-10</v>
       </c>
       <c r="B66" t="str">
         <v>Groceries</v>
       </c>
       <c r="C66" t="str">
-        <v>Lidl And Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D66">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B67" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C67" t="str">
-        <v>Vegetables, Fruits</v>
+        <v>Lidl And Sainsbury's</v>
       </c>
       <c r="D67">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
@@ -15530,83 +15530,83 @@
         <v>2026-06-06</v>
       </c>
       <c r="B68" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C68" t="str">
-        <v>Lamb</v>
+        <v>Vegetables, Fruits</v>
       </c>
       <c r="D68">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-06-12</v>
+        <v>2026-06-06</v>
       </c>
       <c r="B69" t="str">
-        <v>Movie</v>
+        <v>Meats</v>
       </c>
       <c r="C69" t="str">
-        <v>Peddi</v>
+        <v>Lamb</v>
       </c>
       <c r="D69">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-05-31</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B70" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C70" t="str">
-        <v>Yogurt, Corn, Kefir</v>
+        <v>Peddi</v>
       </c>
       <c r="D70">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-31</v>
       </c>
       <c r="B71" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C71" t="str">
-        <v>Oyster Card</v>
+        <v>Yogurt, Corn, Kefir</v>
       </c>
       <c r="D71">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-29</v>
       </c>
       <c r="B72" t="str">
-        <v>Amazon</v>
+        <v>Travel</v>
       </c>
       <c r="C72" t="str">
-        <v>Face Wash, Moisturizer</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D72">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-28</v>
       </c>
       <c r="B73" t="str">
-        <v>Eating Out</v>
+        <v>Amazon</v>
       </c>
       <c r="C73" t="str">
-        <v>Praveen</v>
+        <v>Face Wash, Moisturizer</v>
       </c>
       <c r="D73">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74">
@@ -15614,13 +15614,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B74" t="str">
-        <v>Meats</v>
+        <v>Eating Out</v>
       </c>
       <c r="C74" t="str">
-        <v>Chicken</v>
+        <v>Praveen</v>
       </c>
       <c r="D74">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
@@ -15628,13 +15628,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B75" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C75" t="str">
-        <v>Shakto</v>
+        <v>Chicken</v>
       </c>
       <c r="D75">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -15645,24 +15645,24 @@
         <v>Groceries</v>
       </c>
       <c r="C76" t="str">
-        <v>Bread, Avacado, Lemon, Onion</v>
+        <v>Shakto</v>
       </c>
       <c r="D76">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="B77" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C77" t="str">
-        <v>Praveen Cake</v>
+        <v>Bread, Avacado, Lemon, Onion</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -15670,10 +15670,10 @@
         <v>2026-05-23</v>
       </c>
       <c r="B78" t="str">
-        <v>Fruits</v>
+        <v>Eating Out</v>
       </c>
       <c r="C78" t="str">
-        <v>Avacado, Guava</v>
+        <v>Praveen Cake</v>
       </c>
       <c r="D78">
         <v>5</v>
@@ -15684,55 +15684,55 @@
         <v>2026-05-23</v>
       </c>
       <c r="B79" t="str">
-        <v>Groceries</v>
+        <v>Fruits</v>
       </c>
       <c r="C79" t="str">
-        <v>Corn, Yogurt, Cucumber, Cake</v>
+        <v>Avacado, Guava</v>
       </c>
       <c r="D79">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="B80" t="str">
         <v>Groceries</v>
       </c>
       <c r="C80" t="str">
-        <v>Banana</v>
+        <v>Corn, Yogurt, Cucumber, Cake</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="B81" t="str">
         <v>Groceries</v>
       </c>
       <c r="C81" t="str">
-        <v>Potatoes And Dish Was Liquid</v>
+        <v>Banana</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="B82" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C82" t="str">
-        <v>Lamb</v>
+        <v>Potatoes And Dish Was Liquid</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -15740,27 +15740,27 @@
         <v>2026-05-17</v>
       </c>
       <c r="B83" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C83" t="str">
-        <v>Sainsbury's - Carrots, Onion</v>
+        <v>Lamb</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="B84" t="str">
         <v>Groceries</v>
       </c>
       <c r="C84" t="str">
-        <v>Shakti</v>
+        <v>Sainsbury's - Carrots, Onion</v>
       </c>
       <c r="D84">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -15768,55 +15768,55 @@
         <v>2026-05-16</v>
       </c>
       <c r="B85" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C85" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D85">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="B86" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C86" t="str">
-        <v>Yogurt, Vegetables</v>
+        <v>Chicken</v>
       </c>
       <c r="D86">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B87" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C87" t="str">
-        <v>Munich - Gifts To Office</v>
+        <v>Yogurt, Vegetables</v>
       </c>
       <c r="D87">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="B88" t="str">
         <v>Travel</v>
       </c>
       <c r="C88" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Gifts To Office</v>
       </c>
       <c r="D88">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
@@ -15827,10 +15827,10 @@
         <v>Travel</v>
       </c>
       <c r="C89" t="str">
-        <v>Munich - Water And Juice</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90">
@@ -15841,10 +15841,10 @@
         <v>Travel</v>
       </c>
       <c r="C90" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Water And Juice</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -15855,24 +15855,24 @@
         <v>Travel</v>
       </c>
       <c r="C91" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D91">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="B92" t="str">
         <v>Travel</v>
       </c>
       <c r="C92" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D92">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93">
@@ -15883,10 +15883,10 @@
         <v>Travel</v>
       </c>
       <c r="C93" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D93">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
@@ -15897,10 +15897,10 @@
         <v>Travel</v>
       </c>
       <c r="C94" t="str">
-        <v>Munich - Bmw Museum Ticket</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D94">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -15911,10 +15911,10 @@
         <v>Travel</v>
       </c>
       <c r="C95" t="str">
-        <v>Munich Lunch</v>
+        <v>Munich - Bmw Museum Ticket</v>
       </c>
       <c r="D95">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
@@ -15925,10 +15925,10 @@
         <v>Travel</v>
       </c>
       <c r="C96" t="str">
-        <v>Munich Walking Tour</v>
+        <v>Munich Lunch</v>
       </c>
       <c r="D96">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97">
@@ -15939,24 +15939,24 @@
         <v>Travel</v>
       </c>
       <c r="C97" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich Walking Tour</v>
       </c>
       <c r="D97">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B98" t="str">
         <v>Travel</v>
       </c>
       <c r="C98" t="str">
-        <v>Dinner - Mac And Cheese</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D98">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99">
@@ -15967,10 +15967,10 @@
         <v>Travel</v>
       </c>
       <c r="C99" t="str">
-        <v>Pretzel Snack</v>
+        <v>Dinner - Mac And Cheese</v>
       </c>
       <c r="D99">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100">
@@ -15981,10 +15981,10 @@
         <v>Travel</v>
       </c>
       <c r="C100" t="str">
-        <v>Lidl - Water, Coke, Yogurt</v>
+        <v>Pretzel Snack</v>
       </c>
       <c r="D100">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -15995,10 +15995,10 @@
         <v>Travel</v>
       </c>
       <c r="C101" t="str">
-        <v>Germany Public Transport Ticket</v>
+        <v>Lidl - Water, Coke, Yogurt</v>
       </c>
       <c r="D101">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -16006,27 +16006,27 @@
         <v>2026-05-09</v>
       </c>
       <c r="B102" t="str">
-        <v>Eating Out</v>
+        <v>Travel</v>
       </c>
       <c r="C102" t="str">
-        <v>Airport Pret</v>
+        <v>Germany Public Transport Ticket</v>
       </c>
       <c r="D102">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B103" t="str">
-        <v>Boots</v>
+        <v>Eating Out</v>
       </c>
       <c r="C103" t="str">
-        <v>Face Moisturizer</v>
+        <v>Airport Pret</v>
       </c>
       <c r="D103">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104">
@@ -16034,13 +16034,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B104" t="str">
-        <v>Provisions</v>
+        <v>Boots</v>
       </c>
       <c r="C104" t="str">
-        <v>Eggs</v>
+        <v>Face Moisturizer</v>
       </c>
       <c r="D104">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105">
@@ -16048,13 +16048,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B105" t="str">
-        <v>Shopping</v>
+        <v>Provisions</v>
       </c>
       <c r="C105" t="str">
-        <v>Belt</v>
+        <v>Eggs</v>
       </c>
       <c r="D105">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
@@ -16062,10 +16062,10 @@
         <v>2026-05-08</v>
       </c>
       <c r="B106" t="str">
-        <v>Eating Out</v>
+        <v>Shopping</v>
       </c>
       <c r="C106" t="str">
-        <v>Praveen</v>
+        <v>Belt</v>
       </c>
       <c r="D106">
         <v>7</v>
@@ -16073,30 +16073,30 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B107" t="str">
-        <v>Travel</v>
+        <v>Eating Out</v>
       </c>
       <c r="C107" t="str">
-        <v>Oyster Card</v>
+        <v>Praveen</v>
       </c>
       <c r="D107">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2026-04-18</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B108" t="str">
-        <v>Souvenir</v>
+        <v>Travel</v>
       </c>
       <c r="C108" t="str">
-        <v>Gift, Biscuits</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D108">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109">
@@ -16104,55 +16104,55 @@
         <v>2026-04-18</v>
       </c>
       <c r="B109" t="str">
-        <v>Groceries</v>
+        <v>Souvenir</v>
       </c>
       <c r="C109" t="str">
-        <v>Corn And Gauva</v>
+        <v>Gift, Biscuits</v>
       </c>
       <c r="D109">
-        <v>3.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-18</v>
       </c>
       <c r="B110" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C110" t="str">
-        <v>Oyster Card</v>
+        <v>Corn And Gauva</v>
       </c>
       <c r="D110">
-        <v>30</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>2026-03-31</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B111" t="str">
         <v>Travel</v>
       </c>
       <c r="C111" t="str">
-        <v>Total Tfl Cost</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D111">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2026-04-11</v>
+        <v>2026-03-31</v>
       </c>
       <c r="B112" t="str">
-        <v>Praveen Shoes</v>
+        <v>Travel</v>
       </c>
       <c r="C112" t="str">
-        <v>Shoes</v>
+        <v>Total Tfl Cost</v>
       </c>
       <c r="D112">
-        <v>110</v>
+        <v>67</v>
       </c>
     </row>
     <row r="113">
@@ -16160,27 +16160,27 @@
         <v>2026-04-11</v>
       </c>
       <c r="B113" t="str">
-        <v>Eating Out</v>
+        <v>Praveen Shoes</v>
       </c>
       <c r="C113" t="str">
-        <v>Spitalfield Market</v>
+        <v>Shoes</v>
       </c>
       <c r="D113">
-        <v>8</v>
+        <v>110</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="B114" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C114" t="str">
-        <v>Too Good To Go</v>
+        <v>Spitalfield Market</v>
       </c>
       <c r="D114">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115">
@@ -16188,10 +16188,10 @@
         <v>2026-04-09</v>
       </c>
       <c r="B115" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C115" t="str">
-        <v>Yogurt</v>
+        <v>Too Good To Go</v>
       </c>
       <c r="D115">
         <v>4</v>
@@ -16199,72 +16199,72 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-09</v>
       </c>
       <c r="B116" t="str">
-        <v>Visa Fee</v>
+        <v>Groceries</v>
       </c>
       <c r="C116" t="str">
-        <v>Visa Gee</v>
+        <v>Yogurt</v>
       </c>
       <c r="D116">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B117" t="str">
-        <v>Travel</v>
+        <v>Visa Fee</v>
       </c>
       <c r="C117" t="str">
-        <v>Oyster Card</v>
+        <v>Visa Gee</v>
       </c>
       <c r="D117">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B118" t="str">
-        <v>Visa Picture</v>
+        <v>Travel</v>
       </c>
       <c r="C118" t="str">
-        <v>Snappy Snap</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D118">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B119" t="str">
-        <v>Provisions</v>
+        <v>Visa Picture</v>
       </c>
       <c r="C119" t="str">
-        <v>Water Bottle</v>
+        <v>Snappy Snap</v>
       </c>
       <c r="D119">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B120" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C120" t="str">
-        <v>Poornima Roti Curry(malaysia Food)</v>
+        <v>Water Bottle</v>
       </c>
       <c r="D120">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -16272,41 +16272,41 @@
         <v>2026-04-06</v>
       </c>
       <c r="B121" t="str">
-        <v>Germany Visa Stuff</v>
+        <v>Eating Out</v>
       </c>
       <c r="C121" t="str">
-        <v>Travel Insurance, Airbnb</v>
+        <v>Poornima Roti Curry(malaysia Food)</v>
       </c>
       <c r="D121">
-        <v>111</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B122" t="str">
-        <v>Provisions</v>
+        <v>Germany Visa Stuff</v>
       </c>
       <c r="C122" t="str">
-        <v>Yogurt, Lemon</v>
+        <v>Travel Insurance, Airbnb</v>
       </c>
       <c r="D122">
-        <v>3</v>
+        <v>111</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="B123" t="str">
         <v>Provisions</v>
       </c>
       <c r="C123" t="str">
-        <v>Rice Flour, Oil,</v>
+        <v>Yogurt, Lemon</v>
       </c>
       <c r="D123">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -16314,13 +16314,13 @@
         <v>2026-04-04</v>
       </c>
       <c r="B124" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C124" t="str">
-        <v>Spinach, Ginger, Vegetable</v>
+        <v>Rice Flour, Oil,</v>
       </c>
       <c r="D124">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125">
@@ -16328,27 +16328,27 @@
         <v>2026-04-04</v>
       </c>
       <c r="B125" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C125" t="str">
-        <v>Lamb And Chicken</v>
+        <v>Spinach, Ginger, Vegetable</v>
       </c>
       <c r="D125">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-04</v>
       </c>
       <c r="B126" t="str">
-        <v>Cricket Tickets</v>
+        <v>Meats</v>
       </c>
       <c r="C126" t="str">
-        <v>Lords Women World Cup</v>
+        <v>Lamb And Chicken</v>
       </c>
       <c r="D126">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="127">
@@ -16356,27 +16356,27 @@
         <v>2026-04-02</v>
       </c>
       <c r="B127" t="str">
-        <v>Provisions</v>
+        <v>Cricket Tickets</v>
       </c>
       <c r="C127" t="str">
-        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
+        <v>Lords Women World Cup</v>
       </c>
       <c r="D127">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-02</v>
       </c>
       <c r="B128" t="str">
         <v>Provisions</v>
       </c>
       <c r="C128" t="str">
-        <v>Sainsbury's</v>
+        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
       </c>
       <c r="D128">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129">
@@ -16384,27 +16384,27 @@
         <v>2026-03-28</v>
       </c>
       <c r="B129" t="str">
-        <v>Fruits</v>
+        <v>Provisions</v>
       </c>
       <c r="C129" t="str">
-        <v>Blueberries, Avocado, Gauva</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D129">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-28</v>
       </c>
       <c r="B130" t="str">
-        <v>Movie</v>
+        <v>Fruits</v>
       </c>
       <c r="C130" t="str">
-        <v>Dhurandar</v>
+        <v>Blueberries, Avocado, Gauva</v>
       </c>
       <c r="D130">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
@@ -16412,69 +16412,69 @@
         <v>2026-03-25</v>
       </c>
       <c r="B131" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C131" t="str">
-        <v>Yogurt</v>
+        <v>Dhurandar</v>
       </c>
       <c r="D131">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-25</v>
       </c>
       <c r="B132" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C132" t="str">
-        <v>Pizza Pilgrims</v>
+        <v>Yogurt</v>
       </c>
       <c r="D132">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="B133" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C133" t="str">
-        <v>Milk, Yogurt, Flowers, Butter</v>
+        <v>Pizza Pilgrims</v>
       </c>
       <c r="D133">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="B134" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C134" t="str">
-        <v>Praveen</v>
+        <v>Milk, Yogurt, Flowers, Butter</v>
       </c>
       <c r="D134">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-17</v>
       </c>
       <c r="B135" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C135" t="str">
-        <v>Provisions</v>
+        <v>Praveen</v>
       </c>
       <c r="D135">
-        <v>59</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
@@ -16482,27 +16482,27 @@
         <v>2026-03-15</v>
       </c>
       <c r="B136" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C136" t="str">
-        <v>Vegetables</v>
+        <v>Provisions</v>
       </c>
       <c r="D136">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-15</v>
       </c>
       <c r="B137" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C137" t="str">
-        <v>Gauva, Blueberries</v>
+        <v>Vegetables</v>
       </c>
       <c r="D137">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="138">
@@ -16510,13 +16510,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B138" t="str">
-        <v>Eating Out</v>
+        <v>Fruits</v>
       </c>
       <c r="C138" t="str">
-        <v>Haleem And Samosa</v>
+        <v>Gauva, Blueberries</v>
       </c>
       <c r="D138">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
@@ -16524,13 +16524,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B139" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C139" t="str">
-        <v>Frozen Lotus Stem And Beans</v>
+        <v>Haleem And Samosa</v>
       </c>
       <c r="D139">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140">
@@ -16538,13 +16538,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B140" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C140" t="str">
-        <v>Vegetables</v>
+        <v>Frozen Lotus Stem And Beans</v>
       </c>
       <c r="D140">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141">
@@ -16552,27 +16552,27 @@
         <v>2026-03-14</v>
       </c>
       <c r="B141" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C141" t="str">
-        <v>Lidl</v>
+        <v>Vegetables</v>
       </c>
       <c r="D141">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-14</v>
       </c>
       <c r="B142" t="str">
-        <v>Medication</v>
+        <v>Provisions</v>
       </c>
       <c r="C142" t="str">
-        <v>Fish Oil, Pregnacare</v>
+        <v>Lidl</v>
       </c>
       <c r="D142">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143">
@@ -16580,69 +16580,69 @@
         <v>2026-03-09</v>
       </c>
       <c r="B143" t="str">
-        <v>Provisions</v>
+        <v>Medication</v>
       </c>
       <c r="C143" t="str">
-        <v>Yogurt, Oats, Sourdough, Detergent</v>
+        <v>Fish Oil, Pregnacare</v>
       </c>
       <c r="D143">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="B144" t="str">
-        <v>Washing</v>
+        <v>Provisions</v>
       </c>
       <c r="C144" t="str">
-        <v>Clothes</v>
+        <v>Yogurt, Oats, Sourdough, Detergent</v>
       </c>
       <c r="D144">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-08</v>
       </c>
       <c r="B145" t="str">
-        <v>Praveen</v>
+        <v>Washing</v>
       </c>
       <c r="C145" t="str">
-        <v>Praveen eating out</v>
+        <v>Clothes</v>
       </c>
       <c r="D145">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="B146" t="str">
-        <v>Meats</v>
+        <v>Praveen</v>
       </c>
       <c r="C146" t="str">
-        <v>Chicken and Fish</v>
+        <v>Praveen eating out</v>
       </c>
       <c r="D146">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-01</v>
       </c>
       <c r="B147" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C147" t="str">
-        <v>Vegetables</v>
+        <v>Chicken and Fish</v>
       </c>
       <c r="D147">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="148">
@@ -16650,32 +16650,46 @@
         <v>2026-03-07</v>
       </c>
       <c r="B148" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C148" t="str">
-        <v>Mobos Ethiopian Restaurant</v>
+        <v>Vegetables</v>
       </c>
       <c r="D148">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Eating Out</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Mobos Ethiopian Restaurant</v>
+      </c>
+      <c r="D149">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
         <v>2026-03-06</v>
       </c>
-      <c r="B149" t="str">
+      <c r="B150" t="str">
         <v>Provisions</v>
       </c>
-      <c r="C149" t="str">
+      <c r="C150" t="str">
         <v>Milk and Doritos</v>
       </c>
-      <c r="D149">
+      <c r="D150">
         <v>2.95</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D149"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D150"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -14579,7 +14579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D151"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -14606,41 +14606,41 @@
         <v>2026-08-29</v>
       </c>
       <c r="B2" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C2" t="str">
-        <v>Shakti</v>
+        <v>Chicken</v>
       </c>
       <c r="D2">
-        <v>66</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-28</v>
+        <v>2026-08-29</v>
       </c>
       <c r="B3" t="str">
-        <v>Badminton</v>
+        <v>Groceries</v>
       </c>
       <c r="C3" t="str">
-        <v>Badminton</v>
+        <v>Shakti</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-08-25</v>
+        <v>2026-08-28</v>
       </c>
       <c r="B4" t="str">
-        <v>Eating Out</v>
+        <v>Badminton</v>
       </c>
       <c r="C4" t="str">
-        <v>Deliveroo</v>
+        <v>Badminton</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -14648,41 +14648,41 @@
         <v>2026-08-25</v>
       </c>
       <c r="B5" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C5" t="str">
-        <v>Sainsbury's , Tesco</v>
+        <v>Deliveroo</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-25</v>
       </c>
       <c r="B6" t="str">
-        <v>Bike Tyre</v>
+        <v>Groceries</v>
       </c>
       <c r="C6" t="str">
-        <v>Bike Tube And Tyre</v>
+        <v>Sainsbury's , Tesco</v>
       </c>
       <c r="D6">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
       <c r="B7" t="str">
-        <v>Badminton</v>
+        <v>Bike Tyre</v>
       </c>
       <c r="C7" t="str">
-        <v>Badminton</v>
+        <v>Bike Tube And Tyre</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -14690,13 +14690,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B8" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C8" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -14704,13 +14704,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B9" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C9" t="str">
-        <v>Lidl - Prawns , Kefir And Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -14721,38 +14721,38 @@
         <v>Groceries</v>
       </c>
       <c r="C10" t="str">
-        <v>Fruits For Lakshmi Pooja</v>
+        <v>Lidl - Prawns , Kefir And Yogurt</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-21</v>
       </c>
       <c r="B11" t="str">
-        <v>Movie</v>
+        <v>Groceries</v>
       </c>
       <c r="C11" t="str">
-        <v>Toxic</v>
+        <v>Fruits For Lakshmi Pooja</v>
       </c>
       <c r="D11">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-08-15</v>
+        <v>2026-08-18</v>
       </c>
       <c r="B12" t="str">
-        <v>Groceries</v>
+        <v>Movie</v>
       </c>
       <c r="C12" t="str">
-        <v>Sainsbury's And Lidl</v>
+        <v>Toxic</v>
       </c>
       <c r="D12">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -14760,13 +14760,13 @@
         <v>2026-08-15</v>
       </c>
       <c r="B13" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C13" t="str">
-        <v>Fruit</v>
+        <v>Sainsbury's And Lidl</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -14774,27 +14774,27 @@
         <v>2026-08-15</v>
       </c>
       <c r="B14" t="str">
-        <v>Meats</v>
+        <v>Fruits</v>
       </c>
       <c r="C14" t="str">
-        <v>Lamb, Samosa, Chicken Keema</v>
+        <v>Fruit</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-15</v>
       </c>
       <c r="B15" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C15" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Lamb, Samosa, Chicken Keema</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -14802,125 +14802,125 @@
         <v>2026-08-14</v>
       </c>
       <c r="B16" t="str">
-        <v>Badminton</v>
+        <v>Groceries</v>
       </c>
       <c r="C16" t="str">
-        <v>Badminton</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D16">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-14</v>
       </c>
       <c r="B17" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C17" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D17">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-10</v>
       </c>
       <c r="B18" t="str">
-        <v>Badminton</v>
+        <v>Travel</v>
       </c>
       <c r="C18" t="str">
-        <v>Badminton</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D18">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B19" t="str">
-        <v>Groceries</v>
+        <v>Badminton</v>
       </c>
       <c r="C19" t="str">
-        <v>Yogurt And Cheese</v>
+        <v>Badminton</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-08-04</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B20" t="str">
         <v>Groceries</v>
       </c>
       <c r="C20" t="str">
-        <v>Cucumber, Tissues, Corn Flour</v>
+        <v>Yogurt And Cheese</v>
       </c>
       <c r="D20">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-04</v>
       </c>
       <c r="B21" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C21" t="str">
-        <v>Oyster Card</v>
+        <v>Cucumber, Tissues, Corn Flour</v>
       </c>
       <c r="D21">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-28</v>
       </c>
       <c r="B22" t="str">
-        <v>Provisions</v>
+        <v>Travel</v>
       </c>
       <c r="C22" t="str">
-        <v>Egg, Office Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-27</v>
       </c>
       <c r="B23" t="str">
         <v>Provisions</v>
       </c>
       <c r="C23" t="str">
-        <v>Lidl- Yogurt</v>
+        <v>Egg, Office Yogurt</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-30</v>
       </c>
       <c r="B24" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C24" t="str">
-        <v>Praveen - Boba Tea</v>
+        <v>Lidl- Yogurt</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -14928,27 +14928,27 @@
         <v>2026-07-25</v>
       </c>
       <c r="B25" t="str">
-        <v>Abdul Son Marriage Gift</v>
+        <v>Eating Out</v>
       </c>
       <c r="C25" t="str">
-        <v>Gift</v>
+        <v>Praveen - Boba Tea</v>
       </c>
       <c r="D25">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-07-26</v>
+        <v>2026-07-25</v>
       </c>
       <c r="B26" t="str">
-        <v>Badminton</v>
+        <v>Abdul Son Marriage Gift</v>
       </c>
       <c r="C26" t="str">
-        <v>Badminton</v>
+        <v>Gift</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
@@ -14956,27 +14956,27 @@
         <v>2026-07-26</v>
       </c>
       <c r="B27" t="str">
-        <v>House</v>
+        <v>Badminton</v>
       </c>
       <c r="C27" t="str">
-        <v>Houzecheck - House Evaluation</v>
+        <v>Badminton</v>
       </c>
       <c r="D27">
-        <v>593</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-26</v>
       </c>
       <c r="B28" t="str">
-        <v>Travel</v>
+        <v>House</v>
       </c>
       <c r="C28" t="str">
-        <v>Norway - H&amp;m - Pau Baby Dress</v>
+        <v>Houzecheck - House Evaluation</v>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>593</v>
       </c>
     </row>
     <row r="29">
@@ -14987,7 +14987,7 @@
         <v>Travel</v>
       </c>
       <c r="C29" t="str">
-        <v>Norway - Bus Pass</v>
+        <v>Norway - H&amp;m - Pau Baby Dress</v>
       </c>
       <c r="D29">
         <v>12</v>
@@ -14995,58 +14995,58 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B30" t="str">
         <v>Travel</v>
       </c>
       <c r="C30" t="str">
-        <v>Norway - Radical Storage Oslo</v>
+        <v>Norway - Bus Pass</v>
       </c>
       <c r="D30">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B31" t="str">
         <v>Travel</v>
       </c>
       <c r="C31" t="str">
-        <v>Oyster Card</v>
+        <v>Norway - Radical Storage Oslo</v>
       </c>
       <c r="D31">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B32" t="str">
-        <v>Norway</v>
+        <v>Travel</v>
       </c>
       <c r="C32" t="str">
-        <v>Travel Insurance</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D32">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B33" t="str">
         <v>Norway</v>
       </c>
       <c r="C33" t="str">
-        <v>Chocolate</v>
+        <v>Travel Insurance</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -15054,27 +15054,27 @@
         <v>2026-07-13</v>
       </c>
       <c r="B34" t="str">
-        <v>House</v>
+        <v>Norway</v>
       </c>
       <c r="C34" t="str">
-        <v>Leadenhall</v>
+        <v>Chocolate</v>
       </c>
       <c r="D34">
-        <v>820</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B35" t="str">
-        <v>Provisions</v>
+        <v>House</v>
       </c>
       <c r="C35" t="str">
-        <v>Yogurt</v>
+        <v>Leadenhall</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>820</v>
       </c>
     </row>
     <row r="36">
@@ -15082,13 +15082,13 @@
         <v>2026-07-11</v>
       </c>
       <c r="B36" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C36" t="str">
-        <v>Amarino Ice Cream</v>
+        <v>Yogurt</v>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -15096,55 +15096,55 @@
         <v>2026-07-11</v>
       </c>
       <c r="B37" t="str">
-        <v>Gifts To Norway</v>
+        <v>Eating Out</v>
       </c>
       <c r="C37" t="str">
-        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
+        <v>Amarino Ice Cream</v>
       </c>
       <c r="D37">
-        <v>97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B38" t="str">
-        <v>Praveen</v>
+        <v>Gifts To Norway</v>
       </c>
       <c r="C38" t="str">
-        <v>Badminton</v>
+        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B39" t="str">
-        <v>Travel</v>
+        <v>Praveen</v>
       </c>
       <c r="C39" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D39">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B40" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C40" t="str">
-        <v>Shakti</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D40">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
@@ -15152,13 +15152,13 @@
         <v>2026-07-05</v>
       </c>
       <c r="B41" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C41" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D41">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
@@ -15166,41 +15166,41 @@
         <v>2026-07-05</v>
       </c>
       <c r="B42" t="str">
-        <v>Haircut</v>
+        <v>Meats</v>
       </c>
       <c r="C42" t="str">
-        <v>Haircut</v>
+        <v>Chicken</v>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B43" t="str">
-        <v>Provisions</v>
+        <v>Haircut</v>
       </c>
       <c r="C43" t="str">
-        <v>Lidl, Sainsbury's, Iceland</v>
+        <v>Haircut</v>
       </c>
       <c r="D43">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B44" t="str">
-        <v>Superdrug</v>
+        <v>Provisions</v>
       </c>
       <c r="C44" t="str">
-        <v>Shoes Deodorant</v>
+        <v>Lidl, Sainsbury's, Iceland</v>
       </c>
       <c r="D44">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45">
@@ -15208,83 +15208,83 @@
         <v>2026-07-04</v>
       </c>
       <c r="B45" t="str">
-        <v>Medicine</v>
+        <v>Superdrug</v>
       </c>
       <c r="C45" t="str">
-        <v>H&amp;b</v>
+        <v>Shoes Deodorant</v>
       </c>
       <c r="D45">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B46" t="str">
-        <v>Praveen - Badminton</v>
+        <v>Medicine</v>
       </c>
       <c r="C46" t="str">
-        <v>Badminton</v>
+        <v>H&amp;b</v>
       </c>
       <c r="D46">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-06-30</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B47" t="str">
-        <v>Provisions</v>
+        <v>Praveen - Badminton</v>
       </c>
       <c r="C47" t="str">
-        <v>Lidl - Detergent</v>
+        <v>Badminton</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-06-29</v>
+        <v>2026-06-30</v>
       </c>
       <c r="B48" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C48" t="str">
-        <v>Praveen &amp; Poornima - Cake</v>
+        <v>Lidl - Detergent</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-06-28</v>
+        <v>2026-06-29</v>
       </c>
       <c r="B49" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C49" t="str">
-        <v>Poornima And Praveen (tajrish Restaurant)</v>
+        <v>Praveen &amp; Poornima - Cake</v>
       </c>
       <c r="D49">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="B50" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C50" t="str">
-        <v>Lidl</v>
+        <v>Poornima And Praveen (tajrish Restaurant)</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
@@ -15295,10 +15295,10 @@
         <v>Groceries</v>
       </c>
       <c r="C51" t="str">
-        <v>Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D51">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -15306,13 +15306,13 @@
         <v>2026-06-27</v>
       </c>
       <c r="B52" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C52" t="str">
-        <v>Grapes, Guava, Pomegranate, Avacado</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D52">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -15320,41 +15320,41 @@
         <v>2026-06-27</v>
       </c>
       <c r="B53" t="str">
-        <v>Provisions</v>
+        <v>Fruits</v>
       </c>
       <c r="C53" t="str">
-        <v>M&amp;s</v>
+        <v>Grapes, Guava, Pomegranate, Avacado</v>
       </c>
       <c r="D53">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-27</v>
       </c>
       <c r="B54" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C54" t="str">
-        <v>Oyster</v>
+        <v>M&amp;s</v>
       </c>
       <c r="D54">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-26</v>
       </c>
       <c r="B55" t="str">
-        <v>Fan</v>
+        <v>Travel</v>
       </c>
       <c r="C55" t="str">
-        <v>Fan</v>
+        <v>Oyster</v>
       </c>
       <c r="D55">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
@@ -15362,13 +15362,13 @@
         <v>2026-06-24</v>
       </c>
       <c r="B56" t="str">
-        <v>Groceries</v>
+        <v>Fan</v>
       </c>
       <c r="C56" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Fan</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -15376,27 +15376,27 @@
         <v>2026-06-24</v>
       </c>
       <c r="B57" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C57" t="str">
-        <v>Yogurt, Dates, Prunes</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D57">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-06-21</v>
+        <v>2026-06-24</v>
       </c>
       <c r="B58" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C58" t="str">
-        <v>Chicken</v>
+        <v>Yogurt, Dates, Prunes</v>
       </c>
       <c r="D58">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -15407,38 +15407,38 @@
         <v>Meats</v>
       </c>
       <c r="C59" t="str">
-        <v>Fish - Salmon And Travelly</v>
+        <v>Chicken</v>
       </c>
       <c r="D59">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-06-14</v>
+        <v>2026-06-21</v>
       </c>
       <c r="B60" t="str">
-        <v>Travel</v>
+        <v>Meats</v>
       </c>
       <c r="C60" t="str">
-        <v>Flight Trd - Lhr</v>
+        <v>Fish - Salmon And Travelly</v>
       </c>
       <c r="D60">
-        <v>91</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-06-13</v>
+        <v>2026-06-14</v>
       </c>
       <c r="B61" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C61" t="str">
-        <v>Lidl &amp; Sainsbury's</v>
+        <v>Flight Trd - Lhr</v>
       </c>
       <c r="D61">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62">
@@ -15446,27 +15446,27 @@
         <v>2026-06-13</v>
       </c>
       <c r="B62" t="str">
-        <v>Belgravia</v>
+        <v>Groceries</v>
       </c>
       <c r="C62" t="str">
-        <v>Belgravia</v>
+        <v>Lidl &amp; Sainsbury's</v>
       </c>
       <c r="D62">
-        <v>186</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-06-18</v>
+        <v>2026-06-13</v>
       </c>
       <c r="B63" t="str">
-        <v>Provisions</v>
+        <v>Belgravia</v>
       </c>
       <c r="C63" t="str">
-        <v>Egg</v>
+        <v>Belgravia</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64">
@@ -15474,69 +15474,69 @@
         <v>2026-06-18</v>
       </c>
       <c r="B64" t="str">
-        <v>Cycle</v>
+        <v>Provisions</v>
       </c>
       <c r="C64" t="str">
-        <v>Cycle</v>
+        <v>Egg</v>
       </c>
       <c r="D64">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-18</v>
       </c>
       <c r="B65" t="str">
-        <v>Travel</v>
+        <v>Cycle</v>
       </c>
       <c r="C65" t="str">
-        <v>Lgw - Oslo</v>
+        <v>Cycle</v>
       </c>
       <c r="D65">
-        <v>168</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="B66" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C66" t="str">
-        <v>Lidl</v>
+        <v>Lgw - Oslo</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>168</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-10</v>
       </c>
       <c r="B67" t="str">
         <v>Groceries</v>
       </c>
       <c r="C67" t="str">
-        <v>Lidl And Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D67">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B68" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C68" t="str">
-        <v>Vegetables, Fruits</v>
+        <v>Lidl And Sainsbury's</v>
       </c>
       <c r="D68">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
@@ -15544,83 +15544,83 @@
         <v>2026-06-06</v>
       </c>
       <c r="B69" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C69" t="str">
-        <v>Lamb</v>
+        <v>Vegetables, Fruits</v>
       </c>
       <c r="D69">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-06-12</v>
+        <v>2026-06-06</v>
       </c>
       <c r="B70" t="str">
-        <v>Movie</v>
+        <v>Meats</v>
       </c>
       <c r="C70" t="str">
-        <v>Peddi</v>
+        <v>Lamb</v>
       </c>
       <c r="D70">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-05-31</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B71" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C71" t="str">
-        <v>Yogurt, Corn, Kefir</v>
+        <v>Peddi</v>
       </c>
       <c r="D71">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-31</v>
       </c>
       <c r="B72" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C72" t="str">
-        <v>Oyster Card</v>
+        <v>Yogurt, Corn, Kefir</v>
       </c>
       <c r="D72">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-29</v>
       </c>
       <c r="B73" t="str">
-        <v>Amazon</v>
+        <v>Travel</v>
       </c>
       <c r="C73" t="str">
-        <v>Face Wash, Moisturizer</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D73">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-28</v>
       </c>
       <c r="B74" t="str">
-        <v>Eating Out</v>
+        <v>Amazon</v>
       </c>
       <c r="C74" t="str">
-        <v>Praveen</v>
+        <v>Face Wash, Moisturizer</v>
       </c>
       <c r="D74">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75">
@@ -15628,13 +15628,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B75" t="str">
-        <v>Meats</v>
+        <v>Eating Out</v>
       </c>
       <c r="C75" t="str">
-        <v>Chicken</v>
+        <v>Praveen</v>
       </c>
       <c r="D75">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76">
@@ -15642,13 +15642,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B76" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C76" t="str">
-        <v>Shakto</v>
+        <v>Chicken</v>
       </c>
       <c r="D76">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -15659,24 +15659,24 @@
         <v>Groceries</v>
       </c>
       <c r="C77" t="str">
-        <v>Bread, Avacado, Lemon, Onion</v>
+        <v>Shakto</v>
       </c>
       <c r="D77">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="B78" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C78" t="str">
-        <v>Praveen Cake</v>
+        <v>Bread, Avacado, Lemon, Onion</v>
       </c>
       <c r="D78">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -15684,10 +15684,10 @@
         <v>2026-05-23</v>
       </c>
       <c r="B79" t="str">
-        <v>Fruits</v>
+        <v>Eating Out</v>
       </c>
       <c r="C79" t="str">
-        <v>Avacado, Guava</v>
+        <v>Praveen Cake</v>
       </c>
       <c r="D79">
         <v>5</v>
@@ -15698,55 +15698,55 @@
         <v>2026-05-23</v>
       </c>
       <c r="B80" t="str">
-        <v>Groceries</v>
+        <v>Fruits</v>
       </c>
       <c r="C80" t="str">
-        <v>Corn, Yogurt, Cucumber, Cake</v>
+        <v>Avacado, Guava</v>
       </c>
       <c r="D80">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="B81" t="str">
         <v>Groceries</v>
       </c>
       <c r="C81" t="str">
-        <v>Banana</v>
+        <v>Corn, Yogurt, Cucumber, Cake</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="B82" t="str">
         <v>Groceries</v>
       </c>
       <c r="C82" t="str">
-        <v>Potatoes And Dish Was Liquid</v>
+        <v>Banana</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="B83" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C83" t="str">
-        <v>Lamb</v>
+        <v>Potatoes And Dish Was Liquid</v>
       </c>
       <c r="D83">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -15754,27 +15754,27 @@
         <v>2026-05-17</v>
       </c>
       <c r="B84" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C84" t="str">
-        <v>Sainsbury's - Carrots, Onion</v>
+        <v>Lamb</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="B85" t="str">
         <v>Groceries</v>
       </c>
       <c r="C85" t="str">
-        <v>Shakti</v>
+        <v>Sainsbury's - Carrots, Onion</v>
       </c>
       <c r="D85">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -15782,55 +15782,55 @@
         <v>2026-05-16</v>
       </c>
       <c r="B86" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C86" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D86">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="B87" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C87" t="str">
-        <v>Yogurt, Vegetables</v>
+        <v>Chicken</v>
       </c>
       <c r="D87">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B88" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C88" t="str">
-        <v>Munich - Gifts To Office</v>
+        <v>Yogurt, Vegetables</v>
       </c>
       <c r="D88">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="B89" t="str">
         <v>Travel</v>
       </c>
       <c r="C89" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Gifts To Office</v>
       </c>
       <c r="D89">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
@@ -15841,10 +15841,10 @@
         <v>Travel</v>
       </c>
       <c r="C90" t="str">
-        <v>Munich - Water And Juice</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D90">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91">
@@ -15855,10 +15855,10 @@
         <v>Travel</v>
       </c>
       <c r="C91" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Water And Juice</v>
       </c>
       <c r="D91">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -15869,24 +15869,24 @@
         <v>Travel</v>
       </c>
       <c r="C92" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D92">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="B93" t="str">
         <v>Travel</v>
       </c>
       <c r="C93" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D93">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94">
@@ -15897,10 +15897,10 @@
         <v>Travel</v>
       </c>
       <c r="C94" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D94">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95">
@@ -15911,10 +15911,10 @@
         <v>Travel</v>
       </c>
       <c r="C95" t="str">
-        <v>Munich - Bmw Museum Ticket</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D95">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -15925,10 +15925,10 @@
         <v>Travel</v>
       </c>
       <c r="C96" t="str">
-        <v>Munich Lunch</v>
+        <v>Munich - Bmw Museum Ticket</v>
       </c>
       <c r="D96">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -15939,10 +15939,10 @@
         <v>Travel</v>
       </c>
       <c r="C97" t="str">
-        <v>Munich Walking Tour</v>
+        <v>Munich Lunch</v>
       </c>
       <c r="D97">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98">
@@ -15953,24 +15953,24 @@
         <v>Travel</v>
       </c>
       <c r="C98" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich Walking Tour</v>
       </c>
       <c r="D98">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B99" t="str">
         <v>Travel</v>
       </c>
       <c r="C99" t="str">
-        <v>Dinner - Mac And Cheese</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D99">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">
@@ -15981,10 +15981,10 @@
         <v>Travel</v>
       </c>
       <c r="C100" t="str">
-        <v>Pretzel Snack</v>
+        <v>Dinner - Mac And Cheese</v>
       </c>
       <c r="D100">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101">
@@ -15995,10 +15995,10 @@
         <v>Travel</v>
       </c>
       <c r="C101" t="str">
-        <v>Lidl - Water, Coke, Yogurt</v>
+        <v>Pretzel Snack</v>
       </c>
       <c r="D101">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -16009,10 +16009,10 @@
         <v>Travel</v>
       </c>
       <c r="C102" t="str">
-        <v>Germany Public Transport Ticket</v>
+        <v>Lidl - Water, Coke, Yogurt</v>
       </c>
       <c r="D102">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -16020,27 +16020,27 @@
         <v>2026-05-09</v>
       </c>
       <c r="B103" t="str">
-        <v>Eating Out</v>
+        <v>Travel</v>
       </c>
       <c r="C103" t="str">
-        <v>Airport Pret</v>
+        <v>Germany Public Transport Ticket</v>
       </c>
       <c r="D103">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B104" t="str">
-        <v>Boots</v>
+        <v>Eating Out</v>
       </c>
       <c r="C104" t="str">
-        <v>Face Moisturizer</v>
+        <v>Airport Pret</v>
       </c>
       <c r="D104">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">
@@ -16048,13 +16048,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B105" t="str">
-        <v>Provisions</v>
+        <v>Boots</v>
       </c>
       <c r="C105" t="str">
-        <v>Eggs</v>
+        <v>Face Moisturizer</v>
       </c>
       <c r="D105">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106">
@@ -16062,13 +16062,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B106" t="str">
-        <v>Shopping</v>
+        <v>Provisions</v>
       </c>
       <c r="C106" t="str">
-        <v>Belt</v>
+        <v>Eggs</v>
       </c>
       <c r="D106">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -16076,10 +16076,10 @@
         <v>2026-05-08</v>
       </c>
       <c r="B107" t="str">
-        <v>Eating Out</v>
+        <v>Shopping</v>
       </c>
       <c r="C107" t="str">
-        <v>Praveen</v>
+        <v>Belt</v>
       </c>
       <c r="D107">
         <v>7</v>
@@ -16087,30 +16087,30 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B108" t="str">
-        <v>Travel</v>
+        <v>Eating Out</v>
       </c>
       <c r="C108" t="str">
-        <v>Oyster Card</v>
+        <v>Praveen</v>
       </c>
       <c r="D108">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2026-04-18</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B109" t="str">
-        <v>Souvenir</v>
+        <v>Travel</v>
       </c>
       <c r="C109" t="str">
-        <v>Gift, Biscuits</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D109">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110">
@@ -16118,55 +16118,55 @@
         <v>2026-04-18</v>
       </c>
       <c r="B110" t="str">
-        <v>Groceries</v>
+        <v>Souvenir</v>
       </c>
       <c r="C110" t="str">
-        <v>Corn And Gauva</v>
+        <v>Gift, Biscuits</v>
       </c>
       <c r="D110">
-        <v>3.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-18</v>
       </c>
       <c r="B111" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C111" t="str">
-        <v>Oyster Card</v>
+        <v>Corn And Gauva</v>
       </c>
       <c r="D111">
-        <v>30</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2026-03-31</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B112" t="str">
         <v>Travel</v>
       </c>
       <c r="C112" t="str">
-        <v>Total Tfl Cost</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D112">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2026-04-11</v>
+        <v>2026-03-31</v>
       </c>
       <c r="B113" t="str">
-        <v>Praveen Shoes</v>
+        <v>Travel</v>
       </c>
       <c r="C113" t="str">
-        <v>Shoes</v>
+        <v>Total Tfl Cost</v>
       </c>
       <c r="D113">
-        <v>110</v>
+        <v>67</v>
       </c>
     </row>
     <row r="114">
@@ -16174,27 +16174,27 @@
         <v>2026-04-11</v>
       </c>
       <c r="B114" t="str">
-        <v>Eating Out</v>
+        <v>Praveen Shoes</v>
       </c>
       <c r="C114" t="str">
-        <v>Spitalfield Market</v>
+        <v>Shoes</v>
       </c>
       <c r="D114">
-        <v>8</v>
+        <v>110</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="B115" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C115" t="str">
-        <v>Too Good To Go</v>
+        <v>Spitalfield Market</v>
       </c>
       <c r="D115">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116">
@@ -16202,10 +16202,10 @@
         <v>2026-04-09</v>
       </c>
       <c r="B116" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C116" t="str">
-        <v>Yogurt</v>
+        <v>Too Good To Go</v>
       </c>
       <c r="D116">
         <v>4</v>
@@ -16213,72 +16213,72 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-09</v>
       </c>
       <c r="B117" t="str">
-        <v>Visa Fee</v>
+        <v>Groceries</v>
       </c>
       <c r="C117" t="str">
-        <v>Visa Gee</v>
+        <v>Yogurt</v>
       </c>
       <c r="D117">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B118" t="str">
-        <v>Travel</v>
+        <v>Visa Fee</v>
       </c>
       <c r="C118" t="str">
-        <v>Oyster Card</v>
+        <v>Visa Gee</v>
       </c>
       <c r="D118">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B119" t="str">
-        <v>Visa Picture</v>
+        <v>Travel</v>
       </c>
       <c r="C119" t="str">
-        <v>Snappy Snap</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D119">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B120" t="str">
-        <v>Provisions</v>
+        <v>Visa Picture</v>
       </c>
       <c r="C120" t="str">
-        <v>Water Bottle</v>
+        <v>Snappy Snap</v>
       </c>
       <c r="D120">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B121" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C121" t="str">
-        <v>Poornima Roti Curry(malaysia Food)</v>
+        <v>Water Bottle</v>
       </c>
       <c r="D121">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
@@ -16286,41 +16286,41 @@
         <v>2026-04-06</v>
       </c>
       <c r="B122" t="str">
-        <v>Germany Visa Stuff</v>
+        <v>Eating Out</v>
       </c>
       <c r="C122" t="str">
-        <v>Travel Insurance, Airbnb</v>
+        <v>Poornima Roti Curry(malaysia Food)</v>
       </c>
       <c r="D122">
-        <v>111</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B123" t="str">
-        <v>Provisions</v>
+        <v>Germany Visa Stuff</v>
       </c>
       <c r="C123" t="str">
-        <v>Yogurt, Lemon</v>
+        <v>Travel Insurance, Airbnb</v>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>111</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="B124" t="str">
         <v>Provisions</v>
       </c>
       <c r="C124" t="str">
-        <v>Rice Flour, Oil,</v>
+        <v>Yogurt, Lemon</v>
       </c>
       <c r="D124">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
@@ -16328,13 +16328,13 @@
         <v>2026-04-04</v>
       </c>
       <c r="B125" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C125" t="str">
-        <v>Spinach, Ginger, Vegetable</v>
+        <v>Rice Flour, Oil,</v>
       </c>
       <c r="D125">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126">
@@ -16342,27 +16342,27 @@
         <v>2026-04-04</v>
       </c>
       <c r="B126" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C126" t="str">
-        <v>Lamb And Chicken</v>
+        <v>Spinach, Ginger, Vegetable</v>
       </c>
       <c r="D126">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-04</v>
       </c>
       <c r="B127" t="str">
-        <v>Cricket Tickets</v>
+        <v>Meats</v>
       </c>
       <c r="C127" t="str">
-        <v>Lords Women World Cup</v>
+        <v>Lamb And Chicken</v>
       </c>
       <c r="D127">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128">
@@ -16370,27 +16370,27 @@
         <v>2026-04-02</v>
       </c>
       <c r="B128" t="str">
-        <v>Provisions</v>
+        <v>Cricket Tickets</v>
       </c>
       <c r="C128" t="str">
-        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
+        <v>Lords Women World Cup</v>
       </c>
       <c r="D128">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-02</v>
       </c>
       <c r="B129" t="str">
         <v>Provisions</v>
       </c>
       <c r="C129" t="str">
-        <v>Sainsbury's</v>
+        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
       </c>
       <c r="D129">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130">
@@ -16398,27 +16398,27 @@
         <v>2026-03-28</v>
       </c>
       <c r="B130" t="str">
-        <v>Fruits</v>
+        <v>Provisions</v>
       </c>
       <c r="C130" t="str">
-        <v>Blueberries, Avocado, Gauva</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D130">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-28</v>
       </c>
       <c r="B131" t="str">
-        <v>Movie</v>
+        <v>Fruits</v>
       </c>
       <c r="C131" t="str">
-        <v>Dhurandar</v>
+        <v>Blueberries, Avocado, Gauva</v>
       </c>
       <c r="D131">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
@@ -16426,69 +16426,69 @@
         <v>2026-03-25</v>
       </c>
       <c r="B132" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C132" t="str">
-        <v>Yogurt</v>
+        <v>Dhurandar</v>
       </c>
       <c r="D132">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-25</v>
       </c>
       <c r="B133" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C133" t="str">
-        <v>Pizza Pilgrims</v>
+        <v>Yogurt</v>
       </c>
       <c r="D133">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="B134" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C134" t="str">
-        <v>Milk, Yogurt, Flowers, Butter</v>
+        <v>Pizza Pilgrims</v>
       </c>
       <c r="D134">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="B135" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C135" t="str">
-        <v>Praveen</v>
+        <v>Milk, Yogurt, Flowers, Butter</v>
       </c>
       <c r="D135">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-17</v>
       </c>
       <c r="B136" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C136" t="str">
-        <v>Provisions</v>
+        <v>Praveen</v>
       </c>
       <c r="D136">
-        <v>59</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
@@ -16496,27 +16496,27 @@
         <v>2026-03-15</v>
       </c>
       <c r="B137" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C137" t="str">
-        <v>Vegetables</v>
+        <v>Provisions</v>
       </c>
       <c r="D137">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-15</v>
       </c>
       <c r="B138" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C138" t="str">
-        <v>Gauva, Blueberries</v>
+        <v>Vegetables</v>
       </c>
       <c r="D138">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="139">
@@ -16524,13 +16524,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B139" t="str">
-        <v>Eating Out</v>
+        <v>Fruits</v>
       </c>
       <c r="C139" t="str">
-        <v>Haleem And Samosa</v>
+        <v>Gauva, Blueberries</v>
       </c>
       <c r="D139">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
@@ -16538,13 +16538,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B140" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C140" t="str">
-        <v>Frozen Lotus Stem And Beans</v>
+        <v>Haleem And Samosa</v>
       </c>
       <c r="D140">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141">
@@ -16552,13 +16552,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B141" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C141" t="str">
-        <v>Vegetables</v>
+        <v>Frozen Lotus Stem And Beans</v>
       </c>
       <c r="D141">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
@@ -16566,27 +16566,27 @@
         <v>2026-03-14</v>
       </c>
       <c r="B142" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C142" t="str">
-        <v>Lidl</v>
+        <v>Vegetables</v>
       </c>
       <c r="D142">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-14</v>
       </c>
       <c r="B143" t="str">
-        <v>Medication</v>
+        <v>Provisions</v>
       </c>
       <c r="C143" t="str">
-        <v>Fish Oil, Pregnacare</v>
+        <v>Lidl</v>
       </c>
       <c r="D143">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144">
@@ -16594,69 +16594,69 @@
         <v>2026-03-09</v>
       </c>
       <c r="B144" t="str">
-        <v>Provisions</v>
+        <v>Medication</v>
       </c>
       <c r="C144" t="str">
-        <v>Yogurt, Oats, Sourdough, Detergent</v>
+        <v>Fish Oil, Pregnacare</v>
       </c>
       <c r="D144">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="B145" t="str">
-        <v>Washing</v>
+        <v>Provisions</v>
       </c>
       <c r="C145" t="str">
-        <v>Clothes</v>
+        <v>Yogurt, Oats, Sourdough, Detergent</v>
       </c>
       <c r="D145">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-08</v>
       </c>
       <c r="B146" t="str">
-        <v>Praveen</v>
+        <v>Washing</v>
       </c>
       <c r="C146" t="str">
-        <v>Praveen eating out</v>
+        <v>Clothes</v>
       </c>
       <c r="D146">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="B147" t="str">
-        <v>Meats</v>
+        <v>Praveen</v>
       </c>
       <c r="C147" t="str">
-        <v>Chicken and Fish</v>
+        <v>Praveen eating out</v>
       </c>
       <c r="D147">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-01</v>
       </c>
       <c r="B148" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C148" t="str">
-        <v>Vegetables</v>
+        <v>Chicken and Fish</v>
       </c>
       <c r="D148">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="149">
@@ -16664,32 +16664,46 @@
         <v>2026-03-07</v>
       </c>
       <c r="B149" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C149" t="str">
-        <v>Mobos Ethiopian Restaurant</v>
+        <v>Vegetables</v>
       </c>
       <c r="D149">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Eating Out</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Mobos Ethiopian Restaurant</v>
+      </c>
+      <c r="D150">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
         <v>2026-03-06</v>
       </c>
-      <c r="B150" t="str">
+      <c r="B151" t="str">
         <v>Provisions</v>
       </c>
-      <c r="C150" t="str">
+      <c r="C151" t="str">
         <v>Milk and Doritos</v>
       </c>
-      <c r="D150">
+      <c r="D151">
         <v>2.95</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D150"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D151"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -14579,7 +14579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D152"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -14603,16 +14603,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-29</v>
+        <v>2026-09-02</v>
       </c>
       <c r="B2" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C2" t="str">
-        <v>Chicken</v>
+        <v>Sainsbury's And Lidl</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -14620,41 +14620,41 @@
         <v>2026-08-29</v>
       </c>
       <c r="B3" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C3" t="str">
-        <v>Shakti</v>
+        <v>Chicken</v>
       </c>
       <c r="D3">
-        <v>66</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-08-28</v>
+        <v>2026-08-29</v>
       </c>
       <c r="B4" t="str">
-        <v>Badminton</v>
+        <v>Groceries</v>
       </c>
       <c r="C4" t="str">
-        <v>Badminton</v>
+        <v>Shakti</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-08-25</v>
+        <v>2026-08-28</v>
       </c>
       <c r="B5" t="str">
-        <v>Eating Out</v>
+        <v>Badminton</v>
       </c>
       <c r="C5" t="str">
-        <v>Deliveroo</v>
+        <v>Badminton</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -14662,41 +14662,41 @@
         <v>2026-08-25</v>
       </c>
       <c r="B6" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C6" t="str">
-        <v>Sainsbury's , Tesco</v>
+        <v>Deliveroo</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-08-23</v>
+        <v>2026-08-25</v>
       </c>
       <c r="B7" t="str">
-        <v>Bike Tyre</v>
+        <v>Groceries</v>
       </c>
       <c r="C7" t="str">
-        <v>Bike Tube And Tyre</v>
+        <v>Sainsbury's , Tesco</v>
       </c>
       <c r="D7">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-23</v>
       </c>
       <c r="B8" t="str">
-        <v>Badminton</v>
+        <v>Bike Tyre</v>
       </c>
       <c r="C8" t="str">
-        <v>Badminton</v>
+        <v>Bike Tube And Tyre</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -14704,13 +14704,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B9" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C9" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -14718,13 +14718,13 @@
         <v>2026-08-21</v>
       </c>
       <c r="B10" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C10" t="str">
-        <v>Lidl - Prawns , Kefir And Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D10">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -14735,38 +14735,38 @@
         <v>Groceries</v>
       </c>
       <c r="C11" t="str">
-        <v>Fruits For Lakshmi Pooja</v>
+        <v>Lidl - Prawns , Kefir And Yogurt</v>
       </c>
       <c r="D11">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-21</v>
       </c>
       <c r="B12" t="str">
-        <v>Movie</v>
+        <v>Groceries</v>
       </c>
       <c r="C12" t="str">
-        <v>Toxic</v>
+        <v>Fruits For Lakshmi Pooja</v>
       </c>
       <c r="D12">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-08-15</v>
+        <v>2026-08-18</v>
       </c>
       <c r="B13" t="str">
-        <v>Groceries</v>
+        <v>Movie</v>
       </c>
       <c r="C13" t="str">
-        <v>Sainsbury's And Lidl</v>
+        <v>Toxic</v>
       </c>
       <c r="D13">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -14774,13 +14774,13 @@
         <v>2026-08-15</v>
       </c>
       <c r="B14" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C14" t="str">
-        <v>Fruit</v>
+        <v>Sainsbury's And Lidl</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -14788,27 +14788,27 @@
         <v>2026-08-15</v>
       </c>
       <c r="B15" t="str">
-        <v>Meats</v>
+        <v>Fruits</v>
       </c>
       <c r="C15" t="str">
-        <v>Lamb, Samosa, Chicken Keema</v>
+        <v>Fruit</v>
       </c>
       <c r="D15">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-15</v>
       </c>
       <c r="B16" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C16" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Lamb, Samosa, Chicken Keema</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -14816,125 +14816,125 @@
         <v>2026-08-14</v>
       </c>
       <c r="B17" t="str">
-        <v>Badminton</v>
+        <v>Groceries</v>
       </c>
       <c r="C17" t="str">
-        <v>Badminton</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D17">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-08-10</v>
+        <v>2026-08-14</v>
       </c>
       <c r="B18" t="str">
-        <v>Travel</v>
+        <v>Badminton</v>
       </c>
       <c r="C18" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D18">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-10</v>
       </c>
       <c r="B19" t="str">
-        <v>Badminton</v>
+        <v>Travel</v>
       </c>
       <c r="C19" t="str">
-        <v>Badminton</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D19">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-08-05</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B20" t="str">
-        <v>Groceries</v>
+        <v>Badminton</v>
       </c>
       <c r="C20" t="str">
-        <v>Yogurt And Cheese</v>
+        <v>Badminton</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-08-04</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B21" t="str">
         <v>Groceries</v>
       </c>
       <c r="C21" t="str">
-        <v>Cucumber, Tissues, Corn Flour</v>
+        <v>Yogurt And Cheese</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-04</v>
       </c>
       <c r="B22" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C22" t="str">
-        <v>Oyster Card</v>
+        <v>Cucumber, Tissues, Corn Flour</v>
       </c>
       <c r="D22">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-28</v>
       </c>
       <c r="B23" t="str">
-        <v>Provisions</v>
+        <v>Travel</v>
       </c>
       <c r="C23" t="str">
-        <v>Egg, Office Yogurt</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-27</v>
       </c>
       <c r="B24" t="str">
         <v>Provisions</v>
       </c>
       <c r="C24" t="str">
-        <v>Lidl- Yogurt</v>
+        <v>Egg, Office Yogurt</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-30</v>
       </c>
       <c r="B25" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C25" t="str">
-        <v>Praveen - Boba Tea</v>
+        <v>Lidl- Yogurt</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -14942,27 +14942,27 @@
         <v>2026-07-25</v>
       </c>
       <c r="B26" t="str">
-        <v>Abdul Son Marriage Gift</v>
+        <v>Eating Out</v>
       </c>
       <c r="C26" t="str">
-        <v>Gift</v>
+        <v>Praveen - Boba Tea</v>
       </c>
       <c r="D26">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-07-26</v>
+        <v>2026-07-25</v>
       </c>
       <c r="B27" t="str">
-        <v>Badminton</v>
+        <v>Abdul Son Marriage Gift</v>
       </c>
       <c r="C27" t="str">
-        <v>Badminton</v>
+        <v>Gift</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -14970,27 +14970,27 @@
         <v>2026-07-26</v>
       </c>
       <c r="B28" t="str">
-        <v>House</v>
+        <v>Badminton</v>
       </c>
       <c r="C28" t="str">
-        <v>Houzecheck - House Evaluation</v>
+        <v>Badminton</v>
       </c>
       <c r="D28">
-        <v>593</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-26</v>
       </c>
       <c r="B29" t="str">
-        <v>Travel</v>
+        <v>House</v>
       </c>
       <c r="C29" t="str">
-        <v>Norway - H&amp;m - Pau Baby Dress</v>
+        <v>Houzecheck - House Evaluation</v>
       </c>
       <c r="D29">
-        <v>12</v>
+        <v>593</v>
       </c>
     </row>
     <row r="30">
@@ -15001,7 +15001,7 @@
         <v>Travel</v>
       </c>
       <c r="C30" t="str">
-        <v>Norway - Bus Pass</v>
+        <v>Norway - H&amp;m - Pau Baby Dress</v>
       </c>
       <c r="D30">
         <v>12</v>
@@ -15009,58 +15009,58 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B31" t="str">
         <v>Travel</v>
       </c>
       <c r="C31" t="str">
-        <v>Norway - Radical Storage Oslo</v>
+        <v>Norway - Bus Pass</v>
       </c>
       <c r="D31">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B32" t="str">
         <v>Travel</v>
       </c>
       <c r="C32" t="str">
-        <v>Oyster Card</v>
+        <v>Norway - Radical Storage Oslo</v>
       </c>
       <c r="D32">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B33" t="str">
-        <v>Norway</v>
+        <v>Travel</v>
       </c>
       <c r="C33" t="str">
-        <v>Travel Insurance</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D33">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B34" t="str">
         <v>Norway</v>
       </c>
       <c r="C34" t="str">
-        <v>Chocolate</v>
+        <v>Travel Insurance</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
@@ -15068,27 +15068,27 @@
         <v>2026-07-13</v>
       </c>
       <c r="B35" t="str">
-        <v>House</v>
+        <v>Norway</v>
       </c>
       <c r="C35" t="str">
-        <v>Leadenhall</v>
+        <v>Chocolate</v>
       </c>
       <c r="D35">
-        <v>820</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B36" t="str">
-        <v>Provisions</v>
+        <v>House</v>
       </c>
       <c r="C36" t="str">
-        <v>Yogurt</v>
+        <v>Leadenhall</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>820</v>
       </c>
     </row>
     <row r="37">
@@ -15096,13 +15096,13 @@
         <v>2026-07-11</v>
       </c>
       <c r="B37" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C37" t="str">
-        <v>Amarino Ice Cream</v>
+        <v>Yogurt</v>
       </c>
       <c r="D37">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -15110,55 +15110,55 @@
         <v>2026-07-11</v>
       </c>
       <c r="B38" t="str">
-        <v>Gifts To Norway</v>
+        <v>Eating Out</v>
       </c>
       <c r="C38" t="str">
-        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
+        <v>Amarino Ice Cream</v>
       </c>
       <c r="D38">
-        <v>97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B39" t="str">
-        <v>Praveen</v>
+        <v>Gifts To Norway</v>
       </c>
       <c r="C39" t="str">
-        <v>Badminton</v>
+        <v>Go Outdoors, Mountain Warehouse And M&amp;s</v>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B40" t="str">
-        <v>Travel</v>
+        <v>Praveen</v>
       </c>
       <c r="C40" t="str">
-        <v>Oyster Card</v>
+        <v>Badminton</v>
       </c>
       <c r="D40">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B41" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C41" t="str">
-        <v>Shakti</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
@@ -15166,13 +15166,13 @@
         <v>2026-07-05</v>
       </c>
       <c r="B42" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C42" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D42">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -15180,41 +15180,41 @@
         <v>2026-07-05</v>
       </c>
       <c r="B43" t="str">
-        <v>Haircut</v>
+        <v>Meats</v>
       </c>
       <c r="C43" t="str">
-        <v>Haircut</v>
+        <v>Chicken</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B44" t="str">
-        <v>Provisions</v>
+        <v>Haircut</v>
       </c>
       <c r="C44" t="str">
-        <v>Lidl, Sainsbury's, Iceland</v>
+        <v>Haircut</v>
       </c>
       <c r="D44">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B45" t="str">
-        <v>Superdrug</v>
+        <v>Provisions</v>
       </c>
       <c r="C45" t="str">
-        <v>Shoes Deodorant</v>
+        <v>Lidl, Sainsbury's, Iceland</v>
       </c>
       <c r="D45">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46">
@@ -15222,83 +15222,83 @@
         <v>2026-07-04</v>
       </c>
       <c r="B46" t="str">
-        <v>Medicine</v>
+        <v>Superdrug</v>
       </c>
       <c r="C46" t="str">
-        <v>H&amp;b</v>
+        <v>Shoes Deodorant</v>
       </c>
       <c r="D46">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B47" t="str">
-        <v>Praveen - Badminton</v>
+        <v>Medicine</v>
       </c>
       <c r="C47" t="str">
-        <v>Badminton</v>
+        <v>H&amp;b</v>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-06-30</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B48" t="str">
-        <v>Provisions</v>
+        <v>Praveen - Badminton</v>
       </c>
       <c r="C48" t="str">
-        <v>Lidl - Detergent</v>
+        <v>Badminton</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-06-29</v>
+        <v>2026-06-30</v>
       </c>
       <c r="B49" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C49" t="str">
-        <v>Praveen &amp; Poornima - Cake</v>
+        <v>Lidl - Detergent</v>
       </c>
       <c r="D49">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-06-28</v>
+        <v>2026-06-29</v>
       </c>
       <c r="B50" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C50" t="str">
-        <v>Poornima And Praveen (tajrish Restaurant)</v>
+        <v>Praveen &amp; Poornima - Cake</v>
       </c>
       <c r="D50">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="B51" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C51" t="str">
-        <v>Lidl</v>
+        <v>Poornima And Praveen (tajrish Restaurant)</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52">
@@ -15309,10 +15309,10 @@
         <v>Groceries</v>
       </c>
       <c r="C52" t="str">
-        <v>Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D52">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -15320,13 +15320,13 @@
         <v>2026-06-27</v>
       </c>
       <c r="B53" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C53" t="str">
-        <v>Grapes, Guava, Pomegranate, Avacado</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D53">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -15334,41 +15334,41 @@
         <v>2026-06-27</v>
       </c>
       <c r="B54" t="str">
-        <v>Provisions</v>
+        <v>Fruits</v>
       </c>
       <c r="C54" t="str">
-        <v>M&amp;s</v>
+        <v>Grapes, Guava, Pomegranate, Avacado</v>
       </c>
       <c r="D54">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-27</v>
       </c>
       <c r="B55" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C55" t="str">
-        <v>Oyster</v>
+        <v>M&amp;s</v>
       </c>
       <c r="D55">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-26</v>
       </c>
       <c r="B56" t="str">
-        <v>Fan</v>
+        <v>Travel</v>
       </c>
       <c r="C56" t="str">
-        <v>Fan</v>
+        <v>Oyster</v>
       </c>
       <c r="D56">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57">
@@ -15376,13 +15376,13 @@
         <v>2026-06-24</v>
       </c>
       <c r="B57" t="str">
-        <v>Groceries</v>
+        <v>Fan</v>
       </c>
       <c r="C57" t="str">
-        <v>Praveen Yogurt</v>
+        <v>Fan</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
@@ -15390,27 +15390,27 @@
         <v>2026-06-24</v>
       </c>
       <c r="B58" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C58" t="str">
-        <v>Yogurt, Dates, Prunes</v>
+        <v>Praveen Yogurt</v>
       </c>
       <c r="D58">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-06-21</v>
+        <v>2026-06-24</v>
       </c>
       <c r="B59" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C59" t="str">
-        <v>Chicken</v>
+        <v>Yogurt, Dates, Prunes</v>
       </c>
       <c r="D59">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
@@ -15421,38 +15421,38 @@
         <v>Meats</v>
       </c>
       <c r="C60" t="str">
-        <v>Fish - Salmon And Travelly</v>
+        <v>Chicken</v>
       </c>
       <c r="D60">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-06-14</v>
+        <v>2026-06-21</v>
       </c>
       <c r="B61" t="str">
-        <v>Travel</v>
+        <v>Meats</v>
       </c>
       <c r="C61" t="str">
-        <v>Flight Trd - Lhr</v>
+        <v>Fish - Salmon And Travelly</v>
       </c>
       <c r="D61">
-        <v>91</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-06-13</v>
+        <v>2026-06-14</v>
       </c>
       <c r="B62" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C62" t="str">
-        <v>Lidl &amp; Sainsbury's</v>
+        <v>Flight Trd - Lhr</v>
       </c>
       <c r="D62">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63">
@@ -15460,27 +15460,27 @@
         <v>2026-06-13</v>
       </c>
       <c r="B63" t="str">
-        <v>Belgravia</v>
+        <v>Groceries</v>
       </c>
       <c r="C63" t="str">
-        <v>Belgravia</v>
+        <v>Lidl &amp; Sainsbury's</v>
       </c>
       <c r="D63">
-        <v>186</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-06-18</v>
+        <v>2026-06-13</v>
       </c>
       <c r="B64" t="str">
-        <v>Provisions</v>
+        <v>Belgravia</v>
       </c>
       <c r="C64" t="str">
-        <v>Egg</v>
+        <v>Belgravia</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65">
@@ -15488,69 +15488,69 @@
         <v>2026-06-18</v>
       </c>
       <c r="B65" t="str">
-        <v>Cycle</v>
+        <v>Provisions</v>
       </c>
       <c r="C65" t="str">
-        <v>Cycle</v>
+        <v>Egg</v>
       </c>
       <c r="D65">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-18</v>
       </c>
       <c r="B66" t="str">
-        <v>Travel</v>
+        <v>Cycle</v>
       </c>
       <c r="C66" t="str">
-        <v>Lgw - Oslo</v>
+        <v>Cycle</v>
       </c>
       <c r="D66">
-        <v>168</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="B67" t="str">
-        <v>Groceries</v>
+        <v>Travel</v>
       </c>
       <c r="C67" t="str">
-        <v>Lidl</v>
+        <v>Lgw - Oslo</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>168</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-10</v>
       </c>
       <c r="B68" t="str">
         <v>Groceries</v>
       </c>
       <c r="C68" t="str">
-        <v>Lidl And Sainsbury's</v>
+        <v>Lidl</v>
       </c>
       <c r="D68">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B69" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C69" t="str">
-        <v>Vegetables, Fruits</v>
+        <v>Lidl And Sainsbury's</v>
       </c>
       <c r="D69">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -15558,83 +15558,83 @@
         <v>2026-06-06</v>
       </c>
       <c r="B70" t="str">
-        <v>Meats</v>
+        <v>Provisions</v>
       </c>
       <c r="C70" t="str">
-        <v>Lamb</v>
+        <v>Vegetables, Fruits</v>
       </c>
       <c r="D70">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-06-12</v>
+        <v>2026-06-06</v>
       </c>
       <c r="B71" t="str">
-        <v>Movie</v>
+        <v>Meats</v>
       </c>
       <c r="C71" t="str">
-        <v>Peddi</v>
+        <v>Lamb</v>
       </c>
       <c r="D71">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-05-31</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B72" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C72" t="str">
-        <v>Yogurt, Corn, Kefir</v>
+        <v>Peddi</v>
       </c>
       <c r="D72">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-31</v>
       </c>
       <c r="B73" t="str">
-        <v>Travel</v>
+        <v>Provisions</v>
       </c>
       <c r="C73" t="str">
-        <v>Oyster Card</v>
+        <v>Yogurt, Corn, Kefir</v>
       </c>
       <c r="D73">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-29</v>
       </c>
       <c r="B74" t="str">
-        <v>Amazon</v>
+        <v>Travel</v>
       </c>
       <c r="C74" t="str">
-        <v>Face Wash, Moisturizer</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D74">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-28</v>
       </c>
       <c r="B75" t="str">
-        <v>Eating Out</v>
+        <v>Amazon</v>
       </c>
       <c r="C75" t="str">
-        <v>Praveen</v>
+        <v>Face Wash, Moisturizer</v>
       </c>
       <c r="D75">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76">
@@ -15642,13 +15642,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B76" t="str">
-        <v>Meats</v>
+        <v>Eating Out</v>
       </c>
       <c r="C76" t="str">
-        <v>Chicken</v>
+        <v>Praveen</v>
       </c>
       <c r="D76">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77">
@@ -15656,13 +15656,13 @@
         <v>2026-05-24</v>
       </c>
       <c r="B77" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C77" t="str">
-        <v>Shakto</v>
+        <v>Chicken</v>
       </c>
       <c r="D77">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -15673,24 +15673,24 @@
         <v>Groceries</v>
       </c>
       <c r="C78" t="str">
-        <v>Bread, Avacado, Lemon, Onion</v>
+        <v>Shakto</v>
       </c>
       <c r="D78">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="B79" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C79" t="str">
-        <v>Praveen Cake</v>
+        <v>Bread, Avacado, Lemon, Onion</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
@@ -15698,10 +15698,10 @@
         <v>2026-05-23</v>
       </c>
       <c r="B80" t="str">
-        <v>Fruits</v>
+        <v>Eating Out</v>
       </c>
       <c r="C80" t="str">
-        <v>Avacado, Guava</v>
+        <v>Praveen Cake</v>
       </c>
       <c r="D80">
         <v>5</v>
@@ -15712,55 +15712,55 @@
         <v>2026-05-23</v>
       </c>
       <c r="B81" t="str">
-        <v>Groceries</v>
+        <v>Fruits</v>
       </c>
       <c r="C81" t="str">
-        <v>Corn, Yogurt, Cucumber, Cake</v>
+        <v>Avacado, Guava</v>
       </c>
       <c r="D81">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="B82" t="str">
         <v>Groceries</v>
       </c>
       <c r="C82" t="str">
-        <v>Banana</v>
+        <v>Corn, Yogurt, Cucumber, Cake</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="B83" t="str">
         <v>Groceries</v>
       </c>
       <c r="C83" t="str">
-        <v>Potatoes And Dish Was Liquid</v>
+        <v>Banana</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="B84" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C84" t="str">
-        <v>Lamb</v>
+        <v>Potatoes And Dish Was Liquid</v>
       </c>
       <c r="D84">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -15768,27 +15768,27 @@
         <v>2026-05-17</v>
       </c>
       <c r="B85" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C85" t="str">
-        <v>Sainsbury's - Carrots, Onion</v>
+        <v>Lamb</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="B86" t="str">
         <v>Groceries</v>
       </c>
       <c r="C86" t="str">
-        <v>Shakti</v>
+        <v>Sainsbury's - Carrots, Onion</v>
       </c>
       <c r="D86">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -15796,55 +15796,55 @@
         <v>2026-05-16</v>
       </c>
       <c r="B87" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C87" t="str">
-        <v>Chicken</v>
+        <v>Shakti</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="B88" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C88" t="str">
-        <v>Yogurt, Vegetables</v>
+        <v>Chicken</v>
       </c>
       <c r="D88">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-14</v>
       </c>
       <c r="B89" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C89" t="str">
-        <v>Munich - Gifts To Office</v>
+        <v>Yogurt, Vegetables</v>
       </c>
       <c r="D89">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="B90" t="str">
         <v>Travel</v>
       </c>
       <c r="C90" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Gifts To Office</v>
       </c>
       <c r="D90">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
@@ -15855,10 +15855,10 @@
         <v>Travel</v>
       </c>
       <c r="C91" t="str">
-        <v>Munich - Water And Juice</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D91">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92">
@@ -15869,10 +15869,10 @@
         <v>Travel</v>
       </c>
       <c r="C92" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Water And Juice</v>
       </c>
       <c r="D92">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -15883,24 +15883,24 @@
         <v>Travel</v>
       </c>
       <c r="C93" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D93">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="B94" t="str">
         <v>Travel</v>
       </c>
       <c r="C94" t="str">
-        <v>Munich - Dinner</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D94">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95">
@@ -15911,10 +15911,10 @@
         <v>Travel</v>
       </c>
       <c r="C95" t="str">
-        <v>Munich - Snack</v>
+        <v>Munich - Dinner</v>
       </c>
       <c r="D95">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96">
@@ -15925,10 +15925,10 @@
         <v>Travel</v>
       </c>
       <c r="C96" t="str">
-        <v>Munich - Bmw Museum Ticket</v>
+        <v>Munich - Snack</v>
       </c>
       <c r="D96">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -15939,10 +15939,10 @@
         <v>Travel</v>
       </c>
       <c r="C97" t="str">
-        <v>Munich Lunch</v>
+        <v>Munich - Bmw Museum Ticket</v>
       </c>
       <c r="D97">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
@@ -15953,10 +15953,10 @@
         <v>Travel</v>
       </c>
       <c r="C98" t="str">
-        <v>Munich Walking Tour</v>
+        <v>Munich Lunch</v>
       </c>
       <c r="D98">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99">
@@ -15967,24 +15967,24 @@
         <v>Travel</v>
       </c>
       <c r="C99" t="str">
-        <v>Munich - Pass</v>
+        <v>Munich Walking Tour</v>
       </c>
       <c r="D99">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="B100" t="str">
         <v>Travel</v>
       </c>
       <c r="C100" t="str">
-        <v>Dinner - Mac And Cheese</v>
+        <v>Munich - Pass</v>
       </c>
       <c r="D100">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
@@ -15995,10 +15995,10 @@
         <v>Travel</v>
       </c>
       <c r="C101" t="str">
-        <v>Pretzel Snack</v>
+        <v>Dinner - Mac And Cheese</v>
       </c>
       <c r="D101">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102">
@@ -16009,10 +16009,10 @@
         <v>Travel</v>
       </c>
       <c r="C102" t="str">
-        <v>Lidl - Water, Coke, Yogurt</v>
+        <v>Pretzel Snack</v>
       </c>
       <c r="D102">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -16023,10 +16023,10 @@
         <v>Travel</v>
       </c>
       <c r="C103" t="str">
-        <v>Germany Public Transport Ticket</v>
+        <v>Lidl - Water, Coke, Yogurt</v>
       </c>
       <c r="D103">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -16034,27 +16034,27 @@
         <v>2026-05-09</v>
       </c>
       <c r="B104" t="str">
-        <v>Eating Out</v>
+        <v>Travel</v>
       </c>
       <c r="C104" t="str">
-        <v>Airport Pret</v>
+        <v>Germany Public Transport Ticket</v>
       </c>
       <c r="D104">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="B105" t="str">
-        <v>Boots</v>
+        <v>Eating Out</v>
       </c>
       <c r="C105" t="str">
-        <v>Face Moisturizer</v>
+        <v>Airport Pret</v>
       </c>
       <c r="D105">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106">
@@ -16062,13 +16062,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B106" t="str">
-        <v>Provisions</v>
+        <v>Boots</v>
       </c>
       <c r="C106" t="str">
-        <v>Eggs</v>
+        <v>Face Moisturizer</v>
       </c>
       <c r="D106">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107">
@@ -16076,13 +16076,13 @@
         <v>2026-05-08</v>
       </c>
       <c r="B107" t="str">
-        <v>Shopping</v>
+        <v>Provisions</v>
       </c>
       <c r="C107" t="str">
-        <v>Belt</v>
+        <v>Eggs</v>
       </c>
       <c r="D107">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -16090,10 +16090,10 @@
         <v>2026-05-08</v>
       </c>
       <c r="B108" t="str">
-        <v>Eating Out</v>
+        <v>Shopping</v>
       </c>
       <c r="C108" t="str">
-        <v>Praveen</v>
+        <v>Belt</v>
       </c>
       <c r="D108">
         <v>7</v>
@@ -16101,30 +16101,30 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="B109" t="str">
-        <v>Travel</v>
+        <v>Eating Out</v>
       </c>
       <c r="C109" t="str">
-        <v>Oyster Card</v>
+        <v>Praveen</v>
       </c>
       <c r="D109">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2026-04-18</v>
+        <v>2026-05-07</v>
       </c>
       <c r="B110" t="str">
-        <v>Souvenir</v>
+        <v>Travel</v>
       </c>
       <c r="C110" t="str">
-        <v>Gift, Biscuits</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D110">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111">
@@ -16132,55 +16132,55 @@
         <v>2026-04-18</v>
       </c>
       <c r="B111" t="str">
-        <v>Groceries</v>
+        <v>Souvenir</v>
       </c>
       <c r="C111" t="str">
-        <v>Corn And Gauva</v>
+        <v>Gift, Biscuits</v>
       </c>
       <c r="D111">
-        <v>3.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2026-04-14</v>
+        <v>2026-04-18</v>
       </c>
       <c r="B112" t="str">
-        <v>Travel</v>
+        <v>Groceries</v>
       </c>
       <c r="C112" t="str">
-        <v>Oyster Card</v>
+        <v>Corn And Gauva</v>
       </c>
       <c r="D112">
-        <v>30</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2026-03-31</v>
+        <v>2026-04-14</v>
       </c>
       <c r="B113" t="str">
         <v>Travel</v>
       </c>
       <c r="C113" t="str">
-        <v>Total Tfl Cost</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D113">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2026-04-11</v>
+        <v>2026-03-31</v>
       </c>
       <c r="B114" t="str">
-        <v>Praveen Shoes</v>
+        <v>Travel</v>
       </c>
       <c r="C114" t="str">
-        <v>Shoes</v>
+        <v>Total Tfl Cost</v>
       </c>
       <c r="D114">
-        <v>110</v>
+        <v>67</v>
       </c>
     </row>
     <row r="115">
@@ -16188,27 +16188,27 @@
         <v>2026-04-11</v>
       </c>
       <c r="B115" t="str">
-        <v>Eating Out</v>
+        <v>Praveen Shoes</v>
       </c>
       <c r="C115" t="str">
-        <v>Spitalfield Market</v>
+        <v>Shoes</v>
       </c>
       <c r="D115">
-        <v>8</v>
+        <v>110</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="B116" t="str">
         <v>Eating Out</v>
       </c>
       <c r="C116" t="str">
-        <v>Too Good To Go</v>
+        <v>Spitalfield Market</v>
       </c>
       <c r="D116">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117">
@@ -16216,10 +16216,10 @@
         <v>2026-04-09</v>
       </c>
       <c r="B117" t="str">
-        <v>Groceries</v>
+        <v>Eating Out</v>
       </c>
       <c r="C117" t="str">
-        <v>Yogurt</v>
+        <v>Too Good To Go</v>
       </c>
       <c r="D117">
         <v>4</v>
@@ -16227,72 +16227,72 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-09</v>
       </c>
       <c r="B118" t="str">
-        <v>Visa Fee</v>
+        <v>Groceries</v>
       </c>
       <c r="C118" t="str">
-        <v>Visa Gee</v>
+        <v>Yogurt</v>
       </c>
       <c r="D118">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B119" t="str">
-        <v>Travel</v>
+        <v>Visa Fee</v>
       </c>
       <c r="C119" t="str">
-        <v>Oyster Card</v>
+        <v>Visa Gee</v>
       </c>
       <c r="D119">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2026-04-07</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B120" t="str">
-        <v>Visa Picture</v>
+        <v>Travel</v>
       </c>
       <c r="C120" t="str">
-        <v>Snappy Snap</v>
+        <v>Oyster Card</v>
       </c>
       <c r="D120">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-07</v>
       </c>
       <c r="B121" t="str">
-        <v>Provisions</v>
+        <v>Visa Picture</v>
       </c>
       <c r="C121" t="str">
-        <v>Water Bottle</v>
+        <v>Snappy Snap</v>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="B122" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C122" t="str">
-        <v>Poornima Roti Curry(malaysia Food)</v>
+        <v>Water Bottle</v>
       </c>
       <c r="D122">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -16300,41 +16300,41 @@
         <v>2026-04-06</v>
       </c>
       <c r="B123" t="str">
-        <v>Germany Visa Stuff</v>
+        <v>Eating Out</v>
       </c>
       <c r="C123" t="str">
-        <v>Travel Insurance, Airbnb</v>
+        <v>Poornima Roti Curry(malaysia Food)</v>
       </c>
       <c r="D123">
-        <v>111</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="B124" t="str">
-        <v>Provisions</v>
+        <v>Germany Visa Stuff</v>
       </c>
       <c r="C124" t="str">
-        <v>Yogurt, Lemon</v>
+        <v>Travel Insurance, Airbnb</v>
       </c>
       <c r="D124">
-        <v>3</v>
+        <v>111</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="B125" t="str">
         <v>Provisions</v>
       </c>
       <c r="C125" t="str">
-        <v>Rice Flour, Oil,</v>
+        <v>Yogurt, Lemon</v>
       </c>
       <c r="D125">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -16342,13 +16342,13 @@
         <v>2026-04-04</v>
       </c>
       <c r="B126" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C126" t="str">
-        <v>Spinach, Ginger, Vegetable</v>
+        <v>Rice Flour, Oil,</v>
       </c>
       <c r="D126">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127">
@@ -16356,27 +16356,27 @@
         <v>2026-04-04</v>
       </c>
       <c r="B127" t="str">
-        <v>Meats</v>
+        <v>Groceries</v>
       </c>
       <c r="C127" t="str">
-        <v>Lamb And Chicken</v>
+        <v>Spinach, Ginger, Vegetable</v>
       </c>
       <c r="D127">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-04</v>
       </c>
       <c r="B128" t="str">
-        <v>Cricket Tickets</v>
+        <v>Meats</v>
       </c>
       <c r="C128" t="str">
-        <v>Lords Women World Cup</v>
+        <v>Lamb And Chicken</v>
       </c>
       <c r="D128">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129">
@@ -16384,27 +16384,27 @@
         <v>2026-04-02</v>
       </c>
       <c r="B129" t="str">
-        <v>Provisions</v>
+        <v>Cricket Tickets</v>
       </c>
       <c r="C129" t="str">
-        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
+        <v>Lords Women World Cup</v>
       </c>
       <c r="D129">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-02</v>
       </c>
       <c r="B130" t="str">
         <v>Provisions</v>
       </c>
       <c r="C130" t="str">
-        <v>Sainsbury's</v>
+        <v>Yogurt, Milk, Dry Fruit, Broccoli</v>
       </c>
       <c r="D130">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="131">
@@ -16412,27 +16412,27 @@
         <v>2026-03-28</v>
       </c>
       <c r="B131" t="str">
-        <v>Fruits</v>
+        <v>Provisions</v>
       </c>
       <c r="C131" t="str">
-        <v>Blueberries, Avocado, Gauva</v>
+        <v>Sainsbury's</v>
       </c>
       <c r="D131">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-28</v>
       </c>
       <c r="B132" t="str">
-        <v>Movie</v>
+        <v>Fruits</v>
       </c>
       <c r="C132" t="str">
-        <v>Dhurandar</v>
+        <v>Blueberries, Avocado, Gauva</v>
       </c>
       <c r="D132">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
@@ -16440,69 +16440,69 @@
         <v>2026-03-25</v>
       </c>
       <c r="B133" t="str">
-        <v>Provisions</v>
+        <v>Movie</v>
       </c>
       <c r="C133" t="str">
-        <v>Yogurt</v>
+        <v>Dhurandar</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-25</v>
       </c>
       <c r="B134" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C134" t="str">
-        <v>Pizza Pilgrims</v>
+        <v>Yogurt</v>
       </c>
       <c r="D134">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="B135" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C135" t="str">
-        <v>Milk, Yogurt, Flowers, Butter</v>
+        <v>Pizza Pilgrims</v>
       </c>
       <c r="D135">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="B136" t="str">
-        <v>Eating Out</v>
+        <v>Provisions</v>
       </c>
       <c r="C136" t="str">
-        <v>Praveen</v>
+        <v>Milk, Yogurt, Flowers, Butter</v>
       </c>
       <c r="D136">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-17</v>
       </c>
       <c r="B137" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C137" t="str">
-        <v>Provisions</v>
+        <v>Praveen</v>
       </c>
       <c r="D137">
-        <v>59</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
@@ -16510,27 +16510,27 @@
         <v>2026-03-15</v>
       </c>
       <c r="B138" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C138" t="str">
-        <v>Vegetables</v>
+        <v>Provisions</v>
       </c>
       <c r="D138">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-15</v>
       </c>
       <c r="B139" t="str">
-        <v>Fruits</v>
+        <v>Groceries</v>
       </c>
       <c r="C139" t="str">
-        <v>Gauva, Blueberries</v>
+        <v>Vegetables</v>
       </c>
       <c r="D139">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="140">
@@ -16538,13 +16538,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B140" t="str">
-        <v>Eating Out</v>
+        <v>Fruits</v>
       </c>
       <c r="C140" t="str">
-        <v>Haleem And Samosa</v>
+        <v>Gauva, Blueberries</v>
       </c>
       <c r="D140">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141">
@@ -16552,13 +16552,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B141" t="str">
-        <v>Provisions</v>
+        <v>Eating Out</v>
       </c>
       <c r="C141" t="str">
-        <v>Frozen Lotus Stem And Beans</v>
+        <v>Haleem And Samosa</v>
       </c>
       <c r="D141">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142">
@@ -16566,13 +16566,13 @@
         <v>2026-03-14</v>
       </c>
       <c r="B142" t="str">
-        <v>Groceries</v>
+        <v>Provisions</v>
       </c>
       <c r="C142" t="str">
-        <v>Vegetables</v>
+        <v>Frozen Lotus Stem And Beans</v>
       </c>
       <c r="D142">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
@@ -16580,27 +16580,27 @@
         <v>2026-03-14</v>
       </c>
       <c r="B143" t="str">
-        <v>Provisions</v>
+        <v>Groceries</v>
       </c>
       <c r="C143" t="str">
-        <v>Lidl</v>
+        <v>Vegetables</v>
       </c>
       <c r="D143">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-14</v>
       </c>
       <c r="B144" t="str">
-        <v>Medication</v>
+        <v>Provisions</v>
       </c>
       <c r="C144" t="str">
-        <v>Fish Oil, Pregnacare</v>
+        <v>Lidl</v>
       </c>
       <c r="D144">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145">
@@ -16608,69 +16608,69 @@
         <v>2026-03-09</v>
       </c>
       <c r="B145" t="str">
-        <v>Provisions</v>
+        <v>Medication</v>
       </c>
       <c r="C145" t="str">
-        <v>Yogurt, Oats, Sourdough, Detergent</v>
+        <v>Fish Oil, Pregnacare</v>
       </c>
       <c r="D145">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="B146" t="str">
-        <v>Washing</v>
+        <v>Provisions</v>
       </c>
       <c r="C146" t="str">
-        <v>Clothes</v>
+        <v>Yogurt, Oats, Sourdough, Detergent</v>
       </c>
       <c r="D146">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-08</v>
       </c>
       <c r="B147" t="str">
-        <v>Praveen</v>
+        <v>Washing</v>
       </c>
       <c r="C147" t="str">
-        <v>Praveen eating out</v>
+        <v>Clothes</v>
       </c>
       <c r="D147">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="B148" t="str">
-        <v>Meats</v>
+        <v>Praveen</v>
       </c>
       <c r="C148" t="str">
-        <v>Chicken and Fish</v>
+        <v>Praveen eating out</v>
       </c>
       <c r="D148">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-01</v>
       </c>
       <c r="B149" t="str">
-        <v>Groceries</v>
+        <v>Meats</v>
       </c>
       <c r="C149" t="str">
-        <v>Vegetables</v>
+        <v>Chicken and Fish</v>
       </c>
       <c r="D149">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="150">
@@ -16678,32 +16678,46 @@
         <v>2026-03-07</v>
       </c>
       <c r="B150" t="str">
-        <v>Eating Out</v>
+        <v>Groceries</v>
       </c>
       <c r="C150" t="str">
-        <v>Mobos Ethiopian Restaurant</v>
+        <v>Vegetables</v>
       </c>
       <c r="D150">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Eating Out</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Mobos Ethiopian Restaurant</v>
+      </c>
+      <c r="D151">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
         <v>2026-03-06</v>
       </c>
-      <c r="B151" t="str">
+      <c r="B152" t="str">
         <v>Provisions</v>
       </c>
-      <c r="C151" t="str">
+      <c r="C152" t="str">
         <v>Milk and Doritos</v>
       </c>
-      <c r="D151">
+      <c r="D152">
         <v>2.95</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D152"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -787,7 +787,7 @@
         <v>15</v>
       </c>
       <c r="F19">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -18998,7 +18998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -19014,15 +19014,15 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mushroom</v>
+        <v>Onion</v>
       </c>
       <c r="B2" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Tomatoes</v>
+        <v>Mushroom</v>
       </c>
       <c r="B3" t="str">
         <v>Yes</v>
@@ -19030,7 +19030,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Carrots</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B4" t="str">
         <v>Yes</v>
@@ -19038,7 +19038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Lemon</v>
+        <v>Carrots</v>
       </c>
       <c r="B5" t="str">
         <v>Yes</v>
@@ -19046,7 +19046,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Mint</v>
+        <v>Lemon</v>
       </c>
       <c r="B6" t="str">
         <v>Yes</v>
@@ -19054,7 +19054,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Peas</v>
+        <v>Mint</v>
       </c>
       <c r="B7" t="str">
         <v>Yes</v>
@@ -19062,7 +19062,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Yogurt</v>
+        <v>Peas</v>
       </c>
       <c r="B8" t="str">
         <v>Yes</v>
@@ -19070,7 +19070,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Toothpaste</v>
+        <v>Yogurt</v>
       </c>
       <c r="B9" t="str">
         <v>Yes</v>
@@ -19078,7 +19078,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Corn Flour</v>
+        <v>Toothpaste</v>
       </c>
       <c r="B10" t="str">
         <v>Yes</v>
@@ -19086,7 +19086,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Onion</v>
+        <v>Corn Flour</v>
       </c>
       <c r="B11" t="str">
         <v>Yes</v>
@@ -19094,7 +19094,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Toilet Tissue</v>
+        <v>Onion</v>
       </c>
       <c r="B12" t="str">
         <v>Yes</v>
@@ -19102,7 +19102,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Yogurt</v>
+        <v>Toilet Tissue</v>
       </c>
       <c r="B13" t="str">
         <v>Yes</v>
@@ -19110,7 +19110,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Cucumber</v>
+        <v>Yogurt</v>
       </c>
       <c r="B14" t="str">
         <v>Yes</v>
@@ -19118,7 +19118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Chilli</v>
+        <v>Cucumber</v>
       </c>
       <c r="B15" t="str">
         <v>Yes</v>
@@ -19126,7 +19126,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Tomatoes</v>
+        <v>Chilli</v>
       </c>
       <c r="B16" t="str">
         <v>Yes</v>
@@ -19134,7 +19134,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Palak/gongura</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B17" t="str">
         <v>Yes</v>
@@ -19142,7 +19142,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Fresh Vegetables</v>
+        <v>Palak/gongura</v>
       </c>
       <c r="B18" t="str">
         <v>Yes</v>
@@ -19150,7 +19150,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Coconut Oil</v>
+        <v>Fresh Vegetables</v>
       </c>
       <c r="B19" t="str">
         <v>Yes</v>
@@ -19158,7 +19158,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Idly Rice</v>
+        <v>Coconut Oil</v>
       </c>
       <c r="B20" t="str">
         <v>Yes</v>
@@ -19166,7 +19166,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Chicken</v>
+        <v>Idly Rice</v>
       </c>
       <c r="B21" t="str">
         <v>Yes</v>
@@ -19174,7 +19174,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jysk Bed Cover</v>
+        <v>Chicken</v>
       </c>
       <c r="B22" t="str">
         <v>Yes</v>
@@ -19182,7 +19182,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Stromberg Rain Jacket</v>
+        <v>Jysk Bed Cover</v>
       </c>
       <c r="B23" t="str">
         <v>Yes</v>
@@ -19190,7 +19190,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Whipping Cream</v>
+        <v>Stromberg Rain Jacket</v>
       </c>
       <c r="B24" t="str">
         <v>Yes</v>
@@ -19198,7 +19198,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Gram Flour</v>
+        <v>Whipping Cream</v>
       </c>
       <c r="B25" t="str">
         <v>Yes</v>
@@ -19206,7 +19206,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Coriander</v>
+        <v>Gram Flour</v>
       </c>
       <c r="B26" t="str">
         <v>Yes</v>
@@ -19214,15 +19214,23 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Rose Water</v>
+        <v>Coriander</v>
       </c>
       <c r="B27" t="str">
         <v>Yes</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Rose Water</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B28"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -18998,7 +18998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -19014,7 +19014,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Onion</v>
+        <v>Potato</v>
       </c>
       <c r="B2" t="str">
         <v>No</v>
@@ -19022,15 +19022,15 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Mushroom</v>
+        <v>Onion</v>
       </c>
       <c r="B3" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Tomatoes</v>
+        <v>Mushroom</v>
       </c>
       <c r="B4" t="str">
         <v>Yes</v>
@@ -19038,7 +19038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Carrots</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B5" t="str">
         <v>Yes</v>
@@ -19046,7 +19046,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Lemon</v>
+        <v>Carrots</v>
       </c>
       <c r="B6" t="str">
         <v>Yes</v>
@@ -19054,7 +19054,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Mint</v>
+        <v>Lemon</v>
       </c>
       <c r="B7" t="str">
         <v>Yes</v>
@@ -19062,7 +19062,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Peas</v>
+        <v>Mint</v>
       </c>
       <c r="B8" t="str">
         <v>Yes</v>
@@ -19070,7 +19070,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Yogurt</v>
+        <v>Peas</v>
       </c>
       <c r="B9" t="str">
         <v>Yes</v>
@@ -19078,7 +19078,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Toothpaste</v>
+        <v>Yogurt</v>
       </c>
       <c r="B10" t="str">
         <v>Yes</v>
@@ -19086,7 +19086,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Corn Flour</v>
+        <v>Toothpaste</v>
       </c>
       <c r="B11" t="str">
         <v>Yes</v>
@@ -19094,7 +19094,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Onion</v>
+        <v>Corn Flour</v>
       </c>
       <c r="B12" t="str">
         <v>Yes</v>
@@ -19102,7 +19102,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Toilet Tissue</v>
+        <v>Onion</v>
       </c>
       <c r="B13" t="str">
         <v>Yes</v>
@@ -19110,7 +19110,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Yogurt</v>
+        <v>Toilet Tissue</v>
       </c>
       <c r="B14" t="str">
         <v>Yes</v>
@@ -19118,7 +19118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Cucumber</v>
+        <v>Yogurt</v>
       </c>
       <c r="B15" t="str">
         <v>Yes</v>
@@ -19126,7 +19126,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Chilli</v>
+        <v>Cucumber</v>
       </c>
       <c r="B16" t="str">
         <v>Yes</v>
@@ -19134,7 +19134,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Tomatoes</v>
+        <v>Chilli</v>
       </c>
       <c r="B17" t="str">
         <v>Yes</v>
@@ -19142,7 +19142,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Palak/gongura</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B18" t="str">
         <v>Yes</v>
@@ -19150,7 +19150,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Fresh Vegetables</v>
+        <v>Palak/gongura</v>
       </c>
       <c r="B19" t="str">
         <v>Yes</v>
@@ -19158,7 +19158,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Coconut Oil</v>
+        <v>Fresh Vegetables</v>
       </c>
       <c r="B20" t="str">
         <v>Yes</v>
@@ -19166,7 +19166,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Idly Rice</v>
+        <v>Coconut Oil</v>
       </c>
       <c r="B21" t="str">
         <v>Yes</v>
@@ -19174,7 +19174,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Chicken</v>
+        <v>Idly Rice</v>
       </c>
       <c r="B22" t="str">
         <v>Yes</v>
@@ -19182,7 +19182,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jysk Bed Cover</v>
+        <v>Chicken</v>
       </c>
       <c r="B23" t="str">
         <v>Yes</v>
@@ -19190,7 +19190,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Stromberg Rain Jacket</v>
+        <v>Jysk Bed Cover</v>
       </c>
       <c r="B24" t="str">
         <v>Yes</v>
@@ -19198,7 +19198,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Whipping Cream</v>
+        <v>Stromberg Rain Jacket</v>
       </c>
       <c r="B25" t="str">
         <v>Yes</v>
@@ -19206,7 +19206,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Gram Flour</v>
+        <v>Whipping Cream</v>
       </c>
       <c r="B26" t="str">
         <v>Yes</v>
@@ -19214,7 +19214,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Coriander</v>
+        <v>Gram Flour</v>
       </c>
       <c r="B27" t="str">
         <v>Yes</v>
@@ -19222,15 +19222,23 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Rose Water</v>
+        <v>Coriander</v>
       </c>
       <c r="B28" t="str">
         <v>Yes</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Rose Water</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B29"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -18998,7 +18998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -19014,7 +19014,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Potato</v>
+        <v>Milk</v>
       </c>
       <c r="B2" t="str">
         <v>No</v>
@@ -19022,7 +19022,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Onion</v>
+        <v>Potato</v>
       </c>
       <c r="B3" t="str">
         <v>No</v>
@@ -19030,15 +19030,15 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Mushroom</v>
+        <v>Onion</v>
       </c>
       <c r="B4" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Tomatoes</v>
+        <v>Mushroom</v>
       </c>
       <c r="B5" t="str">
         <v>Yes</v>
@@ -19046,7 +19046,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Carrots</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B6" t="str">
         <v>Yes</v>
@@ -19054,7 +19054,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Lemon</v>
+        <v>Carrots</v>
       </c>
       <c r="B7" t="str">
         <v>Yes</v>
@@ -19062,7 +19062,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Mint</v>
+        <v>Lemon</v>
       </c>
       <c r="B8" t="str">
         <v>Yes</v>
@@ -19070,7 +19070,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Peas</v>
+        <v>Mint</v>
       </c>
       <c r="B9" t="str">
         <v>Yes</v>
@@ -19078,7 +19078,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Yogurt</v>
+        <v>Peas</v>
       </c>
       <c r="B10" t="str">
         <v>Yes</v>
@@ -19086,7 +19086,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Toothpaste</v>
+        <v>Yogurt</v>
       </c>
       <c r="B11" t="str">
         <v>Yes</v>
@@ -19094,7 +19094,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Corn Flour</v>
+        <v>Toothpaste</v>
       </c>
       <c r="B12" t="str">
         <v>Yes</v>
@@ -19102,7 +19102,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Onion</v>
+        <v>Corn Flour</v>
       </c>
       <c r="B13" t="str">
         <v>Yes</v>
@@ -19110,7 +19110,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Toilet Tissue</v>
+        <v>Onion</v>
       </c>
       <c r="B14" t="str">
         <v>Yes</v>
@@ -19118,7 +19118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Yogurt</v>
+        <v>Toilet Tissue</v>
       </c>
       <c r="B15" t="str">
         <v>Yes</v>
@@ -19126,7 +19126,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Cucumber</v>
+        <v>Yogurt</v>
       </c>
       <c r="B16" t="str">
         <v>Yes</v>
@@ -19134,7 +19134,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Chilli</v>
+        <v>Cucumber</v>
       </c>
       <c r="B17" t="str">
         <v>Yes</v>
@@ -19142,7 +19142,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Tomatoes</v>
+        <v>Chilli</v>
       </c>
       <c r="B18" t="str">
         <v>Yes</v>
@@ -19150,7 +19150,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Palak/gongura</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B19" t="str">
         <v>Yes</v>
@@ -19158,7 +19158,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Fresh Vegetables</v>
+        <v>Palak/gongura</v>
       </c>
       <c r="B20" t="str">
         <v>Yes</v>
@@ -19166,7 +19166,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Coconut Oil</v>
+        <v>Fresh Vegetables</v>
       </c>
       <c r="B21" t="str">
         <v>Yes</v>
@@ -19174,7 +19174,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Idly Rice</v>
+        <v>Coconut Oil</v>
       </c>
       <c r="B22" t="str">
         <v>Yes</v>
@@ -19182,7 +19182,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Chicken</v>
+        <v>Idly Rice</v>
       </c>
       <c r="B23" t="str">
         <v>Yes</v>
@@ -19190,7 +19190,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jysk Bed Cover</v>
+        <v>Chicken</v>
       </c>
       <c r="B24" t="str">
         <v>Yes</v>
@@ -19198,7 +19198,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Stromberg Rain Jacket</v>
+        <v>Jysk Bed Cover</v>
       </c>
       <c r="B25" t="str">
         <v>Yes</v>
@@ -19206,7 +19206,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Whipping Cream</v>
+        <v>Stromberg Rain Jacket</v>
       </c>
       <c r="B26" t="str">
         <v>Yes</v>
@@ -19214,7 +19214,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Gram Flour</v>
+        <v>Whipping Cream</v>
       </c>
       <c r="B27" t="str">
         <v>Yes</v>
@@ -19222,7 +19222,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Coriander</v>
+        <v>Gram Flour</v>
       </c>
       <c r="B28" t="str">
         <v>Yes</v>
@@ -19230,15 +19230,23 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Rose Water</v>
+        <v>Coriander</v>
       </c>
       <c r="B29" t="str">
         <v>Yes</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Rose Water</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B30"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -18998,7 +18998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -19014,7 +19014,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Milk</v>
+        <v>Paracetamol</v>
       </c>
       <c r="B2" t="str">
         <v>No</v>
@@ -19022,7 +19022,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Potato</v>
+        <v>Milk</v>
       </c>
       <c r="B3" t="str">
         <v>No</v>
@@ -19030,7 +19030,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Onion</v>
+        <v>Potato</v>
       </c>
       <c r="B4" t="str">
         <v>No</v>
@@ -19038,15 +19038,15 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mushroom</v>
+        <v>Onion</v>
       </c>
       <c r="B5" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Tomatoes</v>
+        <v>Mushroom</v>
       </c>
       <c r="B6" t="str">
         <v>Yes</v>
@@ -19054,7 +19054,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Carrots</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B7" t="str">
         <v>Yes</v>
@@ -19062,7 +19062,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Lemon</v>
+        <v>Carrots</v>
       </c>
       <c r="B8" t="str">
         <v>Yes</v>
@@ -19070,7 +19070,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Mint</v>
+        <v>Lemon</v>
       </c>
       <c r="B9" t="str">
         <v>Yes</v>
@@ -19078,7 +19078,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Peas</v>
+        <v>Mint</v>
       </c>
       <c r="B10" t="str">
         <v>Yes</v>
@@ -19086,7 +19086,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Yogurt</v>
+        <v>Peas</v>
       </c>
       <c r="B11" t="str">
         <v>Yes</v>
@@ -19094,7 +19094,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Toothpaste</v>
+        <v>Yogurt</v>
       </c>
       <c r="B12" t="str">
         <v>Yes</v>
@@ -19102,7 +19102,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Corn Flour</v>
+        <v>Toothpaste</v>
       </c>
       <c r="B13" t="str">
         <v>Yes</v>
@@ -19110,7 +19110,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Onion</v>
+        <v>Corn Flour</v>
       </c>
       <c r="B14" t="str">
         <v>Yes</v>
@@ -19118,7 +19118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Toilet Tissue</v>
+        <v>Onion</v>
       </c>
       <c r="B15" t="str">
         <v>Yes</v>
@@ -19126,7 +19126,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Yogurt</v>
+        <v>Toilet Tissue</v>
       </c>
       <c r="B16" t="str">
         <v>Yes</v>
@@ -19134,7 +19134,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Cucumber</v>
+        <v>Yogurt</v>
       </c>
       <c r="B17" t="str">
         <v>Yes</v>
@@ -19142,7 +19142,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Chilli</v>
+        <v>Cucumber</v>
       </c>
       <c r="B18" t="str">
         <v>Yes</v>
@@ -19150,7 +19150,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Tomatoes</v>
+        <v>Chilli</v>
       </c>
       <c r="B19" t="str">
         <v>Yes</v>
@@ -19158,7 +19158,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Palak/gongura</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B20" t="str">
         <v>Yes</v>
@@ -19166,7 +19166,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Fresh Vegetables</v>
+        <v>Palak/gongura</v>
       </c>
       <c r="B21" t="str">
         <v>Yes</v>
@@ -19174,7 +19174,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Coconut Oil</v>
+        <v>Fresh Vegetables</v>
       </c>
       <c r="B22" t="str">
         <v>Yes</v>
@@ -19182,7 +19182,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Idly Rice</v>
+        <v>Coconut Oil</v>
       </c>
       <c r="B23" t="str">
         <v>Yes</v>
@@ -19190,7 +19190,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Chicken</v>
+        <v>Idly Rice</v>
       </c>
       <c r="B24" t="str">
         <v>Yes</v>
@@ -19198,7 +19198,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jysk Bed Cover</v>
+        <v>Chicken</v>
       </c>
       <c r="B25" t="str">
         <v>Yes</v>
@@ -19206,7 +19206,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Stromberg Rain Jacket</v>
+        <v>Jysk Bed Cover</v>
       </c>
       <c r="B26" t="str">
         <v>Yes</v>
@@ -19214,7 +19214,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Whipping Cream</v>
+        <v>Stromberg Rain Jacket</v>
       </c>
       <c r="B27" t="str">
         <v>Yes</v>
@@ -19222,7 +19222,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Gram Flour</v>
+        <v>Whipping Cream</v>
       </c>
       <c r="B28" t="str">
         <v>Yes</v>
@@ -19230,7 +19230,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Coriander</v>
+        <v>Gram Flour</v>
       </c>
       <c r="B29" t="str">
         <v>Yes</v>
@@ -19238,15 +19238,23 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Rose Water</v>
+        <v>Coriander</v>
       </c>
       <c r="B30" t="str">
         <v>Yes</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Rose Water</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B31"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -18998,7 +18998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B33"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -19014,7 +19014,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Paracetamol</v>
+        <v>Domex</v>
       </c>
       <c r="B2" t="str">
         <v>No</v>
@@ -19022,7 +19022,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Milk</v>
+        <v>Thermometer</v>
       </c>
       <c r="B3" t="str">
         <v>No</v>
@@ -19030,7 +19030,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Potato</v>
+        <v>Paracetamol</v>
       </c>
       <c r="B4" t="str">
         <v>No</v>
@@ -19038,7 +19038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Onion</v>
+        <v>Milk</v>
       </c>
       <c r="B5" t="str">
         <v>No</v>
@@ -19046,23 +19046,23 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Mushroom</v>
+        <v>Potato</v>
       </c>
       <c r="B6" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Tomatoes</v>
+        <v>Onion</v>
       </c>
       <c r="B7" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Carrots</v>
+        <v>Mushroom</v>
       </c>
       <c r="B8" t="str">
         <v>Yes</v>
@@ -19070,7 +19070,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lemon</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B9" t="str">
         <v>Yes</v>
@@ -19078,7 +19078,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Mint</v>
+        <v>Carrots</v>
       </c>
       <c r="B10" t="str">
         <v>Yes</v>
@@ -19086,7 +19086,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Peas</v>
+        <v>Lemon</v>
       </c>
       <c r="B11" t="str">
         <v>Yes</v>
@@ -19094,7 +19094,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Yogurt</v>
+        <v>Mint</v>
       </c>
       <c r="B12" t="str">
         <v>Yes</v>
@@ -19102,7 +19102,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Toothpaste</v>
+        <v>Peas</v>
       </c>
       <c r="B13" t="str">
         <v>Yes</v>
@@ -19110,7 +19110,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Corn Flour</v>
+        <v>Yogurt</v>
       </c>
       <c r="B14" t="str">
         <v>Yes</v>
@@ -19118,7 +19118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Onion</v>
+        <v>Toothpaste</v>
       </c>
       <c r="B15" t="str">
         <v>Yes</v>
@@ -19126,7 +19126,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Toilet Tissue</v>
+        <v>Corn Flour</v>
       </c>
       <c r="B16" t="str">
         <v>Yes</v>
@@ -19134,7 +19134,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Yogurt</v>
+        <v>Onion</v>
       </c>
       <c r="B17" t="str">
         <v>Yes</v>
@@ -19142,7 +19142,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Cucumber</v>
+        <v>Toilet Tissue</v>
       </c>
       <c r="B18" t="str">
         <v>Yes</v>
@@ -19150,7 +19150,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Chilli</v>
+        <v>Yogurt</v>
       </c>
       <c r="B19" t="str">
         <v>Yes</v>
@@ -19158,7 +19158,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tomatoes</v>
+        <v>Cucumber</v>
       </c>
       <c r="B20" t="str">
         <v>Yes</v>
@@ -19166,7 +19166,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Palak/gongura</v>
+        <v>Chilli</v>
       </c>
       <c r="B21" t="str">
         <v>Yes</v>
@@ -19174,7 +19174,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Fresh Vegetables</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B22" t="str">
         <v>Yes</v>
@@ -19182,7 +19182,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Coconut Oil</v>
+        <v>Palak/gongura</v>
       </c>
       <c r="B23" t="str">
         <v>Yes</v>
@@ -19190,7 +19190,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Idly Rice</v>
+        <v>Fresh Vegetables</v>
       </c>
       <c r="B24" t="str">
         <v>Yes</v>
@@ -19198,7 +19198,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Chicken</v>
+        <v>Coconut Oil</v>
       </c>
       <c r="B25" t="str">
         <v>Yes</v>
@@ -19206,7 +19206,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jysk Bed Cover</v>
+        <v>Idly Rice</v>
       </c>
       <c r="B26" t="str">
         <v>Yes</v>
@@ -19214,7 +19214,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Stromberg Rain Jacket</v>
+        <v>Chicken</v>
       </c>
       <c r="B27" t="str">
         <v>Yes</v>
@@ -19222,7 +19222,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Whipping Cream</v>
+        <v>Jysk Bed Cover</v>
       </c>
       <c r="B28" t="str">
         <v>Yes</v>
@@ -19230,7 +19230,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Gram Flour</v>
+        <v>Stromberg Rain Jacket</v>
       </c>
       <c r="B29" t="str">
         <v>Yes</v>
@@ -19238,7 +19238,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Coriander</v>
+        <v>Whipping Cream</v>
       </c>
       <c r="B30" t="str">
         <v>Yes</v>
@@ -19246,15 +19246,31 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Rose Water</v>
+        <v>Gram Flour</v>
       </c>
       <c r="B31" t="str">
         <v>Yes</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Coriander</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Rose Water</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B33"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -18998,7 +18998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -19014,7 +19014,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Domex</v>
+        <v>Hand Wash</v>
       </c>
       <c r="B2" t="str">
         <v>No</v>
@@ -19022,7 +19022,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Thermometer</v>
+        <v>Domex</v>
       </c>
       <c r="B3" t="str">
         <v>No</v>
@@ -19030,7 +19030,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Paracetamol</v>
+        <v>Thermometer</v>
       </c>
       <c r="B4" t="str">
         <v>No</v>
@@ -19038,7 +19038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Milk</v>
+        <v>Paracetamol</v>
       </c>
       <c r="B5" t="str">
         <v>No</v>
@@ -19046,7 +19046,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Potato</v>
+        <v>Milk</v>
       </c>
       <c r="B6" t="str">
         <v>No</v>
@@ -19054,7 +19054,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Onion</v>
+        <v>Potato</v>
       </c>
       <c r="B7" t="str">
         <v>No</v>
@@ -19062,15 +19062,15 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Mushroom</v>
+        <v>Onion</v>
       </c>
       <c r="B8" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Tomatoes</v>
+        <v>Mushroom</v>
       </c>
       <c r="B9" t="str">
         <v>Yes</v>
@@ -19078,7 +19078,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Carrots</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B10" t="str">
         <v>Yes</v>
@@ -19086,7 +19086,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lemon</v>
+        <v>Carrots</v>
       </c>
       <c r="B11" t="str">
         <v>Yes</v>
@@ -19094,7 +19094,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Mint</v>
+        <v>Lemon</v>
       </c>
       <c r="B12" t="str">
         <v>Yes</v>
@@ -19102,7 +19102,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Peas</v>
+        <v>Mint</v>
       </c>
       <c r="B13" t="str">
         <v>Yes</v>
@@ -19110,7 +19110,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Yogurt</v>
+        <v>Peas</v>
       </c>
       <c r="B14" t="str">
         <v>Yes</v>
@@ -19118,7 +19118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Toothpaste</v>
+        <v>Yogurt</v>
       </c>
       <c r="B15" t="str">
         <v>Yes</v>
@@ -19126,7 +19126,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Corn Flour</v>
+        <v>Toothpaste</v>
       </c>
       <c r="B16" t="str">
         <v>Yes</v>
@@ -19134,7 +19134,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Onion</v>
+        <v>Corn Flour</v>
       </c>
       <c r="B17" t="str">
         <v>Yes</v>
@@ -19142,7 +19142,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Toilet Tissue</v>
+        <v>Onion</v>
       </c>
       <c r="B18" t="str">
         <v>Yes</v>
@@ -19150,7 +19150,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Yogurt</v>
+        <v>Toilet Tissue</v>
       </c>
       <c r="B19" t="str">
         <v>Yes</v>
@@ -19158,7 +19158,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Cucumber</v>
+        <v>Yogurt</v>
       </c>
       <c r="B20" t="str">
         <v>Yes</v>
@@ -19166,7 +19166,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Chilli</v>
+        <v>Cucumber</v>
       </c>
       <c r="B21" t="str">
         <v>Yes</v>
@@ -19174,7 +19174,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tomatoes</v>
+        <v>Chilli</v>
       </c>
       <c r="B22" t="str">
         <v>Yes</v>
@@ -19182,7 +19182,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Palak/gongura</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B23" t="str">
         <v>Yes</v>
@@ -19190,7 +19190,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Fresh Vegetables</v>
+        <v>Palak/gongura</v>
       </c>
       <c r="B24" t="str">
         <v>Yes</v>
@@ -19198,7 +19198,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Coconut Oil</v>
+        <v>Fresh Vegetables</v>
       </c>
       <c r="B25" t="str">
         <v>Yes</v>
@@ -19206,7 +19206,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Idly Rice</v>
+        <v>Coconut Oil</v>
       </c>
       <c r="B26" t="str">
         <v>Yes</v>
@@ -19214,7 +19214,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Chicken</v>
+        <v>Idly Rice</v>
       </c>
       <c r="B27" t="str">
         <v>Yes</v>
@@ -19222,7 +19222,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jysk Bed Cover</v>
+        <v>Chicken</v>
       </c>
       <c r="B28" t="str">
         <v>Yes</v>
@@ -19230,7 +19230,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Stromberg Rain Jacket</v>
+        <v>Jysk Bed Cover</v>
       </c>
       <c r="B29" t="str">
         <v>Yes</v>
@@ -19238,7 +19238,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Whipping Cream</v>
+        <v>Stromberg Rain Jacket</v>
       </c>
       <c r="B30" t="str">
         <v>Yes</v>
@@ -19246,7 +19246,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Gram Flour</v>
+        <v>Whipping Cream</v>
       </c>
       <c r="B31" t="str">
         <v>Yes</v>
@@ -19254,7 +19254,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Coriander</v>
+        <v>Gram Flour</v>
       </c>
       <c r="B32" t="str">
         <v>Yes</v>
@@ -19262,15 +19262,23 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Rose Water</v>
+        <v>Coriander</v>
       </c>
       <c r="B33" t="str">
         <v>Yes</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Rose Water</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B34"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/backup.xlsx
+++ b/data/backup.xlsx
@@ -20258,7 +20258,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B10"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -20277,7 +20277,7 @@
         <v>Hand Wash</v>
       </c>
       <c r="B2" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="3">
@@ -20285,7 +20285,7 @@
         <v>Domex</v>
       </c>
       <c r="B3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="4">
@@ -20314,15 +20314,15 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Potato</v>
+        <v>Tomatoes</v>
       </c>
       <c r="B7" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Onion</v>
+        <v>Palak/gongura</v>
       </c>
       <c r="B8" t="str">
         <v>Yes</v>
@@ -20330,7 +20330,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Mushroom</v>
+        <v>Fresh Vegetables</v>
       </c>
       <c r="B9" t="str">
         <v>Yes</v>
@@ -20338,207 +20338,15 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Tomatoes</v>
+        <v>Coconut Oil</v>
       </c>
       <c r="B10" t="str">
         <v>Yes</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Carrots</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Lemon</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Mint</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Peas</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Yogurt</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Toothpaste</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Corn Flour</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Onion</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Toilet Tissue</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Yogurt</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Cucumber</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Chilli</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Tomatoes</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Palak/gongura</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Fresh Vegetables</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Coconut Oil</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Idly Rice</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Chicken</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Jysk Bed Cover</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Stromberg Rain Jacket</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Whipping Cream</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Gram Flour</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Coriander</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Rose Water</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
   </ignoredErrors>
 </worksheet>
 </file>
